--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43006DC8-30F9-4AFC-AC85-826770876C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDED9D92-C566-4284-83AC-8A0BEBB5F442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,66 +943,156 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_026</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_005</t>
   </si>
   <si>
@@ -1027,60 +1117,6 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_008</t>
   </si>
   <si>
@@ -1093,72 +1129,72 @@
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
     <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
   </si>
   <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
-  </si>
-  <si>
     <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
   </si>
   <si>
@@ -1171,46 +1207,100 @@
     <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
     <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
   </si>
   <si>
     <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_005</t>
@@ -1219,76 +1309,76 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_003</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_018</t>
@@ -1309,94 +1399,88 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
   </si>
   <si>
     <t>elc_won_JPN_005</t>
@@ -1405,70 +1489,70 @@
     <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
     <t>elc_won_JPN_003</t>
   </si>
   <si>
     <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
   </si>
   <si>
     <t>elc_won_JPN_018</t>
@@ -1489,88 +1573,28 @@
     <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_015</t>
@@ -1597,6 +1621,144 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_006</t>
   </si>
   <si>
@@ -1621,10 +1783,40 @@
     <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_031</t>
@@ -1645,196 +1837,22 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_015</t>
@@ -1861,6 +1879,126 @@
     <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_006</t>
   </si>
   <si>
@@ -1882,10 +2020,31 @@
     <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_031</t>
@@ -1901,165 +2060,6 @@
   </si>
   <si>
     <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA9E96A-0227-4D53-9B77-61D421C33C6B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAA360C-F5A7-400E-9F13-8CA3B01D6EE3}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99812715296949239</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB11">
-        <v>34.33552889264039</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7692,10 +7692,10 @@
         <v>424</v>
       </c>
       <c r="AO11">
-        <v>0.99876486181024959</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP11">
-        <v>22.644200145424321</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7728,10 +7728,10 @@
         <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.99246863181599732</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD11">
-        <v>138.07508337338285</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99905729110642394</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB12">
-        <v>17.282996382227537</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7835,13 +7835,13 @@
         <v>425</v>
       </c>
       <c r="AN12" t="s">
-        <v>426</v>
+        <v>345</v>
       </c>
       <c r="AO12">
-        <v>0.99621233314208923</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP12">
-        <v>69.440559061696689</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7871,13 +7871,13 @@
         <v>571</v>
       </c>
       <c r="BB12" t="s">
-        <v>572</v>
+        <v>341</v>
       </c>
       <c r="BC12">
-        <v>0.99412039195829205</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD12">
-        <v>107.79281409797902</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.99419544959877137</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB13">
-        <v>106.41675735585797</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7978,16 +7978,16 @@
         <v>365</v>
       </c>
       <c r="AM13" t="s">
+        <v>426</v>
+      </c>
+      <c r="AN13" t="s">
         <v>427</v>
       </c>
-      <c r="AN13" t="s">
-        <v>428</v>
-      </c>
       <c r="AO13">
-        <v>0.99825578453224051</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP13">
-        <v>31.977283575591127</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BB13" t="s">
-        <v>574</v>
+        <v>341</v>
       </c>
       <c r="BC13">
-        <v>0.97589985979527272</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD13">
-        <v>441.83590375333313</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.98845903150961834</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB14">
-        <v>211.58442232366301</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8124,16 +8124,16 @@
         <v>367</v>
       </c>
       <c r="AM14" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN14" t="s">
         <v>429</v>
       </c>
-      <c r="AN14" t="s">
-        <v>347</v>
-      </c>
       <c r="AO14">
-        <v>0.96316479569784719</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP14">
-        <v>675.31207887280175</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BB14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="BC14">
-        <v>0.99502210016107762</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD14">
-        <v>91.26149704691008</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.98176582039027138</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB15">
-        <v>334.29329284502461</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>431</v>
       </c>
       <c r="AO15">
-        <v>0.99192535126433146</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP15">
-        <v>148.0352268205892</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8306,16 +8306,16 @@
         <v>489</v>
       </c>
       <c r="BA15" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="BB15" t="s">
-        <v>347</v>
+        <v>576</v>
       </c>
       <c r="BC15">
-        <v>0.95957195194316591</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD15">
-        <v>741.18088104195795</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99794257572004419</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB16">
-        <v>37.719445132522388</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8419,13 +8419,13 @@
         <v>432</v>
       </c>
       <c r="AN16" t="s">
-        <v>338</v>
+        <v>433</v>
       </c>
       <c r="AO16">
-        <v>0.98949004263841422</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP16">
-        <v>192.68255162907312</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
+        <v>577</v>
+      </c>
+      <c r="BB16" t="s">
         <v>578</v>
       </c>
-      <c r="BB16" t="s">
-        <v>579</v>
-      </c>
       <c r="BC16">
-        <v>0.99232897920121688</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD16">
-        <v>140.63538131102445</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99330431978332978</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB17">
-        <v>122.75413730562111</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8562,16 +8562,16 @@
         <v>373</v>
       </c>
       <c r="AM17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO17">
-        <v>0.99781438034778358</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP17">
-        <v>40.069693623967019</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
+        <v>579</v>
+      </c>
+      <c r="BB17" t="s">
         <v>580</v>
       </c>
-      <c r="BB17" t="s">
-        <v>581</v>
-      </c>
       <c r="BC17">
-        <v>0.9205295464439136</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD17">
-        <v>1456.9583151949184</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Z18" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.97905997046933124</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB18">
-        <v>383.90054139559413</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8708,16 +8708,16 @@
         <v>375</v>
       </c>
       <c r="AM18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN18" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO18">
-        <v>0.99682717865030179</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP18">
-        <v>58.168391411134159</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB18" t="s">
         <v>582</v>
       </c>
-      <c r="BB18" t="s">
-        <v>583</v>
-      </c>
       <c r="BC18">
-        <v>0.98881218539944515</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD18">
-        <v>205.10993434350485</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="Z19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99810840151368141</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB19">
-        <v>34.679305582508199</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8854,16 +8854,16 @@
         <v>377</v>
       </c>
       <c r="AM19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO19">
-        <v>0.99770761097472849</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP19">
-        <v>42.027132129978384</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
+        <v>583</v>
+      </c>
+      <c r="BB19" t="s">
         <v>584</v>
       </c>
-      <c r="BB19" t="s">
-        <v>585</v>
-      </c>
       <c r="BC19">
-        <v>0.95726256957223688</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD19">
-        <v>783.51955784232393</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="Z20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99854662761279667</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB20">
-        <v>26.645160432060571</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9000,16 +9000,16 @@
         <v>379</v>
       </c>
       <c r="AM20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO20">
-        <v>0.99829462257458279</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP20">
-        <v>31.265252799315078</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
+        <v>585</v>
+      </c>
+      <c r="BB20" t="s">
         <v>586</v>
       </c>
-      <c r="BB20" t="s">
-        <v>587</v>
-      </c>
       <c r="BC20">
-        <v>0.98779966071713954</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD20">
-        <v>223.67288685244134</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="Z21" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AA21">
-        <v>0.9983436906516876</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB21">
-        <v>30.365671385728113</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9146,16 +9146,16 @@
         <v>381</v>
       </c>
       <c r="AM21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN21" t="s">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="AO21">
-        <v>0.99763984073088841</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP21">
-        <v>43.269586600378275</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
+        <v>587</v>
+      </c>
+      <c r="BB21" t="s">
         <v>588</v>
       </c>
-      <c r="BB21" t="s">
-        <v>589</v>
-      </c>
       <c r="BC21">
-        <v>0.99604247516580058</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD21">
-        <v>72.554621960323615</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s">
         <v>345</v>
       </c>
       <c r="AA22">
-        <v>0.99886682122259174</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB22">
-        <v>20.774944252484079</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9298,10 +9298,10 @@
         <v>444</v>
       </c>
       <c r="AO22">
-        <v>0.9878316475733655</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP22">
-        <v>223.0864611549656</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="BB22" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="BC22">
-        <v>0.98235584693125277</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD22">
-        <v>323.47613959369914</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="Z23" t="s">
         <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.99830231855562213</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB23">
-        <v>31.124159813595057</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9444,10 +9444,10 @@
         <v>446</v>
       </c>
       <c r="AO23">
-        <v>0.99689519939751359</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP23">
-        <v>56.921344378917169</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BB23" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="BC23">
-        <v>0.97218956380622079</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD23">
-        <v>509.85799688595205</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AA24">
-        <v>0.97645815754785015</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB24">
-        <v>431.60044495608111</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>448</v>
       </c>
       <c r="AO24">
-        <v>0.99670212772821787</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP24">
-        <v>60.460991649339221</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
+        <v>591</v>
+      </c>
+      <c r="BB24" t="s">
         <v>592</v>
       </c>
-      <c r="BB24" t="s">
-        <v>347</v>
-      </c>
       <c r="BC24">
-        <v>0.97591598065988894</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD24">
-        <v>441.54035456870389</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AA25">
-        <v>0.99860543314421912</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB25">
-        <v>25.567059022649978</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9736,10 +9736,10 @@
         <v>450</v>
       </c>
       <c r="AO25">
-        <v>0.99870483393763032</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP25">
-        <v>23.744711143443137</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9772,10 +9772,10 @@
         <v>594</v>
       </c>
       <c r="BC25">
-        <v>0.9437657388784082</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD25">
-        <v>1030.9614538958492</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA26">
-        <v>0.99604289943123792</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB26">
-        <v>72.546843760638723</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.99940622505963084</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP26">
-        <v>10.885873906767051</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9915,13 +9915,13 @@
         <v>595</v>
       </c>
       <c r="BB26" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="BC26">
-        <v>0.99536692897647694</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD26">
-        <v>84.939635431255269</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AA27">
-        <v>0.99586101480039024</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB27">
-        <v>75.881395326178321</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99869874972548245</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP27">
-        <v>23.856255032822389</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10064,10 +10064,10 @@
         <v>597</v>
       </c>
       <c r="BC27">
-        <v>0.99563161774290432</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD27">
-        <v>80.087008046754136</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="Z28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA28">
-        <v>0.96199717699083387</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB28">
-        <v>696.71842183471267</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10174,10 +10174,10 @@
         <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.99720193846171157</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP28">
-        <v>51.297794868621132</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10207,13 +10207,13 @@
         <v>598</v>
       </c>
       <c r="BB28" t="s">
-        <v>599</v>
+        <v>341</v>
       </c>
       <c r="BC28">
-        <v>0.99284590877035406</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD28">
-        <v>131.158339210175</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="AA29">
-        <v>0.99548081999408422</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB29">
-        <v>82.851633441789744</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10320,10 +10320,10 @@
         <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99858912444516823</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP29">
-        <v>25.866051838582347</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
+        <v>599</v>
+      </c>
+      <c r="BB29" t="s">
         <v>600</v>
       </c>
-      <c r="BB29" t="s">
-        <v>338</v>
-      </c>
       <c r="BC29">
-        <v>0.98180592470173533</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD29">
-        <v>333.55804713485287</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Z30" t="s">
         <v>351</v>
       </c>
       <c r="AA30">
-        <v>0.99887089404231622</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB30">
-        <v>20.700275890869406</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10466,10 +10466,10 @@
         <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99809873109145164</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP30">
-        <v>34.856596656720825</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10499,13 +10499,13 @@
         <v>601</v>
       </c>
       <c r="BB30" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="BC30">
-        <v>0.93089405249526469</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD30">
-        <v>1266.9423709201483</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Z31" t="s">
         <v>352</v>
       </c>
       <c r="AA31">
-        <v>0.99870336240961599</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB31">
-        <v>23.771689157039763</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10612,10 +10612,10 @@
         <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.99870209313763569</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP31">
-        <v>23.794959143345142</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="BB31" t="s">
-        <v>341</v>
+        <v>604</v>
       </c>
       <c r="BC31">
-        <v>0.98355967005268352</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD31">
-        <v>301.40604903413595</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="Z32" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AA32">
-        <v>0.99732110244768524</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB32">
-        <v>49.113121792437113</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10758,10 +10758,10 @@
         <v>464</v>
       </c>
       <c r="AO32">
-        <v>0.99805167070369571</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP32">
-        <v>35.719370432245356</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="BB32" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="BC32">
-        <v>0.99648308811729225</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD32">
-        <v>64.476717849642213</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Z33" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA33">
-        <v>0.99858140874136669</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB33">
-        <v>26.007506408276679</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10904,10 +10904,10 @@
         <v>466</v>
       </c>
       <c r="AO33">
-        <v>0.99864153733447103</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP33">
-        <v>24.905148868031663</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="BB33" t="s">
-        <v>347</v>
+        <v>608</v>
       </c>
       <c r="BC33">
-        <v>0.96140381292129873</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD33">
-        <v>707.59676310952364</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Z34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA34">
-        <v>0.9980447041381848</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB34">
-        <v>35.847090799945306</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11050,10 +11050,10 @@
         <v>468</v>
       </c>
       <c r="AO34">
-        <v>0.99556268839291095</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP34">
-        <v>81.350712796633118</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="BB34" t="s">
-        <v>607</v>
+        <v>353</v>
       </c>
       <c r="BC34">
-        <v>0.99490784156958001</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD34">
-        <v>93.356237891033686</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA35">
-        <v>0.99348252287636563</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB35">
-        <v>119.48708059996392</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11193,13 +11193,13 @@
         <v>469</v>
       </c>
       <c r="AN35" t="s">
-        <v>341</v>
+        <v>470</v>
       </c>
       <c r="AO35">
-        <v>0.98819688225969682</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP35">
-        <v>216.39049190555826</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="BB35" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="BC35">
-        <v>0.99560371543286275</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD35">
-        <v>80.598550397515965</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Z36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA36">
-        <v>0.9962850624543711</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB36">
-        <v>68.107188336529873</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN36" t="s">
-        <v>471</v>
+        <v>340</v>
       </c>
       <c r="AO36">
-        <v>0.99750210533018213</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP36">
-        <v>45.794735613327241</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="BB36" t="s">
-        <v>611</v>
+        <v>341</v>
       </c>
       <c r="BC36">
-        <v>0.99663140513677484</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD36">
-        <v>61.757572492461378</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="Z37" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA37">
-        <v>0.99727495176003056</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB37">
-        <v>49.959217732772544</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11485,13 +11485,13 @@
         <v>472</v>
       </c>
       <c r="AN37" t="s">
-        <v>338</v>
+        <v>473</v>
       </c>
       <c r="AO37">
-        <v>0.98092770889280956</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP37">
-        <v>349.65867029849198</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="BB37" t="s">
-        <v>347</v>
+        <v>614</v>
       </c>
       <c r="BC37">
-        <v>0.94616153753972931</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD37">
-        <v>987.03847843829612</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z38" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="AA38">
-        <v>0.98747067058472104</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB38">
-        <v>229.70437261344725</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN38" t="s">
-        <v>474</v>
+        <v>345</v>
       </c>
       <c r="AO38">
-        <v>0.99796586165341161</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP38">
-        <v>37.292536354119903</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="BB38" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="BC38">
-        <v>0.99735612831742793</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD38">
-        <v>48.47098084715428</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99744350359843614</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB39">
-        <v>46.86910069533748</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11780,10 +11780,10 @@
         <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.99811838305018963</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP39">
-        <v>34.496310746523356</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11810,16 +11810,16 @@
         <v>537</v>
       </c>
       <c r="BA39" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="BB39" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="BC39">
-        <v>0.99021846023257276</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD39">
-        <v>179.32822906950017</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.9968826832446267</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB40">
-        <v>57.150807181843469</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.99514593439357002</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP40">
-        <v>88.991202784549174</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11956,16 +11956,16 @@
         <v>539</v>
       </c>
       <c r="BA40" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="BB40" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="BC40">
-        <v>0.99302778580016682</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD40">
-        <v>127.82392699694152</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.9969234886911541</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP41">
-        <v>56.402707328841686</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12030,16 +12030,16 @@
         <v>541</v>
       </c>
       <c r="BA41" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="BB41" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="BC41">
-        <v>0.99114508565756532</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD41">
-        <v>162.34009627796874</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="BB42" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="BC42">
-        <v>0.934538160869965</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD42">
-        <v>1200.1337173839754</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="BB43" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="BC43">
-        <v>0.98822137145239475</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD43">
-        <v>215.94152337276336</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="BB44" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="BC44">
-        <v>0.99234935324205875</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD44">
-        <v>140.26185722892211</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="BB45" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="BC45">
-        <v>0.99361371414581767</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD45">
-        <v>117.0819073266757</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="BB46" t="s">
-        <v>629</v>
+        <v>580</v>
       </c>
       <c r="BC46">
-        <v>0.99637036284424008</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD46">
-        <v>66.543347855598327</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12258,16 +12258,16 @@
         <v>553</v>
       </c>
       <c r="BA47" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="BB47" t="s">
-        <v>631</v>
+        <v>340</v>
       </c>
       <c r="BC47">
-        <v>0.99571574761974857</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD47">
-        <v>78.544626971276415</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12299,13 +12299,13 @@
         <v>632</v>
       </c>
       <c r="BB48" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="BC48">
-        <v>0.97902641975794957</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD48">
-        <v>384.51563777092457</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12340,10 +12340,10 @@
         <v>634</v>
       </c>
       <c r="BC49">
-        <v>0.99603752315790417</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD49">
-        <v>72.64540877175618</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12378,10 +12378,10 @@
         <v>636</v>
       </c>
       <c r="BC50">
-        <v>0.88199812838352587</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD50">
-        <v>2163.367646302027</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12416,10 +12416,10 @@
         <v>638</v>
       </c>
       <c r="BC51">
-        <v>0.99764862450771852</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD51">
-        <v>43.108550691828107</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12454,10 +12454,10 @@
         <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.99678722224176453</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD52">
-        <v>58.900925567650859</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12492,10 +12492,10 @@
         <v>642</v>
       </c>
       <c r="BC53">
-        <v>0.98831275563045873</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD53">
-        <v>214.26614677492421</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12527,13 +12527,13 @@
         <v>643</v>
       </c>
       <c r="BB54" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="BC54">
-        <v>0.97803702976044449</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD54">
-        <v>402.65445439185123</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2372DE0C-1A3C-48BC-B024-10ED4C253C08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075503AE-D684-444A-907F-C711261317B0}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>637</v>
+        <v>583</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>578</v>
+        <v>624</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>643</v>
+        <v>589</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>641</v>
+        <v>587</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>624</v>
+        <v>601</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>580</v>
+        <v>626</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>639</v>
+        <v>585</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>582</v>
+        <v>628</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D73EE0-C0AF-42EB-A6EB-F6FF011D141C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4148EB7-0EA3-4B58-92A4-91E675099D2C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CF47F3-DAC0-46A8-AD7C-D77009A653E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EC210D-02CA-4B17-9DDB-D058ECB71DA1}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDED9D92-C566-4284-83AC-8A0BEBB5F442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D99DA4D0-1630-485C-9B71-F7BD49E0C341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,18 +943,162 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_022</t>
   </si>
   <si>
@@ -967,88 +1111,10 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_solelc_spv_JPN_009</t>
@@ -1063,78 +1129,72 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
     <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
   </si>
   <si>
@@ -1144,37 +1204,7 @@
     <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
   </si>
   <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
   </si>
   <si>
     <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
@@ -1183,36 +1213,6 @@
     <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
   </si>
   <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_028</t>
   </si>
   <si>
@@ -1225,6 +1225,66 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_014</t>
   </si>
   <si>
@@ -1249,6 +1309,72 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_026</t>
   </si>
   <si>
@@ -1273,132 +1399,6 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>elc_won_JPN_028</t>
   </si>
   <si>
@@ -1408,6 +1408,63 @@
     <t>elc_won_JPN_029</t>
   </si>
   <si>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_014</t>
   </si>
   <si>
@@ -1432,6 +1489,66 @@
     <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_026</t>
   </si>
   <si>
@@ -1456,121 +1573,82 @@
     <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_005</t>
@@ -1579,22 +1657,28 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_015</t>
@@ -1621,6 +1705,108 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_009</t>
   </si>
   <si>
@@ -1645,196 +1831,76 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_028</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
+    <t>elc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_005</t>
@@ -1843,16 +1909,25 @@
     <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_015</t>
@@ -1879,6 +1954,87 @@
     <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_009</t>
   </si>
   <si>
@@ -1900,166 +2056,10 @@
     <t>elc_wof_JPN_021</t>
   </si>
   <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_028</t>
   </si>
   <si>
     <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAA360C-F5A7-400E-9F13-8CA3B01D6EE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4181B8-90F1-4E95-B468-2138A85C971B}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99887089404231622</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB11">
-        <v>20.700275890869406</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7728,10 +7728,10 @@
         <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.95726256957223688</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD11">
-        <v>783.51955784232393</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99870336240961599</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB12">
-        <v>23.771689157039763</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7835,7 +7835,7 @@
         <v>425</v>
       </c>
       <c r="AN12" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AO12">
         <v>0.98949004263841422</v>
@@ -7871,13 +7871,13 @@
         <v>571</v>
       </c>
       <c r="BB12" t="s">
-        <v>341</v>
+        <v>572</v>
       </c>
       <c r="BC12">
-        <v>0.97218956380622079</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD12">
-        <v>509.85799688595205</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.99732110244768524</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB13">
-        <v>49.113121792437113</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7984,10 +7984,10 @@
         <v>427</v>
       </c>
       <c r="AO13">
-        <v>0.99781438034778358</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP13">
-        <v>40.069693623967019</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="BB13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BC13">
-        <v>0.97591598065988894</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD13">
-        <v>441.54035456870389</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99810840151368141</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB14">
-        <v>34.679305582508199</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8130,10 +8130,10 @@
         <v>429</v>
       </c>
       <c r="AO14">
-        <v>0.99682717865030179</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP14">
-        <v>58.168391411134159</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="BB14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BC14">
-        <v>0.9437657388784082</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD14">
-        <v>1030.9614538958492</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.99727495176003056</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB15">
-        <v>49.959217732772544</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>431</v>
       </c>
       <c r="AO15">
-        <v>0.99770761097472849</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP15">
-        <v>42.027132129978384</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8306,16 +8306,16 @@
         <v>489</v>
       </c>
       <c r="BA15" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="BB15" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.99246863181599732</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD15">
-        <v>138.07508337338285</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.98747067058472104</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB16">
-        <v>229.70437261344725</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8422,10 +8422,10 @@
         <v>433</v>
       </c>
       <c r="AO16">
-        <v>0.99829462257458279</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP16">
-        <v>31.265252799315078</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BB16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="BC16">
-        <v>0.99412039195829205</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD16">
-        <v>107.79281409797902</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.97645815754785015</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB17">
-        <v>431.60044495608111</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8568,10 +8568,10 @@
         <v>435</v>
       </c>
       <c r="AO17">
-        <v>0.99621233314208923</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP17">
-        <v>69.440559061696689</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="BB17" t="s">
-        <v>580</v>
+        <v>340</v>
       </c>
       <c r="BC17">
-        <v>0.97589985979527272</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD17">
-        <v>441.83590375333313</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="Z18" t="s">
         <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99860543314421912</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB18">
-        <v>25.567059022649978</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8711,13 +8711,13 @@
         <v>436</v>
       </c>
       <c r="AN18" t="s">
-        <v>437</v>
+        <v>339</v>
       </c>
       <c r="AO18">
-        <v>0.99763984073088841</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP18">
-        <v>43.269586600378275</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8747,13 +8747,13 @@
         <v>581</v>
       </c>
       <c r="BB18" t="s">
-        <v>582</v>
+        <v>340</v>
       </c>
       <c r="BC18">
-        <v>0.99502210016107762</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD18">
-        <v>91.26149704691008</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Z19" t="s">
         <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99604289943123792</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB19">
-        <v>72.546843760638723</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8854,16 +8854,16 @@
         <v>377</v>
       </c>
       <c r="AM19" t="s">
+        <v>437</v>
+      </c>
+      <c r="AN19" t="s">
         <v>438</v>
       </c>
-      <c r="AN19" t="s">
-        <v>439</v>
-      </c>
       <c r="AO19">
-        <v>0.9878316475733655</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP19">
-        <v>223.0864611549656</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
+        <v>582</v>
+      </c>
+      <c r="BB19" t="s">
         <v>583</v>
       </c>
-      <c r="BB19" t="s">
-        <v>584</v>
-      </c>
       <c r="BC19">
-        <v>0.99764862450771852</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD19">
-        <v>43.108550691828107</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="Z20" t="s">
         <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99586101480039024</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB20">
-        <v>75.881395326178321</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9000,16 +9000,16 @@
         <v>379</v>
       </c>
       <c r="AM20" t="s">
+        <v>439</v>
+      </c>
+      <c r="AN20" t="s">
         <v>440</v>
       </c>
-      <c r="AN20" t="s">
-        <v>441</v>
-      </c>
       <c r="AO20">
-        <v>0.99689519939751359</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP20">
-        <v>56.921344378917169</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="BB20" t="s">
-        <v>586</v>
+        <v>340</v>
       </c>
       <c r="BC20">
-        <v>0.99678722224176453</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD20">
-        <v>58.900925567650859</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="Z21" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.96199717699083387</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB21">
-        <v>696.71842183471267</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9146,16 +9146,16 @@
         <v>381</v>
       </c>
       <c r="AM21" t="s">
+        <v>441</v>
+      </c>
+      <c r="AN21" t="s">
         <v>442</v>
       </c>
-      <c r="AN21" t="s">
-        <v>341</v>
-      </c>
       <c r="AO21">
-        <v>0.96316479569784719</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP21">
-        <v>675.31207887280175</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="BB21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="BC21">
-        <v>0.98831275563045873</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD21">
-        <v>214.26614677492421</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Z22" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AA22">
-        <v>0.99548081999408422</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB22">
-        <v>82.851633441789744</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9298,10 +9298,10 @@
         <v>444</v>
       </c>
       <c r="AO22">
-        <v>0.99796586165341161</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP22">
-        <v>37.292536354119903</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="BB22" t="s">
-        <v>344</v>
+        <v>588</v>
       </c>
       <c r="BC22">
-        <v>0.97803702976044449</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD22">
-        <v>402.65445439185123</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s">
         <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.99794257572004419</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB23">
-        <v>37.719445132522388</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9444,10 +9444,10 @@
         <v>446</v>
       </c>
       <c r="AO23">
-        <v>0.99811838305018963</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP23">
-        <v>34.496310746523356</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
+        <v>589</v>
+      </c>
+      <c r="BB23" t="s">
         <v>590</v>
       </c>
-      <c r="BB23" t="s">
-        <v>359</v>
-      </c>
       <c r="BC23">
-        <v>0.99536692897647694</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD23">
-        <v>84.939635431255269</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AA24">
-        <v>0.99330431978332978</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB24">
-        <v>122.75413730562111</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>448</v>
       </c>
       <c r="AO24">
-        <v>0.99514593439357002</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP24">
-        <v>88.991202784549174</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9626,10 +9626,10 @@
         <v>592</v>
       </c>
       <c r="BC24">
-        <v>0.99563161774290432</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD24">
-        <v>80.087008046754136</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA25">
-        <v>0.97905997046933124</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB25">
-        <v>383.90054139559413</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9736,10 +9736,10 @@
         <v>450</v>
       </c>
       <c r="AO25">
-        <v>0.9969234886911541</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP25">
-        <v>56.402707328841686</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9769,13 +9769,13 @@
         <v>593</v>
       </c>
       <c r="BB25" t="s">
-        <v>594</v>
+        <v>340</v>
       </c>
       <c r="BC25">
-        <v>0.99284590877035406</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD25">
-        <v>131.158339210175</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Z26" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA26">
-        <v>0.99348252287636563</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB26">
-        <v>119.48708059996392</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.99876486181024959</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP26">
-        <v>22.644200145424321</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
+        <v>594</v>
+      </c>
+      <c r="BB26" t="s">
         <v>595</v>
       </c>
-      <c r="BB26" t="s">
-        <v>345</v>
-      </c>
       <c r="BC26">
-        <v>0.98180592470173533</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD26">
-        <v>333.55804713485287</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA27">
-        <v>0.9962850624543711</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB27">
-        <v>68.107188336529873</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99825578453224051</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP27">
-        <v>31.977283575591127</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10064,10 +10064,10 @@
         <v>597</v>
       </c>
       <c r="BC27">
-        <v>0.99114508565756532</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD27">
-        <v>162.34009627796874</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AA28">
-        <v>0.99744350359843614</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB28">
-        <v>46.86910069533748</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10171,13 +10171,13 @@
         <v>455</v>
       </c>
       <c r="AN28" t="s">
-        <v>456</v>
+        <v>341</v>
       </c>
       <c r="AO28">
-        <v>0.99869874972548245</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP28">
-        <v>23.856255032822389</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10207,13 +10207,13 @@
         <v>598</v>
       </c>
       <c r="BB28" t="s">
-        <v>341</v>
+        <v>599</v>
       </c>
       <c r="BC28">
-        <v>0.934538160869965</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD28">
-        <v>1200.1337173839754</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Z29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA29">
-        <v>0.9968826832446267</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB29">
-        <v>57.150807181843469</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10314,16 +10314,16 @@
         <v>397</v>
       </c>
       <c r="AM29" t="s">
+        <v>456</v>
+      </c>
+      <c r="AN29" t="s">
         <v>457</v>
       </c>
-      <c r="AN29" t="s">
-        <v>458</v>
-      </c>
       <c r="AO29">
-        <v>0.99720193846171157</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP29">
-        <v>51.297794868621132</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="BB29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="BC29">
-        <v>0.98822137145239475</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD29">
-        <v>215.94152337276336</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA30">
-        <v>0.99905729110642394</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB30">
-        <v>17.282996382227537</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10460,16 +10460,16 @@
         <v>399</v>
       </c>
       <c r="AM30" t="s">
+        <v>458</v>
+      </c>
+      <c r="AN30" t="s">
         <v>459</v>
       </c>
-      <c r="AN30" t="s">
-        <v>460</v>
-      </c>
       <c r="AO30">
-        <v>0.99858912444516823</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP30">
-        <v>25.866051838582347</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="BB30" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="BC30">
-        <v>0.99234935324205875</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD30">
-        <v>140.26185722892211</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="Z31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA31">
-        <v>0.99419544959877137</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB31">
-        <v>106.41675735585797</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10606,16 +10606,16 @@
         <v>401</v>
       </c>
       <c r="AM31" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN31" t="s">
         <v>461</v>
       </c>
-      <c r="AN31" t="s">
-        <v>462</v>
-      </c>
       <c r="AO31">
-        <v>0.99809873109145164</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP31">
-        <v>34.856596656720825</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="BB31" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="BC31">
-        <v>0.99361371414581767</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD31">
-        <v>117.0819073266757</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="Z32" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="AA32">
-        <v>0.98845903150961834</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB32">
-        <v>211.58442232366301</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN32" t="s">
-        <v>464</v>
+        <v>340</v>
       </c>
       <c r="AO32">
-        <v>0.99870209313763569</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP32">
-        <v>23.794959143345142</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="BB32" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="BC32">
-        <v>0.99637036284424008</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD32">
-        <v>66.543347855598327</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Z33" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="AA33">
-        <v>0.98176582039027138</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB33">
-        <v>334.29329284502461</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AN33" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AO33">
-        <v>0.99805167070369571</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP33">
-        <v>35.719370432245356</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BB33" t="s">
-        <v>608</v>
+        <v>336</v>
       </c>
       <c r="BC33">
-        <v>0.99571574761974857</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD33">
-        <v>78.544626971276415</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="Z34" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="AA34">
-        <v>0.99812715296949239</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB34">
-        <v>34.33552889264039</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN34" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO34">
-        <v>0.99864153733447103</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP34">
-        <v>24.905148868031663</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11083,13 +11083,13 @@
         <v>609</v>
       </c>
       <c r="BB34" t="s">
-        <v>353</v>
+        <v>610</v>
       </c>
       <c r="BC34">
-        <v>0.97902641975794957</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD34">
-        <v>384.51563777092457</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="Z35" t="s">
         <v>355</v>
       </c>
       <c r="AA35">
-        <v>0.99854662761279667</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB35">
-        <v>26.645160432060571</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11190,16 +11190,16 @@
         <v>409</v>
       </c>
       <c r="AM35" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN35" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO35">
-        <v>0.99556268839291095</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP35">
-        <v>81.350712796633118</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="BB35" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="BC35">
-        <v>0.99648308811729225</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD35">
-        <v>64.476717849642213</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="Z36" t="s">
         <v>356</v>
       </c>
       <c r="AA36">
-        <v>0.9983436906516876</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB36">
-        <v>30.365671385728113</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN36" t="s">
-        <v>340</v>
+        <v>470</v>
       </c>
       <c r="AO36">
-        <v>0.98819688225969682</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP36">
-        <v>216.39049190555826</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="BB36" t="s">
         <v>341</v>
       </c>
       <c r="BC36">
-        <v>0.96140381292129873</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD36">
-        <v>707.59676310952364</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="Z37" t="s">
         <v>357</v>
       </c>
       <c r="AA37">
-        <v>0.99886682122259174</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB37">
-        <v>20.774944252484079</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
+        <v>471</v>
+      </c>
+      <c r="AN37" t="s">
         <v>472</v>
       </c>
-      <c r="AN37" t="s">
-        <v>473</v>
-      </c>
       <c r="AO37">
-        <v>0.99750210533018213</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP37">
-        <v>45.794735613327241</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="BB37" t="s">
-        <v>614</v>
+        <v>340</v>
       </c>
       <c r="BC37">
-        <v>0.99490784156958001</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD37">
-        <v>93.356237891033686</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="Z38" t="s">
         <v>358</v>
       </c>
       <c r="AA38">
-        <v>0.99830231855562213</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB38">
-        <v>31.124159813595057</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN38" t="s">
         <v>474</v>
       </c>
-      <c r="AN38" t="s">
-        <v>345</v>
-      </c>
       <c r="AO38">
-        <v>0.98092770889280956</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP38">
-        <v>349.65867029849198</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11670,10 +11670,10 @@
         <v>616</v>
       </c>
       <c r="BC38">
-        <v>0.99560371543286275</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD38">
-        <v>80.598550397515965</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99858140874136669</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB39">
-        <v>26.007506408276679</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11780,10 +11780,10 @@
         <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.99670212772821787</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP39">
-        <v>60.460991649339221</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11816,10 +11816,10 @@
         <v>618</v>
       </c>
       <c r="BC39">
-        <v>0.99663140513677484</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD39">
-        <v>61.757572492461378</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.9980447041381848</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB40">
-        <v>35.847090799945306</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.99870483393763032</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP40">
-        <v>23.744711143443137</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11962,10 +11962,10 @@
         <v>620</v>
       </c>
       <c r="BC40">
-        <v>0.99603752315790417</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD40">
-        <v>72.64540877175618</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99940622505963084</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP41">
-        <v>10.885873906767051</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12036,10 +12036,10 @@
         <v>622</v>
       </c>
       <c r="BC41">
-        <v>0.88199812838352587</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD41">
-        <v>2163.367646302027</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12071,13 +12071,13 @@
         <v>623</v>
       </c>
       <c r="BB42" t="s">
-        <v>341</v>
+        <v>624</v>
       </c>
       <c r="BC42">
-        <v>0.95957195194316591</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD42">
-        <v>741.18088104195795</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="BB43" t="s">
-        <v>625</v>
+        <v>346</v>
       </c>
       <c r="BC43">
-        <v>0.99232897920121688</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD43">
-        <v>140.63538131102445</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12150,10 +12150,10 @@
         <v>627</v>
       </c>
       <c r="BC44">
-        <v>0.9205295464439136</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD44">
-        <v>1456.9583151949184</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12188,10 +12188,10 @@
         <v>629</v>
       </c>
       <c r="BC45">
-        <v>0.98881218539944515</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD45">
-        <v>205.10993434350485</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12223,13 +12223,13 @@
         <v>630</v>
       </c>
       <c r="BB46" t="s">
-        <v>580</v>
+        <v>339</v>
       </c>
       <c r="BC46">
-        <v>0.93089405249526469</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD46">
-        <v>1266.9423709201483</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12261,13 +12261,13 @@
         <v>631</v>
       </c>
       <c r="BB47" t="s">
-        <v>340</v>
+        <v>632</v>
       </c>
       <c r="BC47">
-        <v>0.98355967005268352</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD47">
-        <v>301.40604903413595</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="BB48" t="s">
-        <v>341</v>
+        <v>605</v>
       </c>
       <c r="BC48">
-        <v>0.94616153753972931</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD48">
-        <v>987.03847843829612</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12334,16 +12334,16 @@
         <v>557</v>
       </c>
       <c r="BA49" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="BB49" t="s">
-        <v>634</v>
+        <v>339</v>
       </c>
       <c r="BC49">
-        <v>0.99735612831742793</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD49">
-        <v>48.47098084715428</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12378,10 +12378,10 @@
         <v>636</v>
       </c>
       <c r="BC50">
-        <v>0.99021846023257276</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD50">
-        <v>179.32822906950017</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12416,10 +12416,10 @@
         <v>638</v>
       </c>
       <c r="BC51">
-        <v>0.99302778580016682</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD51">
-        <v>127.82392699694152</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12454,10 +12454,10 @@
         <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.98779966071713954</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD52">
-        <v>223.67288685244134</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12489,13 +12489,13 @@
         <v>641</v>
       </c>
       <c r="BB53" t="s">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BC53">
-        <v>0.99604247516580058</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD53">
-        <v>72.554621960323615</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB54" t="s">
         <v>643</v>
       </c>
-      <c r="BB54" t="s">
-        <v>340</v>
-      </c>
       <c r="BC54">
-        <v>0.98235584693125277</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD54">
-        <v>323.47613959369914</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075503AE-D684-444A-907F-C711261317B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4A72-EB7B-4E42-A693-D1F0879AA6F7}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>632</v>
+        <v>573</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>633</v>
+        <v>574</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>587</v>
+        <v>639</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>635</v>
+        <v>576</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>621</v>
+        <v>571</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>585</v>
+        <v>637</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>637</v>
+        <v>578</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4148EB7-0EA3-4B58-92A4-91E675099D2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE05591-C114-412A-8C01-35A050EF1675}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EC210D-02CA-4B17-9DDB-D058ECB71DA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91E2037-54A3-498C-BB82-F5211F4B4AD1}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D99DA4D0-1630-485C-9B71-F7BD49E0C341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4390C567-61BC-4816-9B6C-A49542411014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,16 +943,88 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_solelc_spv_JPN_008</t>
@@ -967,18 +1039,6 @@
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_002</t>
   </si>
   <si>
@@ -991,6 +1051,72 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_021</t>
   </si>
   <si>
@@ -1003,157 +1129,82 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
     <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
   </si>
   <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
     <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
   </si>
   <si>
     <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
   </si>
   <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
     <t>e_JP306-500_JPN</t>
   </si>
   <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
   </si>
   <si>
     <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
@@ -1162,57 +1213,6 @@
     <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_028</t>
   </si>
   <si>
@@ -1231,6 +1231,90 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_010</t>
   </si>
   <si>
@@ -1273,18 +1357,6 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_014</t>
   </si>
   <si>
@@ -1303,102 +1375,30 @@
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>elc_won_JPN_028</t>
   </si>
   <si>
@@ -1414,6 +1414,87 @@
     <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_010</t>
   </si>
   <si>
@@ -1453,18 +1534,6 @@
     <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
-  </si>
-  <si>
     <t>elc_won_JPN_014</t>
   </si>
   <si>
@@ -1483,96 +1552,27 @@
     <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_004</t>
   </si>
   <si>
     <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_043</t>
   </si>
   <si>
@@ -1585,6 +1585,162 @@
     <t>connecting wind offshore to buses in cluster 35</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_002</t>
   </si>
   <si>
@@ -1609,78 +1765,6 @@
     <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_015</t>
   </si>
   <si>
@@ -1729,46 +1813,10 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_031</t>
@@ -1789,54 +1837,6 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_043</t>
   </si>
   <si>
@@ -1849,6 +1849,138 @@
     <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_002</t>
   </si>
   <si>
@@ -1870,66 +2002,6 @@
     <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_015</t>
   </si>
   <si>
@@ -1945,9 +2017,6 @@
     <t>elc_wof_JPN_038</t>
   </si>
   <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_017</t>
   </si>
   <si>
@@ -1972,40 +2041,10 @@
     <t>elc_wof_JPN_019</t>
   </si>
   <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_031</t>
@@ -2021,45 +2060,6 @@
   </si>
   <si>
     <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4181B8-90F1-4E95-B468-2138A85C971B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B91C3F7-7230-4148-8460-310421BB4119}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99810840151368141</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB11">
-        <v>34.679305582508199</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99858140874136669</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB12">
-        <v>26.007506408276679</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7835,7 +7835,7 @@
         <v>425</v>
       </c>
       <c r="AN12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AO12">
         <v>0.98949004263841422</v>
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.9980447041381848</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB13">
-        <v>35.847090799945306</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -8017,13 +8017,13 @@
         <v>573</v>
       </c>
       <c r="BB13" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="BC13">
-        <v>0.94616153753972931</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD13">
-        <v>987.03847843829612</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99727495176003056</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB14">
-        <v>49.959217732772544</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8130,10 +8130,10 @@
         <v>429</v>
       </c>
       <c r="AO14">
-        <v>0.99870209313763569</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP14">
-        <v>23.794959143345142</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8166,10 +8166,10 @@
         <v>575</v>
       </c>
       <c r="BC14">
-        <v>0.99735612831742793</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD14">
-        <v>48.47098084715428</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.98747067058472104</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB15">
-        <v>229.70437261344725</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>431</v>
       </c>
       <c r="AO15">
-        <v>0.99805167070369571</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP15">
-        <v>35.719370432245356</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8312,10 +8312,10 @@
         <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.99021846023257276</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD15">
-        <v>179.32822906950017</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.96199717699083387</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB16">
-        <v>696.71842183471267</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8422,10 +8422,10 @@
         <v>433</v>
       </c>
       <c r="AO16">
-        <v>0.99864153733447103</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP16">
-        <v>24.905148868031663</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8458,10 +8458,10 @@
         <v>579</v>
       </c>
       <c r="BC16">
-        <v>0.99302778580016682</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD16">
-        <v>127.82392699694152</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99548081999408422</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB17">
-        <v>82.851633441789744</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8568,10 +8568,10 @@
         <v>435</v>
       </c>
       <c r="AO17">
-        <v>0.99556268839291095</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP17">
-        <v>81.350712796633118</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8601,13 +8601,13 @@
         <v>580</v>
       </c>
       <c r="BB17" t="s">
-        <v>340</v>
+        <v>581</v>
       </c>
       <c r="BC17">
-        <v>0.97218956380622079</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD17">
-        <v>509.85799688595205</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Z18" t="s">
         <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99905729110642394</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB18">
-        <v>17.282996382227537</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8711,13 +8711,13 @@
         <v>436</v>
       </c>
       <c r="AN18" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AO18">
-        <v>0.98819688225969682</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP18">
-        <v>216.39049190555826</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="BB18" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="BC18">
-        <v>0.97591598065988894</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD18">
-        <v>441.54035456870389</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="Z19" t="s">
         <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99419544959877137</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB19">
-        <v>106.41675735585797</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8860,10 +8860,10 @@
         <v>438</v>
       </c>
       <c r="AO19">
-        <v>0.99796586165341161</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP19">
-        <v>37.292536354119903</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="BB19" t="s">
-        <v>583</v>
+        <v>350</v>
       </c>
       <c r="BC19">
-        <v>0.9437657388784082</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD19">
-        <v>1030.9614538958492</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z20" t="s">
         <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99348252287636563</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB20">
-        <v>119.48708059996392</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9006,10 +9006,10 @@
         <v>440</v>
       </c>
       <c r="AO20">
-        <v>0.99811838305018963</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP20">
-        <v>34.496310746523356</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9039,13 +9039,13 @@
         <v>584</v>
       </c>
       <c r="BB20" t="s">
-        <v>340</v>
+        <v>585</v>
       </c>
       <c r="BC20">
-        <v>0.95957195194316591</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD20">
-        <v>741.18088104195795</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Z21" t="s">
         <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.9962850624543711</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB21">
-        <v>68.107188336529873</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9152,10 +9152,10 @@
         <v>442</v>
       </c>
       <c r="AO21">
-        <v>0.99514593439357002</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP21">
-        <v>88.991202784549174</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="BB21" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="BC21">
-        <v>0.99232897920121688</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD21">
-        <v>140.63538131102445</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="Z22" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AA22">
-        <v>0.98845903150961834</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB22">
-        <v>211.58442232366301</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9298,10 +9298,10 @@
         <v>444</v>
       </c>
       <c r="AO22">
-        <v>0.9969234886911541</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP22">
-        <v>56.402707328841686</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="BB22" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="BC22">
-        <v>0.9205295464439136</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD22">
-        <v>1456.9583151949184</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Z23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA23">
-        <v>0.98176582039027138</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB23">
-        <v>334.29329284502461</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9444,10 +9444,10 @@
         <v>446</v>
       </c>
       <c r="AO23">
-        <v>0.99781438034778358</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP23">
-        <v>40.069693623967019</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="BB23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="BC23">
-        <v>0.98881218539944515</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD23">
-        <v>205.10993434350485</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Z24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA24">
-        <v>0.99854662761279667</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB24">
-        <v>26.645160432060571</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>448</v>
       </c>
       <c r="AO24">
-        <v>0.99682717865030179</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP24">
-        <v>58.168391411134159</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="BB24" t="s">
-        <v>592</v>
+        <v>350</v>
       </c>
       <c r="BC24">
-        <v>0.95726256957223688</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD24">
-        <v>783.51955784232393</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="Z25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA25">
-        <v>0.9983436906516876</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB25">
-        <v>30.365671385728113</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9736,10 +9736,10 @@
         <v>450</v>
       </c>
       <c r="AO25">
-        <v>0.99770761097472849</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP25">
-        <v>42.027132129978384</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9769,13 +9769,13 @@
         <v>593</v>
       </c>
       <c r="BB25" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="BC25">
-        <v>0.96140381292129873</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD25">
-        <v>707.59676310952364</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA26">
-        <v>0.99886682122259174</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB26">
-        <v>20.774944252484079</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.99829462257458279</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP26">
-        <v>31.265252799315078</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9918,10 +9918,10 @@
         <v>595</v>
       </c>
       <c r="BC26">
-        <v>0.99490784156958001</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD26">
-        <v>93.356237891033686</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="AA27">
-        <v>0.99830231855562213</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB27">
-        <v>31.124159813595057</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99750210533018213</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP27">
-        <v>45.794735613327241</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10064,10 +10064,10 @@
         <v>597</v>
       </c>
       <c r="BC27">
-        <v>0.99560371543286275</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD27">
-        <v>80.598550397515965</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Z28" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="AA28">
-        <v>0.97645815754785015</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB28">
-        <v>431.60044495608111</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10171,13 +10171,13 @@
         <v>455</v>
       </c>
       <c r="AN28" t="s">
-        <v>341</v>
+        <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.98092770889280956</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP28">
-        <v>349.65867029849198</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10210,10 +10210,10 @@
         <v>599</v>
       </c>
       <c r="BC28">
-        <v>0.99663140513677484</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD28">
-        <v>61.757572492461378</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="Z29" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AA29">
-        <v>0.99860543314421912</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB29">
-        <v>25.567059022649978</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10314,16 +10314,16 @@
         <v>397</v>
       </c>
       <c r="AM29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99670212772821787</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP29">
-        <v>60.460991649339221</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10356,10 +10356,10 @@
         <v>601</v>
       </c>
       <c r="BC29">
-        <v>0.99246863181599732</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD29">
-        <v>138.07508337338285</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="Z30" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="AA30">
-        <v>0.99604289943123792</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB30">
-        <v>72.546843760638723</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10460,16 +10460,16 @@
         <v>399</v>
       </c>
       <c r="AM30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99870483393763032</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP30">
-        <v>23.744711143443137</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10499,13 +10499,13 @@
         <v>602</v>
       </c>
       <c r="BB30" t="s">
-        <v>603</v>
+        <v>356</v>
       </c>
       <c r="BC30">
-        <v>0.99412039195829205</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD30">
-        <v>107.79281409797902</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="Z31" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA31">
-        <v>0.99586101480039024</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB31">
-        <v>75.881395326178321</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10606,16 +10606,16 @@
         <v>401</v>
       </c>
       <c r="AM31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN31" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.99940622505963084</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP31">
-        <v>10.885873906767051</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
+        <v>603</v>
+      </c>
+      <c r="BB31" t="s">
         <v>604</v>
       </c>
-      <c r="BB31" t="s">
-        <v>605</v>
-      </c>
       <c r="BC31">
-        <v>0.97589985979527272</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD31">
-        <v>441.83590375333313</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA32">
-        <v>0.99794257572004419</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB32">
-        <v>37.719445132522388</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN32" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO32">
-        <v>0.96316479569784719</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP32">
-        <v>675.31207887280175</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="BB32" t="s">
-        <v>607</v>
+        <v>350</v>
       </c>
       <c r="BC32">
-        <v>0.99502210016107762</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD32">
-        <v>91.26149704691008</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="Z33" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AA33">
-        <v>0.99330431978332978</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB33">
-        <v>122.75413730562111</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO33">
-        <v>0.99876486181024959</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP33">
-        <v>22.644200145424321</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="BB33" t="s">
-        <v>336</v>
+        <v>607</v>
       </c>
       <c r="BC33">
-        <v>0.99536692897647694</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD33">
-        <v>84.939635431255269</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="AA34">
-        <v>0.97905997046933124</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB34">
-        <v>383.90054139559413</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN34" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO34">
-        <v>0.99869874972548245</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP34">
-        <v>23.856255032822389</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
+        <v>608</v>
+      </c>
+      <c r="BB34" t="s">
         <v>609</v>
       </c>
-      <c r="BB34" t="s">
-        <v>610</v>
-      </c>
       <c r="BC34">
-        <v>0.99563161774290432</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD34">
-        <v>80.087008046754136</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Z35" t="s">
         <v>355</v>
       </c>
       <c r="AA35">
-        <v>0.99887089404231622</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB35">
-        <v>20.700275890869406</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11190,16 +11190,16 @@
         <v>409</v>
       </c>
       <c r="AM35" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN35" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO35">
-        <v>0.99720193846171157</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP35">
-        <v>51.297794868621132</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
+        <v>610</v>
+      </c>
+      <c r="BB35" t="s">
         <v>611</v>
       </c>
-      <c r="BB35" t="s">
-        <v>612</v>
-      </c>
       <c r="BC35">
-        <v>0.99284590877035406</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD35">
-        <v>131.158339210175</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z36" t="s">
         <v>356</v>
       </c>
       <c r="AA36">
-        <v>0.99870336240961599</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB36">
-        <v>23.771689157039763</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN36" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO36">
-        <v>0.99858912444516823</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP36">
-        <v>25.866051838582347</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
+        <v>612</v>
+      </c>
+      <c r="BB36" t="s">
         <v>613</v>
       </c>
-      <c r="BB36" t="s">
-        <v>341</v>
-      </c>
       <c r="BC36">
-        <v>0.98180592470173533</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD36">
-        <v>333.55804713485287</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="Z37" t="s">
         <v>357</v>
       </c>
       <c r="AA37">
-        <v>0.99732110244768524</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB37">
-        <v>49.113121792437113</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN37" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO37">
-        <v>0.99809873109145164</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP37">
-        <v>34.856596656720825</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11521,13 +11521,13 @@
         <v>614</v>
       </c>
       <c r="BB37" t="s">
-        <v>340</v>
+        <v>615</v>
       </c>
       <c r="BC37">
-        <v>0.934538160869965</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD37">
-        <v>1200.1337173839754</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Z38" t="s">
         <v>358</v>
       </c>
       <c r="AA38">
-        <v>0.99812715296949239</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB38">
-        <v>34.33552889264039</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO38">
-        <v>0.99621233314208923</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP38">
-        <v>69.440559061696689</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="BB38" t="s">
-        <v>616</v>
+        <v>337</v>
       </c>
       <c r="BC38">
-        <v>0.98822137145239475</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD38">
-        <v>215.94152337276336</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99744350359843614</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB39">
-        <v>46.86910069533748</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11774,16 +11774,16 @@
         <v>417</v>
       </c>
       <c r="AM39" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN39" t="s">
-        <v>476</v>
+        <v>336</v>
       </c>
       <c r="AO39">
-        <v>0.99763984073088841</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP39">
-        <v>43.269586600378275</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11813,13 +11813,13 @@
         <v>617</v>
       </c>
       <c r="BB39" t="s">
-        <v>618</v>
+        <v>350</v>
       </c>
       <c r="BC39">
-        <v>0.99234935324205875</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD39">
-        <v>140.26185722892211</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.9968826832446267</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB40">
-        <v>57.150807181843469</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.9878316475733655</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP40">
-        <v>223.0864611549656</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11956,16 +11956,16 @@
         <v>539</v>
       </c>
       <c r="BA40" t="s">
+        <v>618</v>
+      </c>
+      <c r="BB40" t="s">
         <v>619</v>
       </c>
-      <c r="BB40" t="s">
-        <v>620</v>
-      </c>
       <c r="BC40">
-        <v>0.99361371414581767</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD40">
-        <v>117.0819073266757</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99689519939751359</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP41">
-        <v>56.921344378917169</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12030,16 +12030,16 @@
         <v>541</v>
       </c>
       <c r="BA41" t="s">
+        <v>620</v>
+      </c>
+      <c r="BB41" t="s">
         <v>621</v>
       </c>
-      <c r="BB41" t="s">
-        <v>622</v>
-      </c>
       <c r="BC41">
-        <v>0.99637036284424008</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD41">
-        <v>66.543347855598327</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
+        <v>622</v>
+      </c>
+      <c r="BB42" t="s">
         <v>623</v>
       </c>
-      <c r="BB42" t="s">
-        <v>624</v>
-      </c>
       <c r="BC42">
-        <v>0.99571574761974857</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD42">
-        <v>78.544626971276415</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
+        <v>624</v>
+      </c>
+      <c r="BB43" t="s">
         <v>625</v>
       </c>
-      <c r="BB43" t="s">
-        <v>346</v>
-      </c>
       <c r="BC43">
-        <v>0.97902641975794957</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD43">
-        <v>384.51563777092457</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12150,10 +12150,10 @@
         <v>627</v>
       </c>
       <c r="BC44">
-        <v>0.98779966071713954</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD44">
-        <v>223.67288685244134</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12185,13 +12185,13 @@
         <v>628</v>
       </c>
       <c r="BB45" t="s">
-        <v>629</v>
+        <v>581</v>
       </c>
       <c r="BC45">
-        <v>0.99604247516580058</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD45">
-        <v>72.554621960323615</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
+        <v>629</v>
+      </c>
+      <c r="BB46" t="s">
         <v>630</v>
       </c>
-      <c r="BB46" t="s">
-        <v>339</v>
-      </c>
       <c r="BC46">
-        <v>0.98235584693125277</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD46">
-        <v>323.47613959369914</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12261,13 +12261,13 @@
         <v>631</v>
       </c>
       <c r="BB47" t="s">
-        <v>632</v>
+        <v>348</v>
       </c>
       <c r="BC47">
-        <v>0.99648308811729225</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD47">
-        <v>64.476717849642213</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
+        <v>632</v>
+      </c>
+      <c r="BB48" t="s">
         <v>633</v>
       </c>
-      <c r="BB48" t="s">
-        <v>605</v>
-      </c>
       <c r="BC48">
-        <v>0.93089405249526469</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD48">
-        <v>1266.9423709201483</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12337,13 +12337,13 @@
         <v>634</v>
       </c>
       <c r="BB49" t="s">
-        <v>339</v>
+        <v>635</v>
       </c>
       <c r="BC49">
-        <v>0.98355967005268352</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD49">
-        <v>301.40604903413595</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12372,16 +12372,16 @@
         <v>559</v>
       </c>
       <c r="BA50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BB50" t="s">
-        <v>636</v>
+        <v>336</v>
       </c>
       <c r="BC50">
-        <v>0.99764862450771852</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD50">
-        <v>43.108550691828107</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12416,10 +12416,10 @@
         <v>638</v>
       </c>
       <c r="BC51">
-        <v>0.99678722224176453</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD51">
-        <v>58.900925567650859</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12454,10 +12454,10 @@
         <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.98831275563045873</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD52">
-        <v>214.26614677492421</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12489,13 +12489,13 @@
         <v>641</v>
       </c>
       <c r="BB53" t="s">
-        <v>353</v>
+        <v>642</v>
       </c>
       <c r="BC53">
-        <v>0.97803702976044449</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD53">
-        <v>402.65445439185123</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB54" t="s">
-        <v>643</v>
+        <v>343</v>
       </c>
       <c r="BC54">
-        <v>0.99114508565756532</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD54">
-        <v>162.34009627796874</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4A72-EB7B-4E42-A693-D1F0879AA6F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF5C4FF-68C4-4F3E-ABDB-F74BE76E9108}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>574</v>
+        <v>618</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>639</v>
+        <v>600</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>634</v>
+        <v>582</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>642</v>
+        <v>603</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>633</v>
+        <v>580</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>637</v>
+        <v>598</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>578</v>
+        <v>622</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE05591-C114-412A-8C01-35A050EF1675}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AFE4EF-27D5-4CAD-BB7B-F70003D60D7E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91E2037-54A3-498C-BB82-F5211F4B4AD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F121326D-26ED-4215-9C31-14CBB606F270}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4390C567-61BC-4816-9B6C-A49542411014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96F48735-6C78-48A6-8F54-075F63EBAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,274 +943,448 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_026</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 26</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
     <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
   </si>
   <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
     <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
   </si>
   <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+    <t>distr_wonelc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_028</t>
@@ -1225,178 +1399,169 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
   </si>
   <si>
     <t>elc_won_JPN_028</t>
@@ -1408,169 +1573,142 @@
     <t>elc_won_JPN_029</t>
   </si>
   <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_043</t>
@@ -1621,6 +1759,48 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_007</t>
   </si>
   <si>
@@ -1645,196 +1825,130 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_005</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_043</t>
@@ -1879,6 +1993,42 @@
     <t>elc_wof_JPN_023</t>
   </si>
   <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_007</t>
   </si>
   <si>
@@ -1900,166 +2050,16 @@
     <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_005</t>
   </si>
   <si>
     <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B91C3F7-7230-4148-8460-310421BB4119}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55638547-CBC3-4AD8-BD33-828E688D227A}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99812715296949239</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB11">
-        <v>34.33552889264039</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7692,10 +7692,10 @@
         <v>424</v>
       </c>
       <c r="AO11">
-        <v>0.99192535126433146</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP11">
-        <v>148.0352268205892</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7725,13 +7725,13 @@
         <v>569</v>
       </c>
       <c r="BB11" t="s">
-        <v>570</v>
+        <v>337</v>
       </c>
       <c r="BC11">
-        <v>0.99603752315790417</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD11">
-        <v>72.64540877175618</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.98845903150961834</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB12">
-        <v>211.58442232366301</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7835,13 +7835,13 @@
         <v>425</v>
       </c>
       <c r="AN12" t="s">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="AO12">
-        <v>0.98949004263841422</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP12">
-        <v>192.68255162907312</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7868,16 +7868,16 @@
         <v>483</v>
       </c>
       <c r="BA12" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BB12" t="s">
-        <v>572</v>
+        <v>337</v>
       </c>
       <c r="BC12">
-        <v>0.88199812838352587</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD12">
-        <v>2163.367646302027</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.98176582039027138</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB13">
-        <v>334.29329284502461</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7978,16 +7978,16 @@
         <v>365</v>
       </c>
       <c r="AM13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.99825578453224051</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP13">
-        <v>31.977283575591127</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="BB13" t="s">
-        <v>350</v>
+        <v>572</v>
       </c>
       <c r="BC13">
-        <v>0.95957195194316591</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD13">
-        <v>741.18088104195795</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99887089404231622</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB14">
-        <v>20.700275890869406</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8124,16 +8124,16 @@
         <v>367</v>
       </c>
       <c r="AM14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.99869874972548245</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP14">
-        <v>23.856255032822389</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BB14" t="s">
-        <v>575</v>
+        <v>335</v>
       </c>
       <c r="BC14">
-        <v>0.99232897920121688</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD14">
-        <v>140.63538131102445</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.99870336240961599</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB15">
-        <v>23.771689157039763</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8270,16 +8270,16 @@
         <v>369</v>
       </c>
       <c r="AM15" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99720193846171157</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP15">
-        <v>51.297794868621132</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8306,16 +8306,16 @@
         <v>489</v>
       </c>
       <c r="BA15" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="BB15" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="BC15">
-        <v>0.9205295464439136</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD15">
-        <v>1456.9583151949184</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99732110244768524</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB16">
-        <v>49.113121792437113</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8416,16 +8416,16 @@
         <v>371</v>
       </c>
       <c r="AM16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO16">
-        <v>0.99858912444516823</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP16">
-        <v>25.866051838582347</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="BB16" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="BC16">
-        <v>0.98881218539944515</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD16">
-        <v>205.10993434350485</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Z17" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AA17">
-        <v>0.99810840151368141</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB17">
-        <v>34.679305582508199</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8562,16 +8562,16 @@
         <v>373</v>
       </c>
       <c r="AM17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO17">
-        <v>0.99809873109145164</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP17">
-        <v>34.856596656720825</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="BB17" t="s">
-        <v>581</v>
+        <v>338</v>
       </c>
       <c r="BC17">
-        <v>0.93089405249526469</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD17">
-        <v>1266.9423709201483</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Z18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.99727495176003056</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB18">
-        <v>49.959217732772544</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8708,16 +8708,16 @@
         <v>375</v>
       </c>
       <c r="AM18" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN18" t="s">
-        <v>350</v>
+        <v>438</v>
       </c>
       <c r="AO18">
-        <v>0.96316479569784719</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP18">
-        <v>675.31207887280175</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="BB18" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="BC18">
-        <v>0.98355967005268352</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD18">
-        <v>301.40604903413595</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Z19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.98747067058472104</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB19">
-        <v>229.70437261344725</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8854,16 +8854,16 @@
         <v>377</v>
       </c>
       <c r="AM19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO19">
-        <v>0.99514593439357002</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP19">
-        <v>88.991202784549174</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="BB19" t="s">
-        <v>350</v>
+        <v>581</v>
       </c>
       <c r="BC19">
-        <v>0.96140381292129873</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD19">
-        <v>707.59676310952364</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="Z20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99854662761279667</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB20">
-        <v>26.645160432060571</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9000,16 +9000,16 @@
         <v>379</v>
       </c>
       <c r="AM20" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN20" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO20">
-        <v>0.9969234886911541</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP20">
-        <v>56.402707328841686</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BB20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="BC20">
-        <v>0.99490784156958001</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD20">
-        <v>93.356237891033686</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="Z21" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AA21">
-        <v>0.9983436906516876</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB21">
-        <v>30.365671385728113</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9146,16 +9146,16 @@
         <v>381</v>
       </c>
       <c r="AM21" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN21" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO21">
-        <v>0.99621233314208923</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP21">
-        <v>69.440559061696689</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="BB21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="BC21">
-        <v>0.99560371543286275</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD21">
-        <v>80.598550397515965</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Z22" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AA22">
-        <v>0.99886682122259174</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB22">
-        <v>20.774944252484079</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9292,16 +9292,16 @@
         <v>383</v>
       </c>
       <c r="AM22" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN22" t="s">
-        <v>444</v>
+        <v>340</v>
       </c>
       <c r="AO22">
-        <v>0.99670212772821787</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP22">
-        <v>60.460991649339221</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="BB22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="BC22">
-        <v>0.99663140513677484</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD22">
-        <v>61.757572492461378</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA23">
-        <v>0.99830231855562213</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB23">
-        <v>31.124159813595057</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9438,16 +9438,16 @@
         <v>385</v>
       </c>
       <c r="AM23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN23" t="s">
-        <v>446</v>
+        <v>337</v>
       </c>
       <c r="AO23">
-        <v>0.99870483393763032</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP23">
-        <v>23.744711143443137</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="BB23" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="BC23">
-        <v>0.95726256957223688</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD23">
-        <v>783.51955784232393</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="Z24" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AA24">
-        <v>0.99858140874136669</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB24">
-        <v>26.007506408276679</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>448</v>
       </c>
       <c r="AO24">
-        <v>0.99940622505963084</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP24">
-        <v>10.885873906767051</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="BB24" t="s">
         <v>350</v>
       </c>
       <c r="BC24">
-        <v>0.97218956380622079</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD24">
-        <v>509.85799688595205</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Z25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA25">
-        <v>0.9980447041381848</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB25">
-        <v>35.847090799945306</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9736,10 +9736,10 @@
         <v>450</v>
       </c>
       <c r="AO25">
-        <v>0.99763984073088841</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP25">
-        <v>43.269586600378275</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9766,16 +9766,16 @@
         <v>509</v>
       </c>
       <c r="BA25" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BB25" t="s">
-        <v>350</v>
+        <v>592</v>
       </c>
       <c r="BC25">
-        <v>0.97591598065988894</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD25">
-        <v>441.54035456870389</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AA26">
-        <v>0.96199717699083387</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB26">
-        <v>696.71842183471267</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.9878316475733655</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP26">
-        <v>223.0864611549656</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
+        <v>593</v>
+      </c>
+      <c r="BB26" t="s">
         <v>594</v>
       </c>
-      <c r="BB26" t="s">
-        <v>595</v>
-      </c>
       <c r="BC26">
-        <v>0.9437657388784082</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD26">
-        <v>1030.9614538958492</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="AA27">
-        <v>0.99548081999408422</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB27">
-        <v>82.851633441789744</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99689519939751359</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP27">
-        <v>56.921344378917169</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10058,16 +10058,16 @@
         <v>513</v>
       </c>
       <c r="BA27" t="s">
+        <v>595</v>
+      </c>
+      <c r="BB27" t="s">
         <v>596</v>
       </c>
-      <c r="BB27" t="s">
-        <v>597</v>
-      </c>
       <c r="BC27">
-        <v>0.99764862450771852</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD27">
-        <v>43.108550691828107</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AA28">
-        <v>0.99794257572004419</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB28">
-        <v>37.719445132522388</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10174,10 +10174,10 @@
         <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.99870209313763569</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP28">
-        <v>23.794959143345142</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
+        <v>597</v>
+      </c>
+      <c r="BB28" t="s">
         <v>598</v>
       </c>
-      <c r="BB28" t="s">
-        <v>599</v>
-      </c>
       <c r="BC28">
-        <v>0.99678722224176453</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD28">
-        <v>58.900925567650859</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AA29">
-        <v>0.99330431978332978</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB29">
-        <v>122.75413730562111</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10320,10 +10320,10 @@
         <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99805167070369571</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP29">
-        <v>35.719370432245356</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="BB29" t="s">
-        <v>601</v>
+        <v>346</v>
       </c>
       <c r="BC29">
-        <v>0.98831275563045873</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD29">
-        <v>214.26614677492421</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Z30" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="AA30">
-        <v>0.97905997046933124</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB30">
-        <v>383.90054139559413</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10466,10 +10466,10 @@
         <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99864153733447103</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP30">
-        <v>24.905148868031663</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="BB30" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="BC30">
-        <v>0.97803702976044449</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD30">
-        <v>402.65445439185123</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Z31" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA31">
-        <v>0.99744350359843614</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB31">
-        <v>46.86910069533748</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10612,10 +10612,10 @@
         <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.99556268839291095</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP31">
-        <v>81.350712796633118</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="BB31" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="BC31">
-        <v>0.99114508565756532</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD31">
-        <v>162.34009627796874</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Z32" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA32">
-        <v>0.9968826832446267</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB32">
-        <v>57.150807181843469</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10755,13 +10755,13 @@
         <v>463</v>
       </c>
       <c r="AN32" t="s">
-        <v>343</v>
+        <v>464</v>
       </c>
       <c r="AO32">
-        <v>0.98819688225969682</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP32">
-        <v>216.39049190555826</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BB32" t="s">
-        <v>350</v>
+        <v>604</v>
       </c>
       <c r="BC32">
-        <v>0.934538160869965</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD32">
-        <v>1200.1337173839754</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="Z33" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AA33">
-        <v>0.97645815754785015</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB33">
-        <v>431.60044495608111</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO33">
-        <v>0.99796586165341161</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP33">
-        <v>37.292536354119903</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
+        <v>605</v>
+      </c>
+      <c r="BB33" t="s">
         <v>606</v>
       </c>
-      <c r="BB33" t="s">
-        <v>607</v>
-      </c>
       <c r="BC33">
-        <v>0.98822137145239475</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD33">
-        <v>215.94152337276336</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Z34" t="s">
         <v>354</v>
       </c>
       <c r="AA34">
-        <v>0.99860543314421912</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB34">
-        <v>25.567059022649978</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN34" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO34">
-        <v>0.99811838305018963</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP34">
-        <v>34.496310746523356</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
+        <v>607</v>
+      </c>
+      <c r="BB34" t="s">
         <v>608</v>
       </c>
-      <c r="BB34" t="s">
-        <v>609</v>
-      </c>
       <c r="BC34">
-        <v>0.99234935324205875</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD34">
-        <v>140.26185722892211</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="Z35" t="s">
         <v>355</v>
       </c>
       <c r="AA35">
-        <v>0.99604289943123792</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB35">
-        <v>72.546843760638723</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11190,16 +11190,16 @@
         <v>409</v>
       </c>
       <c r="AM35" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN35" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO35">
-        <v>0.99781438034778358</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP35">
-        <v>40.069693623967019</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
+        <v>609</v>
+      </c>
+      <c r="BB35" t="s">
         <v>610</v>
       </c>
-      <c r="BB35" t="s">
-        <v>611</v>
-      </c>
       <c r="BC35">
-        <v>0.99361371414581767</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD35">
-        <v>117.0819073266757</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="Z36" t="s">
         <v>356</v>
       </c>
       <c r="AA36">
-        <v>0.99586101480039024</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB36">
-        <v>75.881395326178321</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN36" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO36">
-        <v>0.99682717865030179</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP36">
-        <v>58.168391411134159</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="BB36" t="s">
-        <v>613</v>
+        <v>337</v>
       </c>
       <c r="BC36">
-        <v>0.99637036284424008</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD36">
-        <v>66.543347855598327</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Z37" t="s">
         <v>357</v>
       </c>
       <c r="AA37">
-        <v>0.99348252287636563</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB37">
-        <v>119.48708059996392</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN37" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO37">
-        <v>0.99770761097472849</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP37">
-        <v>42.027132129978384</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="BB37" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="BC37">
-        <v>0.99571574761974857</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD37">
-        <v>78.544626971276415</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="Z38" t="s">
         <v>358</v>
       </c>
       <c r="AA38">
-        <v>0.9962850624543711</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB38">
-        <v>68.107188336529873</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,10 +11628,10 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO38">
         <v>0.99750210533018213</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="BB38" t="s">
-        <v>337</v>
+        <v>615</v>
       </c>
       <c r="BC38">
-        <v>0.97902641975794957</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD38">
-        <v>384.51563777092457</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99905729110642394</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB39">
-        <v>17.282996382227537</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11774,10 +11774,10 @@
         <v>417</v>
       </c>
       <c r="AM39" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN39" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO39">
         <v>0.98092770889280956</v>
@@ -11810,16 +11810,16 @@
         <v>537</v>
       </c>
       <c r="BA39" t="s">
+        <v>616</v>
+      </c>
+      <c r="BB39" t="s">
         <v>617</v>
       </c>
-      <c r="BB39" t="s">
-        <v>350</v>
-      </c>
       <c r="BC39">
-        <v>0.94616153753972931</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD39">
-        <v>987.03847843829612</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.99419544959877137</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB40">
-        <v>106.41675735585797</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11920,16 +11920,16 @@
         <v>419</v>
       </c>
       <c r="AM40" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO40">
-        <v>0.99876486181024959</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP40">
-        <v>22.644200145424321</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11962,10 +11962,10 @@
         <v>619</v>
       </c>
       <c r="BC40">
-        <v>0.99735612831742793</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD40">
-        <v>48.47098084715428</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -11994,16 +11994,16 @@
         <v>421</v>
       </c>
       <c r="AM41" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN41" t="s">
-        <v>480</v>
+        <v>338</v>
       </c>
       <c r="AO41">
-        <v>0.99829462257458279</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP41">
-        <v>31.265252799315078</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12033,13 +12033,13 @@
         <v>620</v>
       </c>
       <c r="BB41" t="s">
-        <v>621</v>
+        <v>340</v>
       </c>
       <c r="BC41">
-        <v>0.99021846023257276</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD41">
-        <v>179.32822906950017</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
+        <v>621</v>
+      </c>
+      <c r="BB42" t="s">
         <v>622</v>
       </c>
-      <c r="BB42" t="s">
-        <v>623</v>
-      </c>
       <c r="BC42">
-        <v>0.99302778580016682</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD42">
-        <v>127.82392699694152</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
+        <v>623</v>
+      </c>
+      <c r="BB43" t="s">
         <v>624</v>
       </c>
-      <c r="BB43" t="s">
-        <v>625</v>
-      </c>
       <c r="BC43">
-        <v>0.99246863181599732</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD43">
-        <v>138.07508337338285</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="BB44" t="s">
-        <v>627</v>
+        <v>340</v>
       </c>
       <c r="BC44">
-        <v>0.99412039195829205</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD44">
-        <v>107.79281409797902</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="BB45" t="s">
-        <v>581</v>
+        <v>627</v>
       </c>
       <c r="BC45">
-        <v>0.97589985979527272</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD45">
-        <v>441.83590375333313</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
+        <v>628</v>
+      </c>
+      <c r="BB46" t="s">
         <v>629</v>
       </c>
-      <c r="BB46" t="s">
-        <v>630</v>
-      </c>
       <c r="BC46">
-        <v>0.99502210016107762</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD46">
-        <v>91.26149704691008</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12258,16 +12258,16 @@
         <v>553</v>
       </c>
       <c r="BA47" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="BB47" t="s">
-        <v>348</v>
+        <v>619</v>
       </c>
       <c r="BC47">
-        <v>0.99536692897647694</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD47">
-        <v>84.939635431255269</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
+        <v>631</v>
+      </c>
+      <c r="BB48" t="s">
         <v>632</v>
       </c>
-      <c r="BB48" t="s">
-        <v>633</v>
-      </c>
       <c r="BC48">
-        <v>0.99563161774290432</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD48">
-        <v>80.087008046754136</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12334,16 +12334,16 @@
         <v>557</v>
       </c>
       <c r="BA49" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="BB49" t="s">
-        <v>635</v>
+        <v>337</v>
       </c>
       <c r="BC49">
-        <v>0.99284590877035406</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD49">
-        <v>131.158339210175</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12372,16 +12372,16 @@
         <v>559</v>
       </c>
       <c r="BA50" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="BB50" t="s">
-        <v>336</v>
+        <v>635</v>
       </c>
       <c r="BC50">
-        <v>0.98180592470173533</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD50">
-        <v>333.55804713485287</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12410,16 +12410,16 @@
         <v>561</v>
       </c>
       <c r="BA51" t="s">
+        <v>636</v>
+      </c>
+      <c r="BB51" t="s">
         <v>637</v>
       </c>
-      <c r="BB51" t="s">
-        <v>638</v>
-      </c>
       <c r="BC51">
-        <v>0.99648308811729225</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD51">
-        <v>64.476717849642213</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12448,16 +12448,16 @@
         <v>563</v>
       </c>
       <c r="BA52" t="s">
+        <v>638</v>
+      </c>
+      <c r="BB52" t="s">
         <v>639</v>
       </c>
-      <c r="BB52" t="s">
-        <v>640</v>
-      </c>
       <c r="BC52">
-        <v>0.98779966071713954</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD52">
-        <v>223.67288685244134</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12486,16 +12486,16 @@
         <v>565</v>
       </c>
       <c r="BA53" t="s">
+        <v>640</v>
+      </c>
+      <c r="BB53" t="s">
         <v>641</v>
       </c>
-      <c r="BB53" t="s">
-        <v>642</v>
-      </c>
       <c r="BC53">
-        <v>0.99604247516580058</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD53">
-        <v>72.554621960323615</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB54" t="s">
         <v>643</v>
       </c>
-      <c r="BB54" t="s">
-        <v>343</v>
-      </c>
       <c r="BC54">
-        <v>0.98235584693125277</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD54">
-        <v>323.47613959369914</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF5C4FF-68C4-4F3E-ABDB-F74BE76E9108}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4C6B4C-217F-4BDF-94AC-FF161F81A600}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>590</v>
+        <v>642</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>573</v>
+        <v>611</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>583</v>
+        <v>633</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>586</v>
+        <v>636</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>631</v>
+        <v>573</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>610</v>
+        <v>584</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>468</v>
+        <v>427</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>588</v>
+        <v>638</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>636</v>
+        <v>578</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>582</v>
+        <v>620</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>632</v>
+        <v>574</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>584</v>
+        <v>634</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>571</v>
+        <v>609</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>576</v>
+        <v>614</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>578</v>
+        <v>616</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>634</v>
+        <v>576</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>569</v>
+        <v>607</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>637</v>
+        <v>591</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AFE4EF-27D5-4CAD-BB7B-F70003D60D7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8B8DC1-282D-4D89-9065-60847233BC46}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F121326D-26ED-4215-9C31-14CBB606F270}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417CB113-8697-41C5-A046-0542F9C37D44}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96F48735-6C78-48A6-8F54-075F63EBAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C4DD2F7-6154-482B-B656-2C9EFF458277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,34 +943,160 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_030</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_JPN_003</t>
@@ -991,84 +1117,6 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_004</t>
   </si>
   <si>
@@ -1081,138 +1129,90 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
     <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
   </si>
   <si>
     <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
   </si>
   <si>
     <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
   </si>
   <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
     <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
   </si>
   <si>
     <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
   </si>
   <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_006</t>
   </si>
   <si>
@@ -1225,6 +1225,24 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_014</t>
   </si>
   <si>
@@ -1243,10 +1261,76 @@
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_004</t>
@@ -1285,34 +1369,16 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_018</t>
@@ -1333,72 +1399,6 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
     <t>elc_won_JPN_006</t>
   </si>
   <si>
@@ -1411,6 +1411,24 @@
     <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_014</t>
   </si>
   <si>
@@ -1429,10 +1447,70 @@
     <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
   </si>
   <si>
     <t>elc_won_JPN_004</t>
@@ -1468,31 +1546,13 @@
     <t>elc_won_JPN_030</t>
   </si>
   <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
   </si>
   <si>
     <t>elc_won_JPN_018</t>
@@ -1513,64 +1573,70 @@
     <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
+    <t>distr_wofelc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_003</t>
@@ -1591,6 +1657,54 @@
     <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_010</t>
   </si>
   <si>
@@ -1615,6 +1729,12 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_001</t>
   </si>
   <si>
@@ -1657,34 +1777,22 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_002</t>
@@ -1711,54 +1819,6 @@
     <t>connecting wind offshore to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_031</t>
   </si>
   <si>
@@ -1777,64 +1837,64 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_003</t>
@@ -1849,6 +1909,51 @@
     <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_010</t>
   </si>
   <si>
@@ -1867,6 +1972,12 @@
     <t>elc_wof_JPN_019</t>
   </si>
   <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_001</t>
   </si>
   <si>
@@ -1903,31 +2014,16 @@
     <t>elc_wof_JPN_020</t>
   </si>
   <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_002</t>
@@ -1951,48 +2047,6 @@
     <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_031</t>
   </si>
   <si>
@@ -2006,60 +2060,6 @@
   </si>
   <si>
     <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55638547-CBC3-4AD8-BD33-828E688D227A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD905D1F-63E3-4FBE-A908-49D0D38720F9}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99858140874136669</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB11">
-        <v>26.007506408276679</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7725,13 +7725,13 @@
         <v>569</v>
       </c>
       <c r="BB11" t="s">
-        <v>337</v>
+        <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.97218956380622079</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD11">
-        <v>509.85799688595205</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.9980447041381848</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB12">
-        <v>35.847090799945306</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7868,16 +7868,16 @@
         <v>483</v>
       </c>
       <c r="BA12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="BB12" t="s">
-        <v>337</v>
+        <v>572</v>
       </c>
       <c r="BC12">
-        <v>0.97591598065988894</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD12">
-        <v>441.54035456870389</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7984,10 +7984,10 @@
         <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.99781438034778358</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP13">
-        <v>40.069693623967019</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="BB13" t="s">
-        <v>572</v>
+        <v>337</v>
       </c>
       <c r="BC13">
-        <v>0.9437657388784082</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD13">
-        <v>1030.9614538958492</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8130,10 +8130,10 @@
         <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.99682717865030179</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP14">
-        <v>58.168391411134159</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="BB14" t="s">
-        <v>335</v>
+        <v>575</v>
       </c>
       <c r="BC14">
-        <v>0.99536692897647694</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD14">
-        <v>84.939635431255269</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.99794257572004419</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB15">
-        <v>37.719445132522388</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99770761097472849</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP15">
-        <v>42.027132129978384</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8306,16 +8306,16 @@
         <v>489</v>
       </c>
       <c r="BA15" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="BB15" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.99563161774290432</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD15">
-        <v>80.087008046754136</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99330431978332978</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB16">
-        <v>122.75413730562111</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8422,10 +8422,10 @@
         <v>434</v>
       </c>
       <c r="AO16">
-        <v>0.99876486181024959</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP16">
-        <v>22.644200145424321</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="BB16" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="BC16">
-        <v>0.99284590877035406</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD16">
-        <v>131.158339210175</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Z17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.97905997046933124</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB17">
-        <v>383.90054139559413</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8568,10 +8568,10 @@
         <v>436</v>
       </c>
       <c r="AO17">
-        <v>0.99829462257458279</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP17">
-        <v>31.265252799315078</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="BB17" t="s">
-        <v>338</v>
+        <v>581</v>
       </c>
       <c r="BC17">
-        <v>0.98180592470173533</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD17">
-        <v>333.55804713485287</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="Z18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99887089404231622</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB18">
-        <v>20.700275890869406</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8714,10 +8714,10 @@
         <v>438</v>
       </c>
       <c r="AO18">
-        <v>0.99870209313763569</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP18">
-        <v>23.794959143345142</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="BB18" t="s">
         <v>337</v>
       </c>
       <c r="BC18">
-        <v>0.934538160869965</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD18">
-        <v>1200.1337173839754</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99870336240961599</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB19">
-        <v>23.771689157039763</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8860,10 +8860,10 @@
         <v>440</v>
       </c>
       <c r="AO19">
-        <v>0.99805167070369571</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP19">
-        <v>35.719370432245356</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="BB19" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="BC19">
-        <v>0.98822137145239475</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD19">
-        <v>215.94152337276336</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="Z20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99732110244768524</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB20">
-        <v>49.113121792437113</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9006,10 +9006,10 @@
         <v>442</v>
       </c>
       <c r="AO20">
-        <v>0.99864153733447103</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP20">
-        <v>24.905148868031663</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="BB20" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="BC20">
-        <v>0.99234935324205875</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD20">
-        <v>140.26185722892211</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="Z21" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.97645815754785015</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB21">
-        <v>431.60044495608111</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9152,10 +9152,10 @@
         <v>444</v>
       </c>
       <c r="AO21">
-        <v>0.99556268839291095</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP21">
-        <v>81.350712796633118</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="BB21" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="BC21">
-        <v>0.99361371414581767</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD21">
-        <v>117.0819073266757</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="Z22" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AA22">
-        <v>0.99860543314421912</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB22">
-        <v>25.567059022649978</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9295,13 +9295,13 @@
         <v>445</v>
       </c>
       <c r="AN22" t="s">
-        <v>340</v>
+        <v>446</v>
       </c>
       <c r="AO22">
-        <v>0.98819688225969682</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP22">
-        <v>216.39049190555826</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="BB22" t="s">
-        <v>587</v>
+        <v>337</v>
       </c>
       <c r="BC22">
-        <v>0.99637036284424008</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD22">
-        <v>66.543347855598327</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Z23" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA23">
-        <v>0.99604289943123792</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB23">
-        <v>72.546843760638723</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9438,16 +9438,16 @@
         <v>385</v>
       </c>
       <c r="AM23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN23" t="s">
-        <v>337</v>
+        <v>448</v>
       </c>
       <c r="AO23">
-        <v>0.96316479569784719</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP23">
-        <v>675.31207887280175</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="BB23" t="s">
-        <v>589</v>
+        <v>337</v>
       </c>
       <c r="BC23">
-        <v>0.99571574761974857</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD23">
-        <v>78.544626971276415</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="Z24" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AA24">
-        <v>0.99586101480039024</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB24">
-        <v>75.881395326178321</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9584,16 +9584,16 @@
         <v>387</v>
       </c>
       <c r="AM24" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AN24" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO24">
-        <v>0.99869874972548245</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP24">
-        <v>23.856255032822389</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="BB24" t="s">
-        <v>350</v>
+        <v>592</v>
       </c>
       <c r="BC24">
-        <v>0.97902641975794957</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD24">
-        <v>384.51563777092457</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="Z25" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA25">
-        <v>0.99727495176003056</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB25">
-        <v>49.959217732772544</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9730,16 +9730,16 @@
         <v>389</v>
       </c>
       <c r="AM25" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN25" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO25">
-        <v>0.99720193846171157</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP25">
-        <v>51.297794868621132</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9766,16 +9766,16 @@
         <v>509</v>
       </c>
       <c r="BA25" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="BB25" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="BC25">
-        <v>0.99648308811729225</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD25">
-        <v>64.476717849642213</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AA26">
-        <v>0.98747067058472104</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB26">
-        <v>229.70437261344725</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9876,16 +9876,16 @@
         <v>391</v>
       </c>
       <c r="AM26" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN26" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO26">
-        <v>0.99858912444516823</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP26">
-        <v>25.866051838582347</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="BB26" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="BC26">
-        <v>0.99764862450771852</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD26">
-        <v>43.108550691828107</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA27">
-        <v>0.99905729110642394</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB27">
-        <v>17.282996382227537</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10022,16 +10022,16 @@
         <v>393</v>
       </c>
       <c r="AM27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO27">
-        <v>0.99809873109145164</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP27">
-        <v>34.856596656720825</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10058,16 +10058,16 @@
         <v>513</v>
       </c>
       <c r="BA27" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="BB27" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="BC27">
-        <v>0.99678722224176453</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD27">
-        <v>58.900925567650859</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA28">
-        <v>0.99419544959877137</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB28">
-        <v>106.41675735585797</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10168,16 +10168,16 @@
         <v>395</v>
       </c>
       <c r="AM28" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN28" t="s">
-        <v>456</v>
+        <v>337</v>
       </c>
       <c r="AO28">
-        <v>0.99670212772821787</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP28">
-        <v>60.460991649339221</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="BB28" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="BC28">
-        <v>0.98831275563045873</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD28">
-        <v>214.26614677492421</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Z29" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="AA29">
-        <v>0.98845903150961834</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB29">
-        <v>211.58442232366301</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10314,16 +10314,16 @@
         <v>397</v>
       </c>
       <c r="AM29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN29" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO29">
-        <v>0.99870483393763032</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP29">
-        <v>23.744711143443137</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="BB29" t="s">
-        <v>346</v>
+        <v>602</v>
       </c>
       <c r="BC29">
-        <v>0.97803702976044449</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD29">
-        <v>402.65445439185123</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AA30">
-        <v>0.98176582039027138</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB30">
-        <v>334.29329284502461</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10460,16 +10460,16 @@
         <v>399</v>
       </c>
       <c r="AM30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN30" t="s">
-        <v>460</v>
+        <v>338</v>
       </c>
       <c r="AO30">
-        <v>0.99940622505963084</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP30">
-        <v>10.885873906767051</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="BB30" t="s">
-        <v>337</v>
+        <v>604</v>
       </c>
       <c r="BC30">
-        <v>0.94616153753972931</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD30">
-        <v>987.03847843829612</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="Z31" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AA31">
-        <v>0.99348252287636563</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB31">
-        <v>119.48708059996392</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10612,10 +10612,10 @@
         <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.99514593439357002</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP31">
-        <v>88.991202784549174</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="BB31" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="BC31">
-        <v>0.99735612831742793</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD31">
-        <v>48.47098084715428</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="Z32" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="AA32">
-        <v>0.9962850624543711</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB32">
-        <v>68.107188336529873</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10758,10 +10758,10 @@
         <v>464</v>
       </c>
       <c r="AO32">
-        <v>0.9969234886911541</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP32">
-        <v>56.402707328841686</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="BB32" t="s">
-        <v>604</v>
+        <v>357</v>
       </c>
       <c r="BC32">
-        <v>0.99021846023257276</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD32">
-        <v>179.32822906950017</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Z33" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AA33">
-        <v>0.99744350359843614</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB33">
-        <v>46.86910069533748</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10904,10 +10904,10 @@
         <v>466</v>
       </c>
       <c r="AO33">
-        <v>0.99825578453224051</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP33">
-        <v>31.977283575591127</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="BB33" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="BC33">
-        <v>0.99302778580016682</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD33">
-        <v>127.82392699694152</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="Z34" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AA34">
-        <v>0.9968826832446267</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB34">
-        <v>57.150807181843469</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11050,10 +11050,10 @@
         <v>468</v>
       </c>
       <c r="AO34">
-        <v>0.99621233314208923</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP34">
-        <v>69.440559061696689</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="BB34" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="BC34">
-        <v>0.99603752315790417</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD34">
-        <v>72.64540877175618</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="Z35" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA35">
-        <v>0.99854662761279667</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB35">
-        <v>26.645160432060571</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11196,10 +11196,10 @@
         <v>470</v>
       </c>
       <c r="AO35">
-        <v>0.99763984073088841</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP35">
-        <v>43.269586600378275</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="BB35" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="BC35">
-        <v>0.88199812838352587</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD35">
-        <v>2163.367646302027</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z36" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA36">
-        <v>0.9983436906516876</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB36">
-        <v>30.365671385728113</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11339,13 +11339,13 @@
         <v>471</v>
       </c>
       <c r="AN36" t="s">
-        <v>472</v>
+        <v>336</v>
       </c>
       <c r="AO36">
-        <v>0.9878316475733655</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP36">
-        <v>223.0864611549656</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="BB36" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC36">
-        <v>0.95957195194316591</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD36">
-        <v>741.18088104195795</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="Z37" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="AA37">
-        <v>0.99886682122259174</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB37">
-        <v>20.774944252484079</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
+        <v>472</v>
+      </c>
+      <c r="AN37" t="s">
         <v>473</v>
       </c>
-      <c r="AN37" t="s">
-        <v>474</v>
-      </c>
       <c r="AO37">
-        <v>0.99689519939751359</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP37">
-        <v>56.921344378917169</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="BB37" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="BC37">
-        <v>0.99232897920121688</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD37">
-        <v>140.63538131102445</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Z38" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AA38">
-        <v>0.99830231855562213</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB38">
-        <v>31.124159813595057</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AN38" t="s">
-        <v>476</v>
+        <v>338</v>
       </c>
       <c r="AO38">
-        <v>0.99750210533018213</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP38">
-        <v>45.794735613327241</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="BB38" t="s">
-        <v>615</v>
+        <v>337</v>
       </c>
       <c r="BC38">
-        <v>0.9205295464439136</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD38">
-        <v>1456.9583151949184</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99812715296949239</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB39">
-        <v>34.33552889264039</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11774,16 +11774,16 @@
         <v>417</v>
       </c>
       <c r="AM39" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN39" t="s">
-        <v>338</v>
+        <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.98092770889280956</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP39">
-        <v>349.65867029849198</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11810,16 +11810,16 @@
         <v>537</v>
       </c>
       <c r="BA39" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="BB39" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="BC39">
-        <v>0.98881218539944515</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD39">
-        <v>205.10993434350485</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.99810840151368141</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB40">
-        <v>34.679305582508199</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11920,16 +11920,16 @@
         <v>419</v>
       </c>
       <c r="AM40" t="s">
+        <v>477</v>
+      </c>
+      <c r="AN40" t="s">
         <v>478</v>
       </c>
-      <c r="AN40" t="s">
-        <v>479</v>
-      </c>
       <c r="AO40">
-        <v>0.99192535126433146</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP40">
-        <v>148.0352268205892</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11956,16 +11956,16 @@
         <v>539</v>
       </c>
       <c r="BA40" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="BB40" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="BC40">
-        <v>0.93089405249526469</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD40">
-        <v>1266.9423709201483</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -11994,16 +11994,16 @@
         <v>421</v>
       </c>
       <c r="AM41" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN41" t="s">
         <v>480</v>
       </c>
-      <c r="AN41" t="s">
-        <v>338</v>
-      </c>
       <c r="AO41">
-        <v>0.98949004263841422</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP41">
-        <v>192.68255162907312</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12030,16 +12030,16 @@
         <v>541</v>
       </c>
       <c r="BA41" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="BB41" t="s">
-        <v>340</v>
+        <v>622</v>
       </c>
       <c r="BC41">
-        <v>0.98355967005268352</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD41">
-        <v>301.40604903413595</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="BB42" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="BC42">
-        <v>0.98779966071713954</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD42">
-        <v>223.67288685244134</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="BB43" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="BC43">
-        <v>0.99604247516580058</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD43">
-        <v>72.554621960323615</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="BB44" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="BC44">
-        <v>0.98235584693125277</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD44">
-        <v>323.47613959369914</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="BB45" t="s">
-        <v>627</v>
+        <v>598</v>
       </c>
       <c r="BC45">
-        <v>0.99246863181599732</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD45">
-        <v>138.07508337338285</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="BB46" t="s">
-        <v>629</v>
+        <v>336</v>
       </c>
       <c r="BC46">
-        <v>0.99412039195829205</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD46">
-        <v>107.79281409797902</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12261,13 +12261,13 @@
         <v>630</v>
       </c>
       <c r="BB47" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="BC47">
-        <v>0.97589985979527272</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD47">
-        <v>441.83590375333313</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BB48" t="s">
-        <v>632</v>
+        <v>337</v>
       </c>
       <c r="BC48">
-        <v>0.99502210016107762</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD48">
-        <v>91.26149704691008</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12337,13 +12337,13 @@
         <v>633</v>
       </c>
       <c r="BB49" t="s">
-        <v>337</v>
+        <v>634</v>
       </c>
       <c r="BC49">
-        <v>0.96140381292129873</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD49">
-        <v>707.59676310952364</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12372,16 +12372,16 @@
         <v>559</v>
       </c>
       <c r="BA50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="BB50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BC50">
-        <v>0.99490784156958001</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD50">
-        <v>93.356237891033686</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12410,16 +12410,16 @@
         <v>561</v>
       </c>
       <c r="BA51" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BB51" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BC51">
-        <v>0.99560371543286275</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD51">
-        <v>80.598550397515965</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12448,16 +12448,16 @@
         <v>563</v>
       </c>
       <c r="BA52" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB52" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.99663140513677484</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD52">
-        <v>61.757572492461378</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12486,16 +12486,16 @@
         <v>565</v>
       </c>
       <c r="BA53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC53">
-        <v>0.99114508565756532</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD53">
-        <v>162.34009627796874</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB54" t="s">
-        <v>643</v>
+        <v>336</v>
       </c>
       <c r="BC54">
-        <v>0.95726256957223688</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD54">
-        <v>783.51955784232393</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4C6B4C-217F-4BDF-94AC-FF161F81A600}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB94F21-12AB-464B-A3B4-89FE9F024051}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>611</v>
+        <v>573</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>573</v>
+        <v>608</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>612</v>
+        <v>574</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>626</v>
+        <v>593</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>638</v>
+        <v>587</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>631</v>
+        <v>599</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>574</v>
+        <v>609</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>609</v>
+        <v>571</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>616</v>
+        <v>578</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>576</v>
+        <v>611</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8B8DC1-282D-4D89-9065-60847233BC46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B34F27-985F-4798-9ACC-9C57E9127BC4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417CB113-8697-41C5-A046-0542F9C37D44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4658E486-8F95-48DD-8486-A13335F42263}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C4DD2F7-6154-482B-B656-2C9EFF458277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D74BF7BA-CC27-4503-A575-A61E72C2CD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -973,6 +973,102 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_011</t>
   </si>
   <si>
@@ -1003,18 +1099,6 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_021</t>
   </si>
   <si>
@@ -1027,78 +1111,6 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_003</t>
   </si>
   <si>
@@ -1117,18 +1129,6 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1147,6 +1147,48 @@
     <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
   </si>
   <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
     <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
   </si>
   <si>
@@ -1162,55 +1204,181 @@
     <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
   </si>
   <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
-  </si>
-  <si>
     <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
     <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
   </si>
   <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
     <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+    <t>distr_wonelc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_006</t>
@@ -1225,178 +1393,166 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_JPN_020</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_023</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
     <t>elc_won_JPN_006</t>
@@ -1411,166 +1567,112 @@
     <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_020</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_023</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
-  </si>
-  <si>
     <t>elc_won_JPN_004</t>
   </si>
   <si>
     <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_043</t>
@@ -1609,6 +1711,102 @@
     <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_JPN_044</t>
   </si>
   <si>
@@ -1639,202 +1837,91 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
   </si>
   <si>
     <t>elc_wof_JPN_043</t>
@@ -1870,6 +1957,84 @@
     <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
   </si>
   <si>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
     <t>elc_wof_JPN_044</t>
   </si>
   <si>
@@ -1895,171 +2060,6 @@
   </si>
   <si>
     <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD905D1F-63E3-4FBE-A908-49D0D38720F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A820E381-3E08-439D-9261-CE270344213B}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7692,10 +7692,10 @@
         <v>424</v>
       </c>
       <c r="AO11">
-        <v>0.99796586165341161</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP11">
-        <v>37.292536354119903</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7728,10 +7728,10 @@
         <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.99603752315790417</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD11">
-        <v>72.64540877175618</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7838,10 +7838,10 @@
         <v>426</v>
       </c>
       <c r="AO12">
-        <v>0.99811838305018963</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP12">
-        <v>34.496310746523356</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7874,10 +7874,10 @@
         <v>572</v>
       </c>
       <c r="BC12">
-        <v>0.88199812838352587</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD12">
-        <v>2163.367646302027</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7984,10 +7984,10 @@
         <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.99514593439357002</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP13">
-        <v>88.991202784549174</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8017,13 +8017,13 @@
         <v>573</v>
       </c>
       <c r="BB13" t="s">
-        <v>337</v>
+        <v>574</v>
       </c>
       <c r="BC13">
-        <v>0.95957195194316591</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD13">
-        <v>741.18088104195795</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8130,10 +8130,10 @@
         <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.9969234886911541</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP14">
-        <v>56.402707328841686</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BB14" t="s">
-        <v>575</v>
+        <v>352</v>
       </c>
       <c r="BC14">
-        <v>0.99232897920121688</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD14">
-        <v>140.63538131102445</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Z15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.99810840151368141</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB15">
-        <v>34.679305582508199</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99876486181024959</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP15">
-        <v>22.644200145424321</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8312,10 +8312,10 @@
         <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.9205295464439136</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD15">
-        <v>1456.9583151949184</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="Z16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.99854662761279667</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB16">
-        <v>26.645160432060571</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8422,10 +8422,10 @@
         <v>434</v>
       </c>
       <c r="AO16">
-        <v>0.99781438034778358</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP16">
-        <v>40.069693623967019</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8455,13 +8455,13 @@
         <v>578</v>
       </c>
       <c r="BB16" t="s">
-        <v>579</v>
+        <v>336</v>
       </c>
       <c r="BC16">
-        <v>0.98881218539944515</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD16">
-        <v>205.10993434350485</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="Z17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.9983436906516876</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB17">
-        <v>30.365671385728113</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8568,10 +8568,10 @@
         <v>436</v>
       </c>
       <c r="AO17">
-        <v>0.99682717865030179</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP17">
-        <v>58.168391411134159</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
+        <v>579</v>
+      </c>
+      <c r="BB17" t="s">
         <v>580</v>
       </c>
-      <c r="BB17" t="s">
-        <v>581</v>
-      </c>
       <c r="BC17">
-        <v>0.99648308811729225</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD17">
-        <v>64.476717849642213</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Z18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.99886682122259174</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB18">
-        <v>20.774944252484079</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8714,10 +8714,10 @@
         <v>438</v>
       </c>
       <c r="AO18">
-        <v>0.99770761097472849</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP18">
-        <v>42.027132129978384</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB18" t="s">
         <v>582</v>
       </c>
-      <c r="BB18" t="s">
-        <v>337</v>
-      </c>
       <c r="BC18">
-        <v>0.96140381292129873</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD18">
-        <v>707.59676310952364</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="Z19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99830231855562213</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB19">
-        <v>31.124159813595057</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8860,10 +8860,10 @@
         <v>440</v>
       </c>
       <c r="AO19">
-        <v>0.99825578453224051</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP19">
-        <v>31.977283575591127</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8893,13 +8893,13 @@
         <v>583</v>
       </c>
       <c r="BB19" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="BC19">
-        <v>0.99490784156958001</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD19">
-        <v>93.356237891033686</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99858140874136669</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB20">
-        <v>26.007506408276679</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9003,13 +9003,13 @@
         <v>441</v>
       </c>
       <c r="AN20" t="s">
-        <v>442</v>
+        <v>337</v>
       </c>
       <c r="AO20">
-        <v>0.99869874972548245</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP20">
-        <v>23.856255032822389</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
+        <v>584</v>
+      </c>
+      <c r="BB20" t="s">
         <v>585</v>
       </c>
-      <c r="BB20" t="s">
-        <v>586</v>
-      </c>
       <c r="BC20">
-        <v>0.99560371543286275</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD20">
-        <v>80.598550397515965</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="Z21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA21">
-        <v>0.9980447041381848</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB21">
-        <v>35.847090799945306</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9146,16 +9146,16 @@
         <v>381</v>
       </c>
       <c r="AM21" t="s">
+        <v>442</v>
+      </c>
+      <c r="AN21" t="s">
         <v>443</v>
       </c>
-      <c r="AN21" t="s">
-        <v>444</v>
-      </c>
       <c r="AO21">
-        <v>0.99720193846171157</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP21">
-        <v>51.297794868621132</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="BB21" t="s">
-        <v>588</v>
+        <v>337</v>
       </c>
       <c r="BC21">
-        <v>0.99663140513677484</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD21">
-        <v>61.757572492461378</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="Z22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA22">
-        <v>0.99905729110642394</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB22">
-        <v>17.282996382227537</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9292,16 +9292,16 @@
         <v>383</v>
       </c>
       <c r="AM22" t="s">
+        <v>444</v>
+      </c>
+      <c r="AN22" t="s">
         <v>445</v>
       </c>
-      <c r="AN22" t="s">
-        <v>446</v>
-      </c>
       <c r="AO22">
-        <v>0.99858912444516823</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP22">
-        <v>25.866051838582347</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="BB22" t="s">
-        <v>337</v>
+        <v>588</v>
       </c>
       <c r="BC22">
-        <v>0.97218956380622079</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD22">
-        <v>509.85799688595205</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Z23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.99419544959877137</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB23">
-        <v>106.41675735585797</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9438,16 +9438,16 @@
         <v>385</v>
       </c>
       <c r="AM23" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN23" t="s">
         <v>447</v>
       </c>
-      <c r="AN23" t="s">
-        <v>448</v>
-      </c>
       <c r="AO23">
-        <v>0.99809873109145164</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP23">
-        <v>34.856596656720825</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
+        <v>589</v>
+      </c>
+      <c r="BB23" t="s">
         <v>590</v>
       </c>
-      <c r="BB23" t="s">
-        <v>337</v>
-      </c>
       <c r="BC23">
-        <v>0.97591598065988894</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD23">
-        <v>441.54035456870389</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AA24">
-        <v>0.98845903150961834</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB24">
-        <v>211.58442232366301</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9584,16 +9584,16 @@
         <v>387</v>
       </c>
       <c r="AM24" t="s">
+        <v>448</v>
+      </c>
+      <c r="AN24" t="s">
         <v>449</v>
       </c>
-      <c r="AN24" t="s">
-        <v>450</v>
-      </c>
       <c r="AO24">
-        <v>0.99621233314208923</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP24">
-        <v>69.440559061696689</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9626,10 +9626,10 @@
         <v>592</v>
       </c>
       <c r="BC24">
-        <v>0.9437657388784082</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD24">
-        <v>1030.9614538958492</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Z25" t="s">
         <v>348</v>
       </c>
       <c r="AA25">
-        <v>0.98176582039027138</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB25">
-        <v>334.29329284502461</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9730,16 +9730,16 @@
         <v>389</v>
       </c>
       <c r="AM25" t="s">
+        <v>450</v>
+      </c>
+      <c r="AN25" t="s">
         <v>451</v>
       </c>
-      <c r="AN25" t="s">
-        <v>452</v>
-      </c>
       <c r="AO25">
-        <v>0.99763984073088841</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP25">
-        <v>43.269586600378275</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9772,10 +9772,10 @@
         <v>594</v>
       </c>
       <c r="BC25">
-        <v>0.99246863181599732</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD25">
-        <v>138.07508337338285</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s">
         <v>349</v>
       </c>
       <c r="AA26">
-        <v>0.99887089404231622</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB26">
-        <v>20.700275890869406</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9876,16 +9876,16 @@
         <v>391</v>
       </c>
       <c r="AM26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN26" t="s">
-        <v>454</v>
+        <v>336</v>
       </c>
       <c r="AO26">
-        <v>0.9878316475733655</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP26">
-        <v>223.0864611549656</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9918,10 +9918,10 @@
         <v>596</v>
       </c>
       <c r="BC26">
-        <v>0.99412039195829205</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD26">
-        <v>107.79281409797902</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="Z27" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="AA27">
-        <v>0.99870336240961599</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB27">
-        <v>23.771689157039763</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10022,16 +10022,16 @@
         <v>393</v>
       </c>
       <c r="AM27" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN27" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99689519939751359</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP27">
-        <v>56.921344378917169</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10061,13 +10061,13 @@
         <v>597</v>
       </c>
       <c r="BB27" t="s">
-        <v>598</v>
+        <v>339</v>
       </c>
       <c r="BC27">
-        <v>0.97589985979527272</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD27">
-        <v>441.83590375333313</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="Z28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA28">
-        <v>0.99732110244768524</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB28">
-        <v>49.113121792437113</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10168,16 +10168,16 @@
         <v>395</v>
       </c>
       <c r="AM28" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO28">
-        <v>0.96316479569784719</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP28">
-        <v>675.31207887280175</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
+        <v>598</v>
+      </c>
+      <c r="BB28" t="s">
         <v>599</v>
       </c>
-      <c r="BB28" t="s">
-        <v>600</v>
-      </c>
       <c r="BC28">
-        <v>0.99502210016107762</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD28">
-        <v>91.26149704691008</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="Z29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA29">
-        <v>0.99744350359843614</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB29">
-        <v>46.86910069533748</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10314,16 +10314,16 @@
         <v>397</v>
       </c>
       <c r="AM29" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AN29" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AO29">
-        <v>0.99192535126433146</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP29">
-        <v>148.0352268205892</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
+        <v>600</v>
+      </c>
+      <c r="BB29" t="s">
         <v>601</v>
       </c>
-      <c r="BB29" t="s">
-        <v>602</v>
-      </c>
       <c r="BC29">
-        <v>0.99764862450771852</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD29">
-        <v>43.108550691828107</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Z30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA30">
-        <v>0.9968826832446267</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB30">
-        <v>57.150807181843469</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10460,16 +10460,16 @@
         <v>399</v>
       </c>
       <c r="AM30" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN30" t="s">
-        <v>338</v>
+        <v>459</v>
       </c>
       <c r="AO30">
-        <v>0.98949004263841422</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP30">
-        <v>192.68255162907312</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="BB30" t="s">
-        <v>604</v>
+        <v>337</v>
       </c>
       <c r="BC30">
-        <v>0.99678722224176453</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD30">
-        <v>58.900925567650859</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="Z31" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA31">
-        <v>0.99812715296949239</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB31">
-        <v>34.33552889264039</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10606,16 +10606,16 @@
         <v>401</v>
       </c>
       <c r="AM31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AN31" t="s">
-        <v>462</v>
+        <v>338</v>
       </c>
       <c r="AO31">
-        <v>0.99829462257458279</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP31">
-        <v>31.265252799315078</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BB31" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="BC31">
-        <v>0.98831275563045873</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD31">
-        <v>214.26614677492421</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Z32" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="AA32">
-        <v>0.97645815754785015</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB32">
-        <v>431.60044495608111</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AN32" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AO32">
-        <v>0.99870209313763569</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP32">
-        <v>23.794959143345142</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="BB32" t="s">
-        <v>357</v>
+        <v>606</v>
       </c>
       <c r="BC32">
-        <v>0.97803702976044449</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD32">
-        <v>402.65445439185123</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Z33" t="s">
         <v>355</v>
       </c>
       <c r="AA33">
-        <v>0.99860543314421912</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB33">
-        <v>25.567059022649978</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AN33" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AO33">
-        <v>0.99805167070369571</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP33">
-        <v>35.719370432245356</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
+        <v>607</v>
+      </c>
+      <c r="BB33" t="s">
         <v>608</v>
       </c>
-      <c r="BB33" t="s">
-        <v>344</v>
-      </c>
       <c r="BC33">
-        <v>0.99536692897647694</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD33">
-        <v>84.939635431255269</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="Z34" t="s">
         <v>356</v>
       </c>
       <c r="AA34">
-        <v>0.99604289943123792</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB34">
-        <v>72.546843760638723</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN34" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO34">
-        <v>0.99864153733447103</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP34">
-        <v>24.905148868031663</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11086,10 +11086,10 @@
         <v>610</v>
       </c>
       <c r="BC34">
-        <v>0.99563161774290432</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD34">
-        <v>80.087008046754136</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Z35" t="s">
         <v>357</v>
       </c>
       <c r="AA35">
-        <v>0.99586101480039024</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB35">
-        <v>75.881395326178321</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11190,16 +11190,16 @@
         <v>409</v>
       </c>
       <c r="AM35" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN35" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AO35">
-        <v>0.99556268839291095</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP35">
-        <v>81.350712796633118</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11232,10 +11232,10 @@
         <v>612</v>
       </c>
       <c r="BC35">
-        <v>0.99284590877035406</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD35">
-        <v>131.158339210175</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="Z36" t="s">
         <v>358</v>
       </c>
       <c r="AA36">
-        <v>0.99794257572004419</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB36">
-        <v>37.719445132522388</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AN36" t="s">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="AO36">
-        <v>0.98819688225969682</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP36">
-        <v>216.39049190555826</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11375,13 +11375,13 @@
         <v>613</v>
       </c>
       <c r="BB36" t="s">
-        <v>338</v>
+        <v>614</v>
       </c>
       <c r="BC36">
-        <v>0.98180592470173533</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD36">
-        <v>333.55804713485287</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="Z37" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="AA37">
-        <v>0.99330431978332978</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB37">
-        <v>122.75413730562111</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
+        <v>471</v>
+      </c>
+      <c r="AN37" t="s">
         <v>472</v>
       </c>
-      <c r="AN37" t="s">
-        <v>473</v>
-      </c>
       <c r="AO37">
-        <v>0.99750210533018213</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP37">
-        <v>45.794735613327241</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="BB37" t="s">
-        <v>615</v>
+        <v>336</v>
       </c>
       <c r="BC37">
-        <v>0.99114508565756532</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD37">
-        <v>162.34009627796874</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="Z38" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="AA38">
-        <v>0.97905997046933124</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB38">
-        <v>383.90054139559413</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN38" t="s">
         <v>474</v>
       </c>
-      <c r="AN38" t="s">
-        <v>338</v>
-      </c>
       <c r="AO38">
-        <v>0.98092770889280956</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP38">
-        <v>349.65867029849198</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11670,10 +11670,10 @@
         <v>337</v>
       </c>
       <c r="BC38">
-        <v>0.934538160869965</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD38">
-        <v>1200.1337173839754</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="Z39" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="AA39">
-        <v>0.99348252287636563</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB39">
-        <v>119.48708059996392</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11780,10 +11780,10 @@
         <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.99670212772821787</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP39">
-        <v>60.460991649339221</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11816,10 +11816,10 @@
         <v>618</v>
       </c>
       <c r="BC39">
-        <v>0.98822137145239475</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD39">
-        <v>215.94152337276336</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="AA40">
-        <v>0.9962850624543711</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB40">
-        <v>68.107188336529873</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.99870483393763032</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP40">
-        <v>23.744711143443137</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11962,10 +11962,10 @@
         <v>620</v>
       </c>
       <c r="BC40">
-        <v>0.99234935324205875</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD40">
-        <v>140.26185722892211</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99940622505963084</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP41">
-        <v>10.885873906767051</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12036,10 +12036,10 @@
         <v>622</v>
       </c>
       <c r="BC41">
-        <v>0.99361371414581767</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD41">
-        <v>117.0819073266757</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12071,13 +12071,13 @@
         <v>623</v>
       </c>
       <c r="BB42" t="s">
-        <v>624</v>
+        <v>337</v>
       </c>
       <c r="BC42">
-        <v>0.99637036284424008</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD42">
-        <v>66.543347855598327</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="BB43" t="s">
-        <v>626</v>
+        <v>337</v>
       </c>
       <c r="BC43">
-        <v>0.99571574761974857</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD43">
-        <v>78.544626971276415</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="BB44" t="s">
-        <v>348</v>
+        <v>626</v>
       </c>
       <c r="BC44">
-        <v>0.97902641975794957</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD44">
-        <v>384.51563777092457</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="BB45" t="s">
-        <v>598</v>
+        <v>345</v>
       </c>
       <c r="BC45">
-        <v>0.93089405249526469</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD45">
-        <v>1266.9423709201483</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
+        <v>628</v>
+      </c>
+      <c r="BB46" t="s">
         <v>629</v>
       </c>
-      <c r="BB46" t="s">
-        <v>336</v>
-      </c>
       <c r="BC46">
-        <v>0.98355967005268352</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD46">
-        <v>301.40604903413595</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12264,10 +12264,10 @@
         <v>631</v>
       </c>
       <c r="BC47">
-        <v>0.95726256957223688</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD47">
-        <v>783.51955784232393</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12299,13 +12299,13 @@
         <v>632</v>
       </c>
       <c r="BB48" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC48">
-        <v>0.94616153753972931</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD48">
-        <v>987.03847843829612</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12340,10 +12340,10 @@
         <v>634</v>
       </c>
       <c r="BC49">
-        <v>0.99735612831742793</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD49">
-        <v>48.47098084715428</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12378,10 +12378,10 @@
         <v>636</v>
       </c>
       <c r="BC50">
-        <v>0.99021846023257276</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD50">
-        <v>179.32822906950017</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12413,13 +12413,13 @@
         <v>637</v>
       </c>
       <c r="BB51" t="s">
-        <v>638</v>
+        <v>337</v>
       </c>
       <c r="BC51">
-        <v>0.99302778580016682</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD51">
-        <v>127.82392699694152</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12448,16 +12448,16 @@
         <v>563</v>
       </c>
       <c r="BA52" t="s">
+        <v>638</v>
+      </c>
+      <c r="BB52" t="s">
         <v>639</v>
       </c>
-      <c r="BB52" t="s">
-        <v>640</v>
-      </c>
       <c r="BC52">
-        <v>0.98779966071713954</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD52">
-        <v>223.67288685244134</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12486,16 +12486,16 @@
         <v>565</v>
       </c>
       <c r="BA53" t="s">
+        <v>640</v>
+      </c>
+      <c r="BB53" t="s">
         <v>641</v>
       </c>
-      <c r="BB53" t="s">
-        <v>642</v>
-      </c>
       <c r="BC53">
-        <v>0.99604247516580058</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD53">
-        <v>72.554621960323615</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB54" t="s">
         <v>643</v>
       </c>
-      <c r="BB54" t="s">
-        <v>336</v>
-      </c>
       <c r="BC54">
-        <v>0.98235584693125277</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD54">
-        <v>323.47613959369914</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB94F21-12AB-464B-A3B4-89FE9F024051}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FC588-F8E8-40F2-A81E-22C0E1891770}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>616</v>
+        <v>586</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>589</v>
+        <v>623</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>423</v>
+        <v>475</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>582</v>
+        <v>637</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>585</v>
+        <v>640</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>621</v>
+        <v>591</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>617</v>
+        <v>587</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>587</v>
+        <v>642</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>625</v>
+        <v>595</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>605</v>
+        <v>573</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>629</v>
+        <v>578</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>641</v>
+        <v>613</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>591</v>
+        <v>625</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>628</v>
+        <v>576</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>580</v>
+        <v>635</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B34F27-985F-4798-9ACC-9C57E9127BC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF332B2-9408-4965-B068-C87246F903E5}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4658E486-8F95-48DD-8486-A13335F42263}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B60E3DF-DE1C-43FA-9B09-FF1AD01C0E8B}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D74BF7BA-CC27-4503-A575-A61E72C2CD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F349661-AF72-463F-A976-6EB6A9552C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,24 +943,180 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_027</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_002</t>
   </si>
   <si>
@@ -973,168 +1129,45 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
     <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
   </si>
   <si>
@@ -1144,75 +1177,42 @@
     <t>e_JP306-500_JPN</t>
   </si>
   <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
     <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
   </si>
   <si>
     <t>e_JP6-275_JPN</t>
   </si>
   <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
     <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
   </si>
   <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_020</t>
   </si>
   <si>
@@ -1225,6 +1225,24 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_014</t>
   </si>
   <si>
@@ -1243,6 +1261,96 @@
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_JPN_008</t>
   </si>
   <si>
@@ -1273,88 +1381,16 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>distr_wonelc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_026</t>
@@ -1363,42 +1399,6 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_won_JPN_020</t>
   </si>
   <si>
@@ -1411,6 +1411,24 @@
     <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
     <t>elc_won_JPN_014</t>
   </si>
   <si>
@@ -1429,6 +1447,87 @@
     <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
   </si>
   <si>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
     <t>elc_won_JPN_008</t>
   </si>
   <si>
@@ -1456,79 +1555,16 @@
     <t>elc_won_JPN_001</t>
   </si>
   <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+    <t>elc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
   </si>
   <si>
     <t>elc_won_JPN_026</t>
@@ -1537,40 +1573,196 @@
     <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_009</t>
@@ -1597,18 +1789,6 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_015</t>
   </si>
   <si>
@@ -1633,150 +1813,6 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_JPN_010</t>
   </si>
   <si>
@@ -1801,40 +1837,169 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
+    <t>elc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_009</t>
@@ -1858,15 +2023,6 @@
     <t>elc_wof_JPN_021</t>
   </si>
   <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_015</t>
   </si>
   <si>
@@ -1888,129 +2044,6 @@
     <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
     <t>elc_wof_JPN_010</t>
   </si>
   <si>
@@ -2027,39 +2060,6 @@
   </si>
   <si>
     <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A820E381-3E08-439D-9261-CE270344213B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22EC45D4-0966-4C74-B6F5-90E9747035D6}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99727495176003056</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB11">
-        <v>49.959217732772544</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7725,13 +7725,13 @@
         <v>569</v>
       </c>
       <c r="BB11" t="s">
-        <v>570</v>
+        <v>348</v>
       </c>
       <c r="BC11">
-        <v>0.99764862450771852</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD11">
-        <v>43.108550691828107</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.98747067058472104</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB12">
-        <v>229.70437261344725</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7868,16 +7868,16 @@
         <v>483</v>
       </c>
       <c r="BA12" t="s">
+        <v>570</v>
+      </c>
+      <c r="BB12" t="s">
         <v>571</v>
       </c>
-      <c r="BB12" t="s">
-        <v>572</v>
-      </c>
       <c r="BC12">
-        <v>0.99678722224176453</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD12">
-        <v>58.900925567650859</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.96199717699083387</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB13">
-        <v>696.71842183471267</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7984,10 +7984,10 @@
         <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.99781438034778358</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP13">
-        <v>40.069693623967019</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
+        <v>572</v>
+      </c>
+      <c r="BB13" t="s">
         <v>573</v>
       </c>
-      <c r="BB13" t="s">
-        <v>574</v>
-      </c>
       <c r="BC13">
-        <v>0.98831275563045873</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD13">
-        <v>214.26614677492421</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99548081999408422</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB14">
-        <v>82.851633441789744</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8130,10 +8130,10 @@
         <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.99682717865030179</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP14">
-        <v>58.168391411134159</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
+        <v>574</v>
+      </c>
+      <c r="BB14" t="s">
         <v>575</v>
       </c>
-      <c r="BB14" t="s">
-        <v>352</v>
-      </c>
       <c r="BC14">
-        <v>0.97803702976044449</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD14">
-        <v>402.65445439185123</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="Z15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.98845903150961834</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB15">
-        <v>211.58442232366301</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99770761097472849</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP15">
-        <v>42.027132129978384</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8309,13 +8309,13 @@
         <v>576</v>
       </c>
       <c r="BB15" t="s">
-        <v>577</v>
+        <v>348</v>
       </c>
       <c r="BC15">
-        <v>0.93089405249526469</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD15">
-        <v>1266.9423709201483</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="Z16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.98176582039027138</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB16">
-        <v>334.29329284502461</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8422,10 +8422,10 @@
         <v>434</v>
       </c>
       <c r="AO16">
-        <v>0.99869874972548245</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP16">
-        <v>23.856255032822389</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BB16" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="BC16">
-        <v>0.98355967005268352</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD16">
-        <v>301.40604903413595</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Z17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99887089404231622</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB17">
-        <v>20.700275890869406</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8568,10 +8568,10 @@
         <v>436</v>
       </c>
       <c r="AO17">
-        <v>0.99720193846171157</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP17">
-        <v>51.297794868621132</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
+        <v>578</v>
+      </c>
+      <c r="BB17" t="s">
         <v>579</v>
       </c>
-      <c r="BB17" t="s">
-        <v>580</v>
-      </c>
       <c r="BC17">
-        <v>0.99246863181599732</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD17">
-        <v>138.07508337338285</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="Z18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99870336240961599</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB18">
-        <v>23.771689157039763</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8714,10 +8714,10 @@
         <v>438</v>
       </c>
       <c r="AO18">
-        <v>0.99858912444516823</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP18">
-        <v>25.866051838582347</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BB18" t="s">
-        <v>582</v>
+        <v>348</v>
       </c>
       <c r="BC18">
-        <v>0.99412039195829205</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD18">
-        <v>107.79281409797902</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="Z19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99732110244768524</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB19">
-        <v>49.113121792437113</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8860,10 +8860,10 @@
         <v>440</v>
       </c>
       <c r="AO19">
-        <v>0.99809873109145164</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP19">
-        <v>34.856596656720825</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="BB19" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="BC19">
-        <v>0.97589985979527272</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD19">
-        <v>441.83590375333313</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="Z20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99744350359843614</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB20">
-        <v>46.86910069533748</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9003,13 +9003,13 @@
         <v>441</v>
       </c>
       <c r="AN20" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="AO20">
-        <v>0.96316479569784719</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP20">
-        <v>675.31207887280175</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
+        <v>583</v>
+      </c>
+      <c r="BB20" t="s">
         <v>584</v>
       </c>
-      <c r="BB20" t="s">
-        <v>585</v>
-      </c>
       <c r="BC20">
-        <v>0.99502210016107762</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD20">
-        <v>91.26149704691008</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="Z21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.9968826832446267</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB21">
-        <v>57.150807181843469</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9152,10 +9152,10 @@
         <v>443</v>
       </c>
       <c r="AO21">
-        <v>0.99876486181024959</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP21">
-        <v>22.644200145424321</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
+        <v>585</v>
+      </c>
+      <c r="BB21" t="s">
         <v>586</v>
       </c>
-      <c r="BB21" t="s">
-        <v>337</v>
-      </c>
       <c r="BC21">
-        <v>0.934538160869965</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD21">
-        <v>1200.1337173839754</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="Z22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA22">
-        <v>0.99858140874136669</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB22">
-        <v>26.007506408276679</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9298,10 +9298,10 @@
         <v>445</v>
       </c>
       <c r="AO22">
-        <v>0.99870209313763569</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP22">
-        <v>23.794959143345142</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9334,10 +9334,10 @@
         <v>588</v>
       </c>
       <c r="BC22">
-        <v>0.98822137145239475</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD22">
-        <v>215.94152337276336</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="Z23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA23">
-        <v>0.9980447041381848</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB23">
-        <v>35.847090799945306</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9444,10 +9444,10 @@
         <v>447</v>
       </c>
       <c r="AO23">
-        <v>0.99805167070369571</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP23">
-        <v>35.719370432245356</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9480,10 +9480,10 @@
         <v>590</v>
       </c>
       <c r="BC23">
-        <v>0.99234935324205875</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD23">
-        <v>140.26185722892211</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA24">
-        <v>0.99348252287636563</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB24">
-        <v>119.48708059996392</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>449</v>
       </c>
       <c r="AO24">
-        <v>0.99864153733447103</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP24">
-        <v>24.905148868031663</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9623,13 +9623,13 @@
         <v>591</v>
       </c>
       <c r="BB24" t="s">
-        <v>592</v>
+        <v>359</v>
       </c>
       <c r="BC24">
-        <v>0.99361371414581767</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD24">
-        <v>117.0819073266757</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA25">
-        <v>0.9962850624543711</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB25">
-        <v>68.107188336529873</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9733,13 +9733,13 @@
         <v>450</v>
       </c>
       <c r="AN25" t="s">
-        <v>451</v>
+        <v>347</v>
       </c>
       <c r="AO25">
-        <v>0.99556268839291095</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP25">
-        <v>81.350712796633118</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9766,16 +9766,16 @@
         <v>509</v>
       </c>
       <c r="BA25" t="s">
+        <v>592</v>
+      </c>
+      <c r="BB25" t="s">
         <v>593</v>
       </c>
-      <c r="BB25" t="s">
-        <v>594</v>
-      </c>
       <c r="BC25">
-        <v>0.99637036284424008</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD25">
-        <v>66.543347855598327</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA26">
-        <v>0.99812715296949239</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB26">
-        <v>34.33552889264039</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9876,16 +9876,16 @@
         <v>391</v>
       </c>
       <c r="AM26" t="s">
+        <v>451</v>
+      </c>
+      <c r="AN26" t="s">
         <v>452</v>
       </c>
-      <c r="AN26" t="s">
-        <v>336</v>
-      </c>
       <c r="AO26">
-        <v>0.98819688225969682</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP26">
-        <v>216.39049190555826</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
+        <v>594</v>
+      </c>
+      <c r="BB26" t="s">
         <v>595</v>
       </c>
-      <c r="BB26" t="s">
-        <v>596</v>
-      </c>
       <c r="BC26">
-        <v>0.99571574761974857</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD26">
-        <v>78.544626971276415</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="AA27">
-        <v>0.97645815754785015</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB27">
-        <v>431.60044495608111</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99192535126433146</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP27">
-        <v>148.0352268205892</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10058,16 +10058,16 @@
         <v>513</v>
       </c>
       <c r="BA27" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BB27" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="BC27">
-        <v>0.97902641975794957</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD27">
-        <v>384.51563777092457</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="Z28" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA28">
-        <v>0.99860543314421912</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB28">
-        <v>25.567059022649978</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10171,13 +10171,13 @@
         <v>455</v>
       </c>
       <c r="AN28" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.98949004263841422</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP28">
-        <v>192.68255162907312</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
+        <v>597</v>
+      </c>
+      <c r="BB28" t="s">
         <v>598</v>
       </c>
-      <c r="BB28" t="s">
-        <v>599</v>
-      </c>
       <c r="BC28">
-        <v>0.99603752315790417</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD28">
-        <v>72.64540877175618</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Z29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA29">
-        <v>0.99604289943123792</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB29">
-        <v>72.546843760638723</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10314,16 +10314,16 @@
         <v>397</v>
       </c>
       <c r="AM29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN29" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99825578453224051</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP29">
-        <v>31.977283575591127</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
+        <v>599</v>
+      </c>
+      <c r="BB29" t="s">
         <v>600</v>
       </c>
-      <c r="BB29" t="s">
-        <v>601</v>
-      </c>
       <c r="BC29">
-        <v>0.88199812838352587</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD29">
-        <v>2163.367646302027</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="Z30" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AA30">
-        <v>0.99586101480039024</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB30">
-        <v>75.881395326178321</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10460,16 +10460,16 @@
         <v>399</v>
       </c>
       <c r="AM30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99750210533018213</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP30">
-        <v>45.794735613327241</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="BB30" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="BC30">
-        <v>0.95957195194316591</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD30">
-        <v>741.18088104195795</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AA31">
-        <v>0.99810840151368141</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB31">
-        <v>34.679305582508199</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10606,16 +10606,16 @@
         <v>401</v>
       </c>
       <c r="AM31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN31" t="s">
-        <v>338</v>
+        <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.98092770889280956</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP31">
-        <v>349.65867029849198</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="BB31" t="s">
-        <v>604</v>
+        <v>348</v>
       </c>
       <c r="BC31">
-        <v>0.99232897920121688</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD31">
-        <v>140.63538131102445</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AA32">
-        <v>0.99854662761279667</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB32">
-        <v>26.645160432060571</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN32" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO32">
-        <v>0.99670212772821787</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP32">
-        <v>60.460991649339221</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BB32" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="BC32">
-        <v>0.9205295464439136</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD32">
-        <v>1456.9583151949184</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA33">
-        <v>0.9983436906516876</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB33">
-        <v>30.365671385728113</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AN33" t="s">
-        <v>464</v>
+        <v>358</v>
       </c>
       <c r="AO33">
-        <v>0.99870483393763032</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP33">
-        <v>23.744711143443137</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="BB33" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="BC33">
-        <v>0.98881218539944515</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD33">
-        <v>205.10993434350485</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="Z34" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AA34">
-        <v>0.99886682122259174</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB34">
-        <v>20.774944252484079</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN34" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO34">
-        <v>0.99940622505963084</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP34">
-        <v>10.885873906767051</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="BB34" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="BC34">
-        <v>0.95726256957223688</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD34">
-        <v>783.51955784232393</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Z35" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA35">
-        <v>0.99830231855562213</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB35">
-        <v>31.124159813595057</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11190,16 +11190,16 @@
         <v>409</v>
       </c>
       <c r="AM35" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN35" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO35">
-        <v>0.99621233314208923</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP35">
-        <v>69.440559061696689</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="BB35" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="BC35">
-        <v>0.98779966071713954</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD35">
-        <v>223.67288685244134</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="Z36" t="s">
         <v>358</v>
       </c>
       <c r="AA36">
-        <v>0.99905729110642394</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB36">
-        <v>17.282996382227537</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN36" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO36">
-        <v>0.99763984073088841</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP36">
-        <v>43.269586600378275</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="BB36" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="BC36">
-        <v>0.99604247516580058</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD36">
-        <v>72.554621960323615</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="Z37" t="s">
         <v>359</v>
       </c>
       <c r="AA37">
-        <v>0.99419544959877137</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB37">
-        <v>106.41675735585797</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN37" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO37">
-        <v>0.9878316475733655</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP37">
-        <v>223.0864611549656</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="BB37" t="s">
-        <v>336</v>
+        <v>614</v>
       </c>
       <c r="BC37">
-        <v>0.98235584693125277</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD37">
-        <v>323.47613959369914</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="Z38" t="s">
         <v>360</v>
       </c>
       <c r="AA38">
-        <v>0.99794257572004419</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB38">
-        <v>37.719445132522388</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN38" t="s">
-        <v>474</v>
+        <v>348</v>
       </c>
       <c r="AO38">
-        <v>0.99689519939751359</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP38">
-        <v>56.921344378917169</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
+        <v>615</v>
+      </c>
+      <c r="BB38" t="s">
         <v>616</v>
       </c>
-      <c r="BB38" t="s">
-        <v>337</v>
-      </c>
       <c r="BC38">
-        <v>0.94616153753972931</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD38">
-        <v>987.03847843829612</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="Z39" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="AA39">
-        <v>0.99330431978332978</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB39">
-        <v>122.75413730562111</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11813,13 +11813,13 @@
         <v>617</v>
       </c>
       <c r="BB39" t="s">
-        <v>618</v>
+        <v>348</v>
       </c>
       <c r="BC39">
-        <v>0.99735612831742793</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD39">
-        <v>48.47098084715428</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Z40" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="AA40">
-        <v>0.97905997046933124</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB40">
-        <v>383.90054139559413</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11956,16 +11956,16 @@
         <v>539</v>
       </c>
       <c r="BA40" t="s">
+        <v>618</v>
+      </c>
+      <c r="BB40" t="s">
         <v>619</v>
       </c>
-      <c r="BB40" t="s">
-        <v>620</v>
-      </c>
       <c r="BC40">
-        <v>0.99021846023257276</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD40">
-        <v>179.32822906950017</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99829462257458279</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP41">
-        <v>31.265252799315078</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12030,16 +12030,16 @@
         <v>541</v>
       </c>
       <c r="BA41" t="s">
+        <v>620</v>
+      </c>
+      <c r="BB41" t="s">
         <v>621</v>
       </c>
-      <c r="BB41" t="s">
-        <v>622</v>
-      </c>
       <c r="BC41">
-        <v>0.99302778580016682</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD41">
-        <v>127.82392699694152</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
+        <v>622</v>
+      </c>
+      <c r="BB42" t="s">
         <v>623</v>
       </c>
-      <c r="BB42" t="s">
-        <v>337</v>
-      </c>
       <c r="BC42">
-        <v>0.97218956380622079</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD42">
-        <v>509.85799688595205</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12109,13 +12109,13 @@
         <v>624</v>
       </c>
       <c r="BB43" t="s">
-        <v>337</v>
+        <v>625</v>
       </c>
       <c r="BC43">
-        <v>0.97591598065988894</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD43">
-        <v>441.54035456870389</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="BB44" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="BC44">
-        <v>0.9437657388784082</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD44">
-        <v>1030.9614538958492</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="BB45" t="s">
-        <v>345</v>
+        <v>629</v>
       </c>
       <c r="BC45">
-        <v>0.99536692897647694</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD45">
-        <v>84.939635431255269</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="BB46" t="s">
-        <v>629</v>
+        <v>351</v>
       </c>
       <c r="BC46">
-        <v>0.99563161774290432</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD46">
-        <v>80.087008046754136</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12258,16 +12258,16 @@
         <v>553</v>
       </c>
       <c r="BA47" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="BB47" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="BC47">
-        <v>0.99284590877035406</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD47">
-        <v>131.158339210175</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="BB48" t="s">
-        <v>338</v>
+        <v>634</v>
       </c>
       <c r="BC48">
-        <v>0.98180592470173533</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD48">
-        <v>333.55804713485287</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12334,16 +12334,16 @@
         <v>557</v>
       </c>
       <c r="BA49" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="BB49" t="s">
-        <v>634</v>
+        <v>600</v>
       </c>
       <c r="BC49">
-        <v>0.99114508565756532</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD49">
-        <v>162.34009627796874</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12372,16 +12372,16 @@
         <v>559</v>
       </c>
       <c r="BA50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="BB50" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BC50">
-        <v>0.99648308811729225</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD50">
-        <v>64.476717849642213</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12410,16 +12410,16 @@
         <v>561</v>
       </c>
       <c r="BA51" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="BB51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BC51">
-        <v>0.96140381292129873</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD51">
-        <v>707.59676310952364</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12448,16 +12448,16 @@
         <v>563</v>
       </c>
       <c r="BA52" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="BB52" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.99490784156958001</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD52">
-        <v>93.356237891033686</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12486,16 +12486,16 @@
         <v>565</v>
       </c>
       <c r="BA53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="BB53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="BC53">
-        <v>0.99560371543286275</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD53">
-        <v>80.598550397515965</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BB54" t="s">
-        <v>643</v>
+        <v>358</v>
       </c>
       <c r="BC54">
-        <v>0.99663140513677484</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD54">
-        <v>61.757572492461378</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FC588-F8E8-40F2-A81E-22C0E1891770}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEC581C-1937-4BAD-B871-8080317E904D}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>623</v>
+        <v>576</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>624</v>
+        <v>577</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>569</v>
+        <v>624</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>473</v>
+        <v>431</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>579</v>
+        <v>631</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>584</v>
+        <v>636</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>469</v>
+        <v>427</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>575</v>
+        <v>630</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>573</v>
+        <v>628</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>633</v>
+        <v>597</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>581</v>
+        <v>633</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>625</v>
+        <v>578</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>571</v>
+        <v>626</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF332B2-9408-4965-B068-C87246F903E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E709C4-91DF-4ECE-8B8C-9B63FFC027C4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B60E3DF-DE1C-43FA-9B09-FF1AD01C0E8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79597B8-07BA-4B07-BBA7-6F1C4EEAD2E4}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F349661-AF72-463F-A976-6EB6A9552C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9067C96-42CC-46F6-9ACB-0AD4A8F99BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,64 +943,178 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_solelc_spv_JPN_021</t>
@@ -1015,151 +1129,82 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+  </si>
+  <si>
+    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
     <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w242253500-500_JPN,e_w317416612-500_JPN,e_w193544791-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_w307942220-500_JPN,e_JP218-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN,e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w421647841-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
   </si>
   <si>
     <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
@@ -1168,49 +1213,154 @@
     <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
   </si>
   <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w168727982-500_JPN,e_w132913106-500_JPN,e_w168839127-500_JPN,e_w105298089-500_JPN,e_w104391636-500_JPN,e_JP23-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+    <t>distr_wonelc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_020</t>
@@ -1225,24 +1375,6 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_014</t>
   </si>
   <si>
@@ -1261,142 +1393,148 @@
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_003</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
+    <t>elc_won_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_006</t>
+  </si>
+  <si>
+    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_009</t>
+  </si>
+  <si>
+    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
   </si>
   <si>
     <t>elc_won_JPN_020</t>
@@ -1411,24 +1549,6 @@
     <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
     <t>elc_won_JPN_014</t>
   </si>
   <si>
@@ -1447,130 +1567,178 @@
     <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
-  </si>
-  <si>
     <t>elc_won_JPN_003</t>
   </si>
   <si>
     <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_006</t>
-  </si>
-  <si>
-    <t>e_w215451416-500_JPN,e_JP296-500_JPN,e_w405626236-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_009</t>
-  </si>
-  <si>
-    <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+    <t>distr_wofelc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_006</t>
@@ -1597,22 +1765,34 @@
     <t>connecting wind offshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_001</t>
@@ -1657,184 +1837,145 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>elc_wof_JPN_043</t>
+  </si>
+  <si>
+    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_035</t>
+  </si>
+  <si>
+    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_006</t>
@@ -1858,16 +1999,31 @@
     <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
   </si>
   <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_001</t>
@@ -1904,162 +2060,6 @@
   </si>
   <si>
     <t>elc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_043</t>
-  </si>
-  <si>
-    <t>e_w105298089-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_035</t>
-  </si>
-  <si>
-    <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22EC45D4-0966-4C74-B6F5-90E9747035D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D91ABDE-24B4-4661-9920-9618142520EF}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99810840151368141</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB11">
-        <v>34.679305582508199</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7692,10 +7692,10 @@
         <v>424</v>
       </c>
       <c r="AO11">
-        <v>0.99514593439357002</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP11">
-        <v>88.991202784549174</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7725,13 +7725,13 @@
         <v>569</v>
       </c>
       <c r="BB11" t="s">
-        <v>348</v>
+        <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.95957195194316591</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD11">
-        <v>741.18088104195795</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99348252287636563</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB12">
-        <v>119.48708059996392</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7838,10 +7838,10 @@
         <v>426</v>
       </c>
       <c r="AO12">
-        <v>0.9969234886911541</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP12">
-        <v>56.402707328841686</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7868,16 +7868,16 @@
         <v>483</v>
       </c>
       <c r="BA12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="BB12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="BC12">
-        <v>0.99232897920121688</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD12">
-        <v>140.63538131102445</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.9962850624543711</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB13">
-        <v>68.107188336529873</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7984,10 +7984,10 @@
         <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.99763984073088841</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP13">
-        <v>43.269586600378275</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8014,16 +8014,16 @@
         <v>485</v>
       </c>
       <c r="BA13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="BB13" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="BC13">
-        <v>0.9205295464439136</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD13">
-        <v>1456.9583151949184</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99858140874136669</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB14">
-        <v>26.007506408276679</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8130,10 +8130,10 @@
         <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.9878316475733655</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP14">
-        <v>223.0864611549656</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8160,16 +8160,16 @@
         <v>487</v>
       </c>
       <c r="BA14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BB14" t="s">
-        <v>575</v>
+        <v>350</v>
       </c>
       <c r="BC14">
-        <v>0.98881218539944515</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD14">
-        <v>205.10993434350485</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.9980447041381848</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB15">
-        <v>35.847090799945306</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99689519939751359</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP15">
-        <v>56.921344378917169</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8309,13 +8309,13 @@
         <v>576</v>
       </c>
       <c r="BB15" t="s">
-        <v>348</v>
+        <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.97218956380622079</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD15">
-        <v>509.85799688595205</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99854662761279667</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB16">
-        <v>26.645160432060571</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8419,13 +8419,13 @@
         <v>433</v>
       </c>
       <c r="AN16" t="s">
-        <v>434</v>
+        <v>337</v>
       </c>
       <c r="AO16">
-        <v>0.99781438034778358</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP16">
-        <v>40.069693623967019</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="BB16" t="s">
-        <v>348</v>
+        <v>579</v>
       </c>
       <c r="BC16">
-        <v>0.97591598065988894</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD16">
-        <v>441.54035456870389</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.9983436906516876</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB17">
-        <v>30.365671385728113</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8562,16 +8562,16 @@
         <v>373</v>
       </c>
       <c r="AM17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN17" t="s">
-        <v>436</v>
+        <v>350</v>
       </c>
       <c r="AO17">
-        <v>0.99682717865030179</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP17">
-        <v>58.168391411134159</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="BB17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="BC17">
-        <v>0.9437657388784082</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD17">
-        <v>1030.9614538958492</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="Z18" t="s">
         <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99886682122259174</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB18">
-        <v>20.774944252484079</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8708,16 +8708,16 @@
         <v>375</v>
       </c>
       <c r="AM18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AN18" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AO18">
-        <v>0.99770761097472849</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP18">
-        <v>42.027132129978384</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="BB18" t="s">
-        <v>348</v>
+        <v>583</v>
       </c>
       <c r="BC18">
-        <v>0.934538160869965</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD18">
-        <v>1200.1337173839754</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Z19" t="s">
         <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99830231855562213</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB19">
-        <v>31.124159813595057</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8854,16 +8854,16 @@
         <v>377</v>
       </c>
       <c r="AM19" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AN19" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AO19">
-        <v>0.99192535126433146</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP19">
-        <v>148.0352268205892</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="BB19" t="s">
-        <v>582</v>
+        <v>336</v>
       </c>
       <c r="BC19">
-        <v>0.98822137145239475</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD19">
-        <v>215.94152337276336</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="Z20" t="s">
         <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99905729110642394</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB20">
-        <v>17.282996382227537</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9000,16 +9000,16 @@
         <v>379</v>
       </c>
       <c r="AM20" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN20" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="AO20">
-        <v>0.98949004263841422</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP20">
-        <v>192.68255162907312</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="BB20" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="BC20">
-        <v>0.99234935324205875</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD20">
-        <v>140.26185722892211</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z21" t="s">
         <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.99419544959877137</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB21">
-        <v>106.41675735585797</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9146,16 +9146,16 @@
         <v>381</v>
       </c>
       <c r="AM21" t="s">
+        <v>441</v>
+      </c>
+      <c r="AN21" t="s">
         <v>442</v>
       </c>
-      <c r="AN21" t="s">
-        <v>443</v>
-      </c>
       <c r="AO21">
-        <v>0.99870209313763569</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP21">
-        <v>23.794959143345142</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="BB21" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="BC21">
-        <v>0.99361371414581767</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD21">
-        <v>117.0819073266757</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="Z22" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AA22">
-        <v>0.99727495176003056</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB22">
-        <v>49.959217732772544</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9292,16 +9292,16 @@
         <v>383</v>
       </c>
       <c r="AM22" t="s">
+        <v>443</v>
+      </c>
+      <c r="AN22" t="s">
         <v>444</v>
       </c>
-      <c r="AN22" t="s">
-        <v>445</v>
-      </c>
       <c r="AO22">
-        <v>0.99805167070369571</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP22">
-        <v>35.719370432245356</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="BB22" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="BC22">
-        <v>0.99637036284424008</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD22">
-        <v>66.543347855598327</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="Z23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.98747067058472104</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB23">
-        <v>229.70437261344725</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9438,16 +9438,16 @@
         <v>385</v>
       </c>
       <c r="AM23" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN23" t="s">
         <v>446</v>
       </c>
-      <c r="AN23" t="s">
-        <v>447</v>
-      </c>
       <c r="AO23">
-        <v>0.99864153733447103</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP23">
-        <v>24.905148868031663</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="BB23" t="s">
-        <v>590</v>
+        <v>336</v>
       </c>
       <c r="BC23">
-        <v>0.99571574761974857</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD23">
-        <v>78.544626971276415</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="Z24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA24">
-        <v>0.97645815754785015</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB24">
-        <v>431.60044495608111</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9584,16 +9584,16 @@
         <v>387</v>
       </c>
       <c r="AM24" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN24" t="s">
         <v>448</v>
       </c>
-      <c r="AN24" t="s">
-        <v>449</v>
-      </c>
       <c r="AO24">
-        <v>0.99556268839291095</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP24">
-        <v>81.350712796633118</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="BB24" t="s">
-        <v>359</v>
+        <v>593</v>
       </c>
       <c r="BC24">
-        <v>0.97902641975794957</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD24">
-        <v>384.51563777092457</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Z25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA25">
-        <v>0.99860543314421912</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB25">
-        <v>25.567059022649978</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9730,16 +9730,16 @@
         <v>389</v>
       </c>
       <c r="AM25" t="s">
+        <v>449</v>
+      </c>
+      <c r="AN25" t="s">
         <v>450</v>
       </c>
-      <c r="AN25" t="s">
-        <v>347</v>
-      </c>
       <c r="AO25">
-        <v>0.98819688225969682</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP25">
-        <v>216.39049190555826</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9766,16 +9766,16 @@
         <v>509</v>
       </c>
       <c r="BA25" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="BB25" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="BC25">
-        <v>0.98779966071713954</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD25">
-        <v>223.67288685244134</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA26">
-        <v>0.99604289943123792</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB26">
-        <v>72.546843760638723</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.99670212772821787</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP26">
-        <v>60.460991649339221</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="BB26" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="BC26">
-        <v>0.99604247516580058</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD26">
-        <v>72.554621960323615</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="Z27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA27">
-        <v>0.99586101480039024</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB27">
-        <v>75.881395326178321</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99870483393763032</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP27">
-        <v>23.744711143443137</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10058,16 +10058,16 @@
         <v>513</v>
       </c>
       <c r="BA27" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="BB27" t="s">
-        <v>347</v>
+        <v>598</v>
       </c>
       <c r="BC27">
-        <v>0.98235584693125277</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD27">
-        <v>323.47613959369914</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="Z28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA28">
-        <v>0.99887089404231622</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB28">
-        <v>20.700275890869406</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10174,10 +10174,10 @@
         <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.99940622505963084</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP28">
-        <v>10.885873906767051</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="BB28" t="s">
-        <v>598</v>
+        <v>346</v>
       </c>
       <c r="BC28">
-        <v>0.99114508565756532</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD28">
-        <v>162.34009627796874</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Z29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA29">
-        <v>0.99870336240961599</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB29">
-        <v>23.771689157039763</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10320,10 +10320,10 @@
         <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99829462257458279</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP29">
-        <v>31.265252799315078</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="BB29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="BC29">
-        <v>0.93089405249526469</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD29">
-        <v>1266.9423709201483</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="Z30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA30">
-        <v>0.99732110244768524</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB30">
-        <v>49.113121792437113</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10466,10 +10466,10 @@
         <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99876486181024959</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP30">
-        <v>22.644200145424321</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="BB30" t="s">
-        <v>347</v>
+        <v>603</v>
       </c>
       <c r="BC30">
-        <v>0.98355967005268352</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD30">
-        <v>301.40604903413595</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="Z31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA31">
-        <v>0.99744350359843614</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB31">
-        <v>46.86910069533748</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10609,13 +10609,13 @@
         <v>461</v>
       </c>
       <c r="AN31" t="s">
-        <v>462</v>
+        <v>336</v>
       </c>
       <c r="AO31">
-        <v>0.99825578453224051</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP31">
-        <v>31.977283575591127</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="BB31" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="BC31">
-        <v>0.94616153753972931</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD31">
-        <v>987.03847843829612</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z32" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="AA32">
-        <v>0.9968826832446267</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB32">
-        <v>57.150807181843469</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
+        <v>462</v>
+      </c>
+      <c r="AN32" t="s">
         <v>463</v>
       </c>
-      <c r="AN32" t="s">
-        <v>464</v>
-      </c>
       <c r="AO32">
-        <v>0.99750210533018213</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP32">
-        <v>45.794735613327241</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="BB32" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="BC32">
-        <v>0.99735612831742793</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD32">
-        <v>48.47098084715428</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="Z33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AA33">
-        <v>0.99794257572004419</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB33">
-        <v>37.719445132522388</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
+        <v>464</v>
+      </c>
+      <c r="AN33" t="s">
         <v>465</v>
       </c>
-      <c r="AN33" t="s">
-        <v>358</v>
-      </c>
       <c r="AO33">
-        <v>0.98092770889280956</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP33">
-        <v>349.65867029849198</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="BB33" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="BC33">
-        <v>0.99021846023257276</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD33">
-        <v>179.32822906950017</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="Z34" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="AA34">
-        <v>0.99330431978332978</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB34">
-        <v>122.75413730562111</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11050,10 +11050,10 @@
         <v>467</v>
       </c>
       <c r="AO34">
-        <v>0.99869874972548245</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP34">
-        <v>23.856255032822389</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="BB34" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="BC34">
-        <v>0.99302778580016682</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD34">
-        <v>127.82392699694152</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Z35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA35">
-        <v>0.97905997046933124</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB35">
-        <v>383.90054139559413</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11193,13 +11193,13 @@
         <v>468</v>
       </c>
       <c r="AN35" t="s">
-        <v>469</v>
+        <v>337</v>
       </c>
       <c r="AO35">
-        <v>0.99720193846171157</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP35">
-        <v>51.297794868621132</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="BB35" t="s">
-        <v>610</v>
+        <v>353</v>
       </c>
       <c r="BC35">
-        <v>0.99603752315790417</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD35">
-        <v>72.64540877175618</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z36" t="s">
         <v>358</v>
       </c>
       <c r="AA36">
-        <v>0.98845903150961834</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB36">
-        <v>211.58442232366301</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
+        <v>469</v>
+      </c>
+      <c r="AN36" t="s">
         <v>470</v>
       </c>
-      <c r="AN36" t="s">
-        <v>471</v>
-      </c>
       <c r="AO36">
-        <v>0.99858912444516823</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP36">
-        <v>25.866051838582347</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="BB36" t="s">
-        <v>612</v>
+        <v>350</v>
       </c>
       <c r="BC36">
-        <v>0.88199812838352587</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD36">
-        <v>2163.367646302027</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Z37" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AA37">
-        <v>0.98176582039027138</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB37">
-        <v>334.29329284502461</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11482,16 +11482,16 @@
         <v>413</v>
       </c>
       <c r="AM37" t="s">
+        <v>471</v>
+      </c>
+      <c r="AN37" t="s">
         <v>472</v>
       </c>
-      <c r="AN37" t="s">
-        <v>473</v>
-      </c>
       <c r="AO37">
-        <v>0.99809873109145164</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP37">
-        <v>34.856596656720825</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11521,13 +11521,13 @@
         <v>613</v>
       </c>
       <c r="BB37" t="s">
-        <v>614</v>
+        <v>350</v>
       </c>
       <c r="BC37">
-        <v>0.99648308811729225</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD37">
-        <v>64.476717849642213</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Z38" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="AA38">
-        <v>0.99812715296949239</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB38">
-        <v>34.33552889264039</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11628,16 +11628,16 @@
         <v>415</v>
       </c>
       <c r="AM38" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN38" t="s">
         <v>474</v>
       </c>
-      <c r="AN38" t="s">
-        <v>348</v>
-      </c>
       <c r="AO38">
-        <v>0.96316479569784719</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP38">
-        <v>675.31207887280175</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11664,16 +11664,16 @@
         <v>535</v>
       </c>
       <c r="BA38" t="s">
+        <v>614</v>
+      </c>
+      <c r="BB38" t="s">
         <v>615</v>
       </c>
-      <c r="BB38" t="s">
-        <v>616</v>
-      </c>
       <c r="BC38">
-        <v>0.95726256957223688</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD38">
-        <v>783.51955784232393</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="Z39" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.96199717699083387</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB39">
-        <v>696.71842183471267</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11780,10 +11780,10 @@
         <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.99796586165341161</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP39">
-        <v>37.292536354119903</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11810,16 +11810,16 @@
         <v>537</v>
       </c>
       <c r="BA39" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="BB39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="BC39">
-        <v>0.96140381292129873</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD39">
-        <v>707.59676310952364</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="Z40" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.99548081999408422</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB40">
-        <v>82.851633441789744</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.99811838305018963</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP40">
-        <v>34.496310746523356</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11956,16 +11956,16 @@
         <v>539</v>
       </c>
       <c r="BA40" t="s">
+        <v>617</v>
+      </c>
+      <c r="BB40" t="s">
         <v>618</v>
       </c>
-      <c r="BB40" t="s">
-        <v>619</v>
-      </c>
       <c r="BC40">
-        <v>0.99490784156958001</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD40">
-        <v>93.356237891033686</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99621233314208923</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP41">
-        <v>69.440559061696689</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12030,16 +12030,16 @@
         <v>541</v>
       </c>
       <c r="BA41" t="s">
+        <v>619</v>
+      </c>
+      <c r="BB41" t="s">
         <v>620</v>
       </c>
-      <c r="BB41" t="s">
-        <v>621</v>
-      </c>
       <c r="BC41">
-        <v>0.99560371543286275</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD41">
-        <v>80.598550397515965</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>543</v>
       </c>
       <c r="BA42" t="s">
+        <v>621</v>
+      </c>
+      <c r="BB42" t="s">
         <v>622</v>
       </c>
-      <c r="BB42" t="s">
-        <v>623</v>
-      </c>
       <c r="BC42">
-        <v>0.99663140513677484</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD42">
-        <v>61.757572492461378</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>545</v>
       </c>
       <c r="BA43" t="s">
+        <v>623</v>
+      </c>
+      <c r="BB43" t="s">
         <v>624</v>
       </c>
-      <c r="BB43" t="s">
-        <v>625</v>
-      </c>
       <c r="BC43">
-        <v>0.99764862450771852</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD43">
-        <v>43.108550691828107</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12144,16 +12144,16 @@
         <v>547</v>
       </c>
       <c r="BA44" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="BB44" t="s">
-        <v>627</v>
+        <v>350</v>
       </c>
       <c r="BC44">
-        <v>0.99678722224176453</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD44">
-        <v>58.900925567650859</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12182,16 +12182,16 @@
         <v>549</v>
       </c>
       <c r="BA45" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="BB45" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="BC45">
-        <v>0.98831275563045873</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD45">
-        <v>214.26614677492421</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="BB46" t="s">
-        <v>351</v>
+        <v>629</v>
       </c>
       <c r="BC46">
-        <v>0.97803702976044449</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD46">
-        <v>402.65445439185123</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12258,16 +12258,16 @@
         <v>553</v>
       </c>
       <c r="BA47" t="s">
+        <v>630</v>
+      </c>
+      <c r="BB47" t="s">
         <v>631</v>
       </c>
-      <c r="BB47" t="s">
-        <v>632</v>
-      </c>
       <c r="BC47">
-        <v>0.99246863181599732</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD47">
-        <v>138.07508337338285</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="BB48" t="s">
-        <v>634</v>
+        <v>350</v>
       </c>
       <c r="BC48">
-        <v>0.99412039195829205</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD48">
-        <v>107.79281409797902</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12334,16 +12334,16 @@
         <v>557</v>
       </c>
       <c r="BA49" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="BB49" t="s">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="BC49">
-        <v>0.97589985979527272</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD49">
-        <v>441.83590375333313</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12372,16 +12372,16 @@
         <v>559</v>
       </c>
       <c r="BA50" t="s">
+        <v>635</v>
+      </c>
+      <c r="BB50" t="s">
         <v>636</v>
       </c>
-      <c r="BB50" t="s">
-        <v>637</v>
-      </c>
       <c r="BC50">
-        <v>0.99502210016107762</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD50">
-        <v>91.26149704691008</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12410,16 +12410,16 @@
         <v>561</v>
       </c>
       <c r="BA51" t="s">
+        <v>637</v>
+      </c>
+      <c r="BB51" t="s">
         <v>638</v>
       </c>
-      <c r="BB51" t="s">
-        <v>338</v>
-      </c>
       <c r="BC51">
-        <v>0.99536692897647694</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD51">
-        <v>84.939635431255269</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12454,10 +12454,10 @@
         <v>640</v>
       </c>
       <c r="BC52">
-        <v>0.99563161774290432</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD52">
-        <v>80.087008046754136</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12492,10 +12492,10 @@
         <v>642</v>
       </c>
       <c r="BC53">
-        <v>0.99284590877035406</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD53">
-        <v>131.158339210175</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12527,13 +12527,13 @@
         <v>643</v>
       </c>
       <c r="BB54" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="BC54">
-        <v>0.98180592470173533</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD54">
-        <v>333.55804713485287</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEC581C-1937-4BAD-B871-8080317E904D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A7E4FA2-CD64-4B6D-B237-D2CD46BDBA55}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>580</v>
+        <v>632</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>576</v>
+        <v>612</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>577</v>
+        <v>613</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>638</v>
+        <v>599</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>585</v>
+        <v>637</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>581</v>
+        <v>633</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>636</v>
+        <v>597</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>591</v>
+        <v>643</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>639</v>
+        <v>600</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>587</v>
+        <v>639</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>578</v>
+        <v>614</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>626</v>
+        <v>607</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>607</v>
+        <v>580</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>609</v>
+        <v>569</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E709C4-91DF-4ECE-8B8C-9B63FFC027C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB69CD3E-6E4A-4896-AEFF-8AE3EEB2CADE}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79597B8-07BA-4B07-BBA7-6F1C4EEAD2E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10B7AC1-03B4-4B62-8538-00CBB9FC5FBA}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9067C96-42CC-46F6-9ACB-0AD4A8F99BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDC9F6F6-AEAB-415D-BFC4-61945CB5AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -943,18 +943,48 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_JPN_015</t>
   </si>
   <si>
@@ -991,6 +1021,72 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_solelc_spv_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_JPN_023</t>
   </si>
   <si>
@@ -1009,28 +1105,16 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
+    <t>distr_solelc_spv_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_solelc_spv_JPN_004</t>
@@ -1045,105 +1129,33 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN</t>
+  </si>
+  <si>
     <t>e_JP269-500_JPN,e_w186510275-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
   </si>
   <si>
     <t>e_w179863079-275_JPN</t>
   </si>
   <si>
-    <t>e_JP7-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
     <t>e_JP306-500_JPN,e_JP292-500_JPN,e_JP294-500_JPN,e_w172601929-500_JPN,e_w215451416-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
   </si>
   <si>
@@ -1156,6 +1168,30 @@
     <t>e_JP4-275_JPN,e_JP3-275_JPN,e_JP1-275_JPN</t>
   </si>
   <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
     <t>e_w150035494-500_JPN,e_JP73-500_JPN,e_w66098469-500_JPN,e_w315434358-500_JPN,e_w250540807-500_JPN,e_r15580570-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
   </si>
   <si>
@@ -1165,13 +1201,10 @@
     <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
   </si>
   <si>
-    <t>e_JP9-500_JPN,e_JP8-275_JPN,e_w1028554758-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_w785319805-500_JPN,e_w106076988-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN</t>
+    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
   </si>
   <si>
     <t>e_JP306-500_JPN,e_w215451416-500_JPN</t>
@@ -1180,37 +1213,160 @@
     <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN</t>
   </si>
   <si>
-    <t>e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170247312-500_JPN,e_w170850727-500_JPN,e_w170366035-500_JPN,e_w116559939-500_JPN,e_w142662111-500_JPN,e_w209429410-500_JPN,e_w315662839-500_JPN,e_w210090094-500_JPN,e_w459476442-500_JPN,e_w209726348-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>e_JP116-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN,e_JP74-500_JPN,e_JP25-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN,e_r17013811-500_JPN,e_w315662839-500_JPN,e_JP28-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w317511904-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP296-500_JPN,e_w405626236-500_JPN,e_w201293312-500_JPN,e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP5-275_JPN,e_JP9-500_JPN</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w145079972-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w174636874-500_JPN,e_JP10-500_JPN</t>
+    <t>distr_wonelc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wonelc_won_JPN_005</t>
@@ -1219,126 +1375,6 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_006</t>
   </si>
   <si>
@@ -1351,18 +1387,6 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_JPN_020</t>
   </si>
   <si>
@@ -1375,28 +1399,148 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wonelc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>elc_won_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_024</t>
+  </si>
+  <si>
+    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_025</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_010</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_013</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_027</t>
+  </si>
+  <si>
+    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_030</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_016</t>
+  </si>
+  <si>
+    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_031</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_004</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_026</t>
+  </si>
+  <si>
+    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_003</t>
+  </si>
+  <si>
+    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_019</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_002</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_015</t>
+  </si>
+  <si>
+    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_018</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_012</t>
+  </si>
+  <si>
+    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_007</t>
+  </si>
+  <si>
+    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_022</t>
+  </si>
+  <si>
+    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_021</t>
+  </si>
+  <si>
+    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_028</t>
+  </si>
+  <si>
+    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_won_JPN_029</t>
   </si>
   <si>
     <t>elc_won_JPN_005</t>
@@ -1405,117 +1549,6 @@
     <t>e_JP294-500_JPN,e_w172601929-500_JPN,e_w216502300-500_JPN,e_w405626236-500_JPN,e_w172144358-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_019</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_w186510275-500_JPN,e_JP306-500_JPN,e_w185029969-500_JPN,e_w172601929-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_002</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w215451416-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_015</t>
-  </si>
-  <si>
-    <t>e_w210090094-500_JPN,e_JP219-500_JPN,e_w150065045-500_JPN,e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_016</t>
-  </si>
-  <si>
-    <t>e_w204258596-500_JPN,e_w317416612-500_JPN,e_JP117-500_JPN,e_w317511904-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_031</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_004</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w170974371-500_JPN,e_w171066843-500_JPN,e_w241828221-500_JPN,e_w87538349-500_JPN,e_w102958903-500_JPN,e_w241822623-500_JPN,e_JP218-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_026</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP4-275_JPN,e_JP8-275_JPN,e_JP9-500_JPN,e_w1028554758-500_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500_JPN,e_w109834508-500_JPN,e_w161727149-500_JPN,e_w169031998-500_JPN,e_w170589736-500_JPN,e_JP156-500_JPN,e_w170537514-500_JPN,e_JP96-500_JPN,e_w170850727-500_JPN,e_w142662111-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_007</t>
-  </si>
-  <si>
-    <t>e_w169031998-500_JPN,e_w170537514-500_JPN,e_w170247312-500_JPN,e_w116559939-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_022</t>
-  </si>
-  <si>
-    <t>e_w315434358-500_JPN,e_w250540807-500_JPN,e_JP41-500_JPN,e_JP29-500_JPN,e_JP30-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_021</t>
-  </si>
-  <si>
-    <t>e_w168839127-500_JPN,e_w104391636-500_JPN,e_w253566674-500_JPN,e_JP19-500_JPN,e_JP23-500_JPN,e_w104173570-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_018</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_w216953915-500_JPN,e_JP296-500_JPN,e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w722673849-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP135-500_JPN,e_JP120-500_JPN,e_w421647841-500_JPN,e_JP116-500_JPN,e_w1029010255-500_JPN,e_JP122-500_JPN,e_w315618377-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_012</t>
-  </si>
-  <si>
-    <t>e_w145079972-500_JPN,e_r15580570-500_JPN,e_w168839127-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_010</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN,e_w307942220-500_JPN,e_JP248-500_JPN,e_JP175-500_JPN,e_JP249-500_JPN,e_w291678103-500_JPN,e_w170605907-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w256682313-500_JPN,e_JP25-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_013</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_r2269992-500_JPN,e_JP132-500_JPN,e_w168727982-500_JPN,e_w132913106-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_027</t>
-  </si>
-  <si>
-    <t>e_w174636874-500_JPN,e_JP10-500_JPN,e_JP9-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_030</t>
-  </si>
-  <si>
     <t>elc_won_JPN_006</t>
   </si>
   <si>
@@ -1528,15 +1561,6 @@
     <t>e_JP74-500_JPN,e_w975217734-500_JPN,e_JP57-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_028</t>
-  </si>
-  <si>
-    <t>e_w179863079-275_JPN,e_JP6-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_029</t>
-  </si>
-  <si>
     <t>elc_won_JPN_020</t>
   </si>
   <si>
@@ -1549,28 +1573,256 @@
     <t>e_JP21-500_JPN,e_w1030329139-500_JPN,e_w659138214-500_JPN</t>
   </si>
   <si>
-    <t>elc_won_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w459476442-500_JPN,e_w150065045-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_024</t>
-  </si>
-  <si>
-    <t>e_w106076988-500_JPN,e_w785319805-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_025</t>
-  </si>
-  <si>
-    <t>e_w801582512-275_JPN,e_JP5-275_JPN,e_JP4-275_JPN,e_JP9-500_JPN,e_JP3-275_JPN,e_JP1-275_JPN,e_JP7-275_JPN,e_JP6-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_won_JPN_003</t>
-  </si>
-  <si>
-    <t>e_w201293312-500_JPN,e_w204258596-500_JPN,e_w242253500-500_JPN,e_w193544791-500_JPN,e_w317416612-500_JPN,e_w170974371-500_JPN</t>
+    <t>distr_wofelc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_JPN_043</t>
@@ -1585,256 +1837,217 @@
     <t>connecting wind offshore to buses in cluster 35</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_JPN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>elc_wof_JPN_009</t>
+  </si>
+  <si>
+    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_039</t>
+  </si>
+  <si>
+    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_022</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_014</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_025</t>
+  </si>
+  <si>
+    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_042</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_034</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_026</t>
+  </si>
+  <si>
+    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_041</t>
+  </si>
+  <si>
+    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_013</t>
+  </si>
+  <si>
+    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_037</t>
+  </si>
+  <si>
+    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_040</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_036</t>
+  </si>
+  <si>
+    <t>e_JP219-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_030</t>
+  </si>
+  <si>
+    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_008</t>
+  </si>
+  <si>
+    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_016</t>
+  </si>
+  <si>
+    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_015</t>
+  </si>
+  <si>
+    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_033</t>
+  </si>
+  <si>
+    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_038</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_017</t>
+  </si>
+  <si>
+    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_028</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_044</t>
+  </si>
+  <si>
+    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_031</t>
+  </si>
+  <si>
+    <t>e_JP117-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_032</t>
+  </si>
+  <si>
+    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_012</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_029</t>
+  </si>
+  <si>
+    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_011</t>
+  </si>
+  <si>
+    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_027</t>
+  </si>
+  <si>
+    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_018</t>
+  </si>
+  <si>
+    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_JPN_005</t>
+  </si>
+  <si>
+    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
   </si>
   <si>
     <t>elc_wof_JPN_043</t>
@@ -1847,219 +2060,6 @@
   </si>
   <si>
     <t>e_JP132-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_028</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_014</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w187988970-500_JPN,e_w204258596-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_025</t>
-  </si>
-  <si>
-    <t>e_JP21-500_JPN,e_w174636874-500_JPN,e_w659138214-500_JPN,e_w106076988-500_JPN,e_JP10-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_042</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w106076988-500_JPN,e_w174636874-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_036</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_044</t>
-  </si>
-  <si>
-    <t>e_w149843487-500_JPN,e_w315461259-500_JPN,e_JP132-500_JPN,e_w151379730-500_JPN,e_w168727982-500_JPN,e_w105298089-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_031</t>
-  </si>
-  <si>
-    <t>e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_032</t>
-  </si>
-  <si>
-    <t>e_JP121-500_JPN,e_w1029010255-500_JPN,e_w315618377-500_JPN,e_w256682313-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_015</t>
-  </si>
-  <si>
-    <t>e_JP269-500_JPN,e_JP292-500_JPN,e_w186510275-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_033</t>
-  </si>
-  <si>
-    <t>e_w317511904-500_JPN,e_JP117-500_JPN,e_w242103481-500_JPN,e_w242253537-500_JPN,e_JP137-500_JPN,e_JP120-500_JPN,e_JP25-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_038</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_017</t>
-  </si>
-  <si>
-    <t>e_w1028554758-500_JPN,e_JP9-500_JPN,e_JP5-275_JPN,e_JP7-275_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_026</t>
-  </si>
-  <si>
-    <t>e_r17013811-500_JPN,e_JP21-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_041</t>
-  </si>
-  <si>
-    <t>e_w156208858-500_JPN,e_w901872431-500_JPN,e_w104173570-500_JPN,e_w106076988-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_009</t>
-  </si>
-  <si>
-    <t>e_w722673849-500_JPN,e_w1037516198-500_JPN,e_w291678103-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_039</t>
-  </si>
-  <si>
-    <t>e_w170247312-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_022</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_JP1-275_JPN,e_w179863079-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_034</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_JP132-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_013</t>
-  </si>
-  <si>
-    <t>e_JP292-500_JPN,e_JP269-500_JPN,e_JP306-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_037</t>
-  </si>
-  <si>
-    <t>e_w216956620-500_JPN,e_JP219-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_040</t>
-  </si>
-  <si>
-    <t>e_JP219-500_JPN,e_w149843487-500_JPN,e_JP132-500_JPN,e_w315461259-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_005</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_030</t>
-  </si>
-  <si>
-    <t>e_w317416612-500_JPN,e_JP117-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_008</t>
-  </si>
-  <si>
-    <t>e_w216778426-500_JPN,e_w1037299172-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_016</t>
-  </si>
-  <si>
-    <t>e_JP4-275_JPN,e_w179863079-275_JPN,e_JP7-275_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_012</t>
-  </si>
-  <si>
-    <t>e_JP306-500_JPN,e_w216956620-500_JPN,e_w215451416-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_029</t>
-  </si>
-  <si>
-    <t>e_w186510275-500_JPN,e_w204258596-500_JPN,e_w317416612-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_011</t>
-  </si>
-  <si>
-    <t>e_w1037299172-500_JPN,e_w172907196-500_JPN,e_w171066843-500_JPN,e_w722673849-500_JPN,e_w1037516198-500_JPN,e_JP249-500_JPN,e_w1038584990-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_027</t>
-  </si>
-  <si>
-    <t>e_JP25-500_JPN,e_w256682313-500_JPN,e_r17013811-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_018</t>
-  </si>
-  <si>
-    <t>e_JP8-275_JPN,e_w801582512-275_JPN,e_JP9-500_JPN,e_JP10-500_JPN,e_w714627759-500_JPN</t>
-  </si>
-  <si>
-    <t>elc_wof_JPN_020</t>
   </si>
   <si>
     <t>e_won_JPN_001</t>
@@ -7412,7 +7412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D91ABDE-24B4-4661-9920-9618142520EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E4F324-1327-48F3-B5AD-7B6D0E335784}">
   <dimension ref="B9:BD54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -7650,16 +7650,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99794257572004419</v>
+        <v>0.99812715296949239</v>
       </c>
       <c r="AB11">
-        <v>37.719445132522388</v>
+        <v>34.33552889264039</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7692,10 +7692,10 @@
         <v>424</v>
       </c>
       <c r="AO11">
-        <v>0.99876486181024959</v>
+        <v>0.99781438034778358</v>
       </c>
       <c r="AP11">
-        <v>22.644200145424321</v>
+        <v>40.069693623967019</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7728,10 +7728,10 @@
         <v>570</v>
       </c>
       <c r="BC11">
-        <v>0.99603752315790417</v>
+        <v>0.99764862450771852</v>
       </c>
       <c r="BD11">
-        <v>72.64540877175618</v>
+        <v>43.108550691828107</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7796,16 +7796,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99330431978332978</v>
+        <v>0.99905729110642394</v>
       </c>
       <c r="AB12">
-        <v>122.75413730562111</v>
+        <v>17.282996382227537</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7838,10 +7838,10 @@
         <v>426</v>
       </c>
       <c r="AO12">
-        <v>0.99763984073088841</v>
+        <v>0.99682717865030179</v>
       </c>
       <c r="AP12">
-        <v>43.269586600378275</v>
+        <v>58.168391411134159</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7874,10 +7874,10 @@
         <v>572</v>
       </c>
       <c r="BC12">
-        <v>0.88199812838352587</v>
+        <v>0.99678722224176453</v>
       </c>
       <c r="BD12">
-        <v>2163.367646302027</v>
+        <v>58.900925567650859</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7942,16 +7942,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.97905997046933124</v>
+        <v>0.99419544959877137</v>
       </c>
       <c r="AB13">
-        <v>383.90054139559413</v>
+        <v>106.41675735585797</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7984,10 +7984,10 @@
         <v>428</v>
       </c>
       <c r="AO13">
-        <v>0.9878316475733655</v>
+        <v>0.99770761097472849</v>
       </c>
       <c r="AP13">
-        <v>223.0864611549656</v>
+        <v>42.027132129978384</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -8020,10 +8020,10 @@
         <v>574</v>
       </c>
       <c r="BC13">
-        <v>0.99114508565756532</v>
+        <v>0.98831275563045873</v>
       </c>
       <c r="BD13">
-        <v>162.34009627796874</v>
+        <v>214.26614677492421</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8088,16 +8088,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99854662761279667</v>
+        <v>0.98845903150961834</v>
       </c>
       <c r="AB14">
-        <v>26.645160432060571</v>
+        <v>211.58442232366301</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -8130,10 +8130,10 @@
         <v>430</v>
       </c>
       <c r="AO14">
-        <v>0.99689519939751359</v>
+        <v>0.99870209313763569</v>
       </c>
       <c r="AP14">
-        <v>56.921344378917169</v>
+        <v>23.794959143345142</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -8163,13 +8163,13 @@
         <v>575</v>
       </c>
       <c r="BB14" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="BC14">
-        <v>0.94616153753972931</v>
+        <v>0.97803702976044449</v>
       </c>
       <c r="BD14">
-        <v>987.03847843829612</v>
+        <v>402.65445439185123</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8234,16 +8234,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.9983436906516876</v>
+        <v>0.98176582039027138</v>
       </c>
       <c r="AB15">
-        <v>30.365671385728113</v>
+        <v>334.29329284502461</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -8276,10 +8276,10 @@
         <v>432</v>
       </c>
       <c r="AO15">
-        <v>0.99750210533018213</v>
+        <v>0.99805167070369571</v>
       </c>
       <c r="AP15">
-        <v>45.794735613327241</v>
+        <v>35.719370432245356</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -8309,13 +8309,13 @@
         <v>576</v>
       </c>
       <c r="BB15" t="s">
-        <v>577</v>
+        <v>350</v>
       </c>
       <c r="BC15">
-        <v>0.99735612831742793</v>
+        <v>0.94616153753972931</v>
       </c>
       <c r="BD15">
-        <v>48.47098084715428</v>
+        <v>987.03847843829612</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8380,16 +8380,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99886682122259174</v>
+        <v>0.99794257572004419</v>
       </c>
       <c r="AB16">
-        <v>20.774944252484079</v>
+        <v>37.719445132522388</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -8419,13 +8419,13 @@
         <v>433</v>
       </c>
       <c r="AN16" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="AO16">
-        <v>0.98092770889280956</v>
+        <v>0.99864153733447103</v>
       </c>
       <c r="AP16">
-        <v>349.65867029849198</v>
+        <v>24.905148868031663</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -8452,16 +8452,16 @@
         <v>491</v>
       </c>
       <c r="BA16" t="s">
+        <v>577</v>
+      </c>
+      <c r="BB16" t="s">
         <v>578</v>
       </c>
-      <c r="BB16" t="s">
-        <v>579</v>
-      </c>
       <c r="BC16">
-        <v>0.99021846023257276</v>
+        <v>0.99735612831742793</v>
       </c>
       <c r="BD16">
-        <v>179.32822906950017</v>
+        <v>48.47098084715428</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8526,16 +8526,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99830231855562213</v>
+        <v>0.99330431978332978</v>
       </c>
       <c r="AB17">
-        <v>31.124159813595057</v>
+        <v>122.75413730562111</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -8562,16 +8562,16 @@
         <v>373</v>
       </c>
       <c r="AM17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN17" t="s">
-        <v>350</v>
+        <v>436</v>
       </c>
       <c r="AO17">
-        <v>0.96316479569784719</v>
+        <v>0.99556268839291095</v>
       </c>
       <c r="AP17">
-        <v>675.31207887280175</v>
+        <v>81.350712796633118</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -8598,16 +8598,16 @@
         <v>493</v>
       </c>
       <c r="BA17" t="s">
+        <v>579</v>
+      </c>
+      <c r="BB17" t="s">
         <v>580</v>
       </c>
-      <c r="BB17" t="s">
-        <v>581</v>
-      </c>
       <c r="BC17">
-        <v>0.99302778580016682</v>
+        <v>0.99021846023257276</v>
       </c>
       <c r="BD17">
-        <v>127.82392699694152</v>
+        <v>179.32822906950017</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8672,16 +8672,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="Z18" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AA18">
-        <v>0.99887089404231622</v>
+        <v>0.97905997046933124</v>
       </c>
       <c r="AB18">
-        <v>20.700275890869406</v>
+        <v>383.90054139559413</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8708,16 +8708,16 @@
         <v>375</v>
       </c>
       <c r="AM18" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN18" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="AO18">
-        <v>0.99829462257458279</v>
+        <v>0.98819688225969682</v>
       </c>
       <c r="AP18">
-        <v>31.265252799315078</v>
+        <v>216.39049190555826</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8744,16 +8744,16 @@
         <v>495</v>
       </c>
       <c r="BA18" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB18" t="s">
         <v>582</v>
       </c>
-      <c r="BB18" t="s">
-        <v>583</v>
-      </c>
       <c r="BC18">
-        <v>0.93089405249526469</v>
+        <v>0.99302778580016682</v>
       </c>
       <c r="BD18">
-        <v>1266.9423709201483</v>
+        <v>127.82392699694152</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8818,16 +8818,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="Z19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99870336240961599</v>
+        <v>0.99854662761279667</v>
       </c>
       <c r="AB19">
-        <v>23.771689157039763</v>
+        <v>26.645160432060571</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8854,16 +8854,16 @@
         <v>377</v>
       </c>
       <c r="AM19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO19">
-        <v>0.99621233314208923</v>
+        <v>0.99750210533018213</v>
       </c>
       <c r="AP19">
-        <v>69.440559061696689</v>
+        <v>45.794735613327241</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8890,16 +8890,16 @@
         <v>497</v>
       </c>
       <c r="BA19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="BB19" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="BC19">
-        <v>0.98355967005268352</v>
+        <v>0.97218956380622079</v>
       </c>
       <c r="BD19">
-        <v>301.40604903413595</v>
+        <v>509.85799688595205</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8964,16 +8964,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="Z20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99732110244768524</v>
+        <v>0.9983436906516876</v>
       </c>
       <c r="AB20">
-        <v>49.113121792437113</v>
+        <v>30.365671385728113</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -9000,16 +9000,16 @@
         <v>379</v>
       </c>
       <c r="AM20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN20" t="s">
-        <v>440</v>
+        <v>338</v>
       </c>
       <c r="AO20">
-        <v>0.99869874972548245</v>
+        <v>0.98092770889280956</v>
       </c>
       <c r="AP20">
-        <v>23.856255032822389</v>
+        <v>349.65867029849198</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -9036,16 +9036,16 @@
         <v>499</v>
       </c>
       <c r="BA20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="BB20" t="s">
-        <v>586</v>
+        <v>350</v>
       </c>
       <c r="BC20">
-        <v>0.99648308811729225</v>
+        <v>0.97591598065988894</v>
       </c>
       <c r="BD20">
-        <v>64.476717849642213</v>
+        <v>441.54035456870389</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9110,16 +9110,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="Z21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA21">
-        <v>0.99727495176003056</v>
+        <v>0.99886682122259174</v>
       </c>
       <c r="AB21">
-        <v>49.959217732772544</v>
+        <v>20.774944252484079</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -9152,10 +9152,10 @@
         <v>442</v>
       </c>
       <c r="AO21">
-        <v>0.99720193846171157</v>
+        <v>0.99829462257458279</v>
       </c>
       <c r="AP21">
-        <v>51.297794868621132</v>
+        <v>31.265252799315078</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -9182,16 +9182,16 @@
         <v>501</v>
       </c>
       <c r="BA21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="BB21" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="BC21">
-        <v>0.98779966071713954</v>
+        <v>0.9437657388784082</v>
       </c>
       <c r="BD21">
-        <v>223.67288685244134</v>
+        <v>1030.9614538958492</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9256,16 +9256,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="AA22">
-        <v>0.98747067058472104</v>
+        <v>0.99830231855562213</v>
       </c>
       <c r="AB22">
-        <v>229.70437261344725</v>
+        <v>31.124159813595057</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -9298,10 +9298,10 @@
         <v>444</v>
       </c>
       <c r="AO22">
-        <v>0.99858912444516823</v>
+        <v>0.99621233314208923</v>
       </c>
       <c r="AP22">
-        <v>25.866051838582347</v>
+        <v>69.440559061696689</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -9328,16 +9328,16 @@
         <v>503</v>
       </c>
       <c r="BA22" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="BB22" t="s">
-        <v>590</v>
+        <v>348</v>
       </c>
       <c r="BC22">
-        <v>0.99604247516580058</v>
+        <v>0.99536692897647694</v>
       </c>
       <c r="BD22">
-        <v>72.554621960323615</v>
+        <v>84.939635431255269</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9402,16 +9402,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Z23" t="s">
         <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.99858140874136669</v>
+        <v>0.99810840151368141</v>
       </c>
       <c r="AB23">
-        <v>26.007506408276679</v>
+        <v>34.679305582508199</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -9444,10 +9444,10 @@
         <v>446</v>
       </c>
       <c r="AO23">
-        <v>0.99809873109145164</v>
+        <v>0.99825578453224051</v>
       </c>
       <c r="AP23">
-        <v>34.856596656720825</v>
+        <v>31.977283575591127</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -9474,16 +9474,16 @@
         <v>505</v>
       </c>
       <c r="BA23" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="BB23" t="s">
-        <v>336</v>
+        <v>589</v>
       </c>
       <c r="BC23">
-        <v>0.98235584693125277</v>
+        <v>0.99563161774290432</v>
       </c>
       <c r="BD23">
-        <v>323.47613959369914</v>
+        <v>80.087008046754136</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s">
         <v>347</v>
       </c>
       <c r="AA24">
-        <v>0.9980447041381848</v>
+        <v>0.99727495176003056</v>
       </c>
       <c r="AB24">
-        <v>35.847090799945306</v>
+        <v>49.959217732772544</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -9590,10 +9590,10 @@
         <v>448</v>
       </c>
       <c r="AO24">
-        <v>0.99670212772821787</v>
+        <v>0.99763984073088841</v>
       </c>
       <c r="AP24">
-        <v>60.460991649339221</v>
+        <v>43.269586600378275</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9620,16 +9620,16 @@
         <v>507</v>
       </c>
       <c r="BA24" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="BB24" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="BC24">
-        <v>0.99246863181599732</v>
+        <v>0.99284590877035406</v>
       </c>
       <c r="BD24">
-        <v>138.07508337338285</v>
+        <v>131.158339210175</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9694,16 +9694,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="Z25" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="AA25">
-        <v>0.99348252287636563</v>
+        <v>0.98747067058472104</v>
       </c>
       <c r="AB25">
-        <v>119.48708059996392</v>
+        <v>229.70437261344725</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9736,10 +9736,10 @@
         <v>450</v>
       </c>
       <c r="AO25">
-        <v>0.99870483393763032</v>
+        <v>0.9878316475733655</v>
       </c>
       <c r="AP25">
-        <v>23.744711143443137</v>
+        <v>223.0864611549656</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9766,16 +9766,16 @@
         <v>509</v>
       </c>
       <c r="BA25" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="BB25" t="s">
-        <v>595</v>
+        <v>338</v>
       </c>
       <c r="BC25">
-        <v>0.99412039195829205</v>
+        <v>0.98180592470173533</v>
       </c>
       <c r="BD25">
-        <v>107.79281409797902</v>
+        <v>333.55804713485287</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9840,16 +9840,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA26">
-        <v>0.9962850624543711</v>
+        <v>0.99858140874136669</v>
       </c>
       <c r="AB26">
-        <v>68.107188336529873</v>
+        <v>26.007506408276679</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9882,10 +9882,10 @@
         <v>452</v>
       </c>
       <c r="AO26">
-        <v>0.99940622505963084</v>
+        <v>0.99689519939751359</v>
       </c>
       <c r="AP26">
-        <v>10.885873906767051</v>
+        <v>56.921344378917169</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9912,16 +9912,16 @@
         <v>511</v>
       </c>
       <c r="BA26" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="BB26" t="s">
-        <v>583</v>
+        <v>350</v>
       </c>
       <c r="BC26">
-        <v>0.97589985979527272</v>
+        <v>0.95957195194316591</v>
       </c>
       <c r="BD26">
-        <v>441.83590375333313</v>
+        <v>741.18088104195795</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9986,16 +9986,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="Z27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA27">
-        <v>0.97645815754785015</v>
+        <v>0.9980447041381848</v>
       </c>
       <c r="AB27">
-        <v>431.60044495608111</v>
+        <v>35.847090799945306</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -10028,10 +10028,10 @@
         <v>454</v>
       </c>
       <c r="AO27">
-        <v>0.99870209313763569</v>
+        <v>0.99670212772821787</v>
       </c>
       <c r="AP27">
-        <v>23.794959143345142</v>
+        <v>60.460991649339221</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -10058,16 +10058,16 @@
         <v>513</v>
       </c>
       <c r="BA27" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="BB27" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="BC27">
-        <v>0.99502210016107762</v>
+        <v>0.99232897920121688</v>
       </c>
       <c r="BD27">
-        <v>91.26149704691008</v>
+        <v>140.63538131102445</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10132,16 +10132,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA28">
-        <v>0.99860543314421912</v>
+        <v>0.97645815754785015</v>
       </c>
       <c r="AB28">
-        <v>25.567059022649978</v>
+        <v>431.60044495608111</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -10174,10 +10174,10 @@
         <v>456</v>
       </c>
       <c r="AO28">
-        <v>0.99805167070369571</v>
+        <v>0.99870483393763032</v>
       </c>
       <c r="AP28">
-        <v>35.719370432245356</v>
+        <v>23.744711143443137</v>
       </c>
       <c r="AR28" t="s">
         <v>270</v>
@@ -10204,16 +10204,16 @@
         <v>515</v>
       </c>
       <c r="BA28" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="BB28" t="s">
-        <v>346</v>
+        <v>597</v>
       </c>
       <c r="BC28">
-        <v>0.99536692897647694</v>
+        <v>0.9205295464439136</v>
       </c>
       <c r="BD28">
-        <v>84.939635431255269</v>
+        <v>1456.9583151949184</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10278,16 +10278,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="Z29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA29">
-        <v>0.99604289943123792</v>
+        <v>0.99860543314421912</v>
       </c>
       <c r="AB29">
-        <v>72.546843760638723</v>
+        <v>25.567059022649978</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -10320,10 +10320,10 @@
         <v>458</v>
       </c>
       <c r="AO29">
-        <v>0.99864153733447103</v>
+        <v>0.99940622505963084</v>
       </c>
       <c r="AP29">
-        <v>24.905148868031663</v>
+        <v>10.885873906767051</v>
       </c>
       <c r="AR29" t="s">
         <v>270</v>
@@ -10350,16 +10350,16 @@
         <v>517</v>
       </c>
       <c r="BA29" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="BB29" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="BC29">
-        <v>0.99563161774290432</v>
+        <v>0.98881218539944515</v>
       </c>
       <c r="BD29">
-        <v>80.087008046754136</v>
+        <v>205.10993434350485</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10424,16 +10424,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA30">
-        <v>0.99586101480039024</v>
+        <v>0.99604289943123792</v>
       </c>
       <c r="AB30">
-        <v>75.881395326178321</v>
+        <v>72.546843760638723</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -10466,10 +10466,10 @@
         <v>460</v>
       </c>
       <c r="AO30">
-        <v>0.99556268839291095</v>
+        <v>0.99869874972548245</v>
       </c>
       <c r="AP30">
-        <v>81.350712796633118</v>
+        <v>23.856255032822389</v>
       </c>
       <c r="AR30" t="s">
         <v>270</v>
@@ -10496,16 +10496,16 @@
         <v>519</v>
       </c>
       <c r="BA30" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="BB30" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="BC30">
-        <v>0.99284590877035406</v>
+        <v>0.93089405249526469</v>
       </c>
       <c r="BD30">
-        <v>131.158339210175</v>
+        <v>1266.9423709201483</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10570,16 +10570,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="Z31" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA31">
-        <v>0.99812715296949239</v>
+        <v>0.99586101480039024</v>
       </c>
       <c r="AB31">
-        <v>34.33552889264039</v>
+        <v>75.881395326178321</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -10609,13 +10609,13 @@
         <v>461</v>
       </c>
       <c r="AN31" t="s">
-        <v>336</v>
+        <v>462</v>
       </c>
       <c r="AO31">
-        <v>0.98819688225969682</v>
+        <v>0.99720193846171157</v>
       </c>
       <c r="AP31">
-        <v>216.39049190555826</v>
+        <v>51.297794868621132</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -10642,16 +10642,16 @@
         <v>521</v>
       </c>
       <c r="BA31" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="BB31" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="BC31">
-        <v>0.98180592470173533</v>
+        <v>0.98355967005268352</v>
       </c>
       <c r="BD31">
-        <v>333.55804713485287</v>
+        <v>301.40604903413595</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10716,16 +10716,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="Z32" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="AA32">
-        <v>0.98845903150961834</v>
+        <v>0.96199717699083387</v>
       </c>
       <c r="AB32">
-        <v>211.58442232366301</v>
+        <v>696.71842183471267</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10752,16 +10752,16 @@
         <v>403</v>
       </c>
       <c r="AM32" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN32" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO32">
-        <v>0.99796586165341161</v>
+        <v>0.99858912444516823</v>
       </c>
       <c r="AP32">
-        <v>37.292536354119903</v>
+        <v>25.866051838582347</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -10788,16 +10788,16 @@
         <v>523</v>
       </c>
       <c r="BA32" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="BB32" t="s">
-        <v>606</v>
+        <v>350</v>
       </c>
       <c r="BC32">
-        <v>0.99764862450771852</v>
+        <v>0.96140381292129873</v>
       </c>
       <c r="BD32">
-        <v>43.108550691828107</v>
+        <v>707.59676310952364</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10862,16 +10862,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="Z33" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AA33">
-        <v>0.98176582039027138</v>
+        <v>0.99548081999408422</v>
       </c>
       <c r="AB33">
-        <v>334.29329284502461</v>
+        <v>82.851633441789744</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10898,16 +10898,16 @@
         <v>405</v>
       </c>
       <c r="AM33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN33" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO33">
-        <v>0.99811838305018963</v>
+        <v>0.99809873109145164</v>
       </c>
       <c r="AP33">
-        <v>34.496310746523356</v>
+        <v>34.856596656720825</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -10934,16 +10934,16 @@
         <v>525</v>
       </c>
       <c r="BA33" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="BB33" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="BC33">
-        <v>0.99678722224176453</v>
+        <v>0.99490784156958001</v>
       </c>
       <c r="BD33">
-        <v>58.900925567650859</v>
+        <v>93.356237891033686</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11008,16 +11008,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="Z34" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AA34">
-        <v>0.99810840151368141</v>
+        <v>0.99887089404231622</v>
       </c>
       <c r="AB34">
-        <v>34.679305582508199</v>
+        <v>20.700275890869406</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -11044,16 +11044,16 @@
         <v>407</v>
       </c>
       <c r="AM34" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN34" t="s">
-        <v>467</v>
+        <v>350</v>
       </c>
       <c r="AO34">
-        <v>0.99192535126433146</v>
+        <v>0.96316479569784719</v>
       </c>
       <c r="AP34">
-        <v>148.0352268205892</v>
+        <v>675.31207887280175</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -11080,16 +11080,16 @@
         <v>527</v>
       </c>
       <c r="BA34" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BB34" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BC34">
-        <v>0.98831275563045873</v>
+        <v>0.99560371543286275</v>
       </c>
       <c r="BD34">
-        <v>214.26614677492421</v>
+        <v>80.598550397515965</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11154,16 +11154,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="Z35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AA35">
-        <v>0.99744350359843614</v>
+        <v>0.99870336240961599</v>
       </c>
       <c r="AB35">
-        <v>46.86910069533748</v>
+        <v>23.771689157039763</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -11193,13 +11193,13 @@
         <v>468</v>
       </c>
       <c r="AN35" t="s">
-        <v>337</v>
+        <v>469</v>
       </c>
       <c r="AO35">
-        <v>0.98949004263841422</v>
+        <v>0.99192535126433146</v>
       </c>
       <c r="AP35">
-        <v>192.68255162907312</v>
+        <v>148.0352268205892</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
@@ -11226,16 +11226,16 @@
         <v>529</v>
       </c>
       <c r="BA35" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="BB35" t="s">
-        <v>353</v>
+        <v>609</v>
       </c>
       <c r="BC35">
-        <v>0.97803702976044449</v>
+        <v>0.99663140513677484</v>
       </c>
       <c r="BD35">
-        <v>402.65445439185123</v>
+        <v>61.757572492461378</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11300,16 +11300,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Z36" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AA36">
-        <v>0.9968826832446267</v>
+        <v>0.99732110244768524</v>
       </c>
       <c r="AB36">
-        <v>57.150807181843469</v>
+        <v>49.113121792437113</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -11336,16 +11336,16 @@
         <v>411</v>
       </c>
       <c r="AM36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN36" t="s">
-        <v>470</v>
+        <v>338</v>
       </c>
       <c r="AO36">
-        <v>0.99514593439357002</v>
+        <v>0.98949004263841422</v>
       </c>
       <c r="AP36">
-        <v>88.991202784549174</v>
+        <v>192.68255162907312</v>
       </c>
       <c r="AR36" t="s">
         <v>270</v>
@@ -11372,16 +11372,16 @@
         <v>531</v>
       </c>
       <c r="BA36" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="BB36" t="s">
-        <v>350</v>
+        <v>611</v>
       </c>
       <c r="BC36">
-        <v>0.97218956380622079</v>
+        <v>0.99246863181599732</v>
       </c>
       <c r="BD36">
-        <v>509.85799688595205</v>
+        <v>138.07508337338285</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11446,16 +11446,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="Z37" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AA37">
-        <v>0.96199717699083387</v>
+        <v>0.99744350359843614</v>
       </c>
       <c r="AB37">
-        <v>696.71842183471267</v>
+        <v>46.86910069533748</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -11488,10 +11488,10 @@
         <v>472</v>
       </c>
       <c r="AO37">
-        <v>0.9969234886911541</v>
+        <v>0.99876486181024959</v>
       </c>
       <c r="AP37">
-        <v>56.402707328841686</v>
+        <v>22.644200145424321</v>
       </c>
       <c r="AR37" t="s">
         <v>270</v>
@@ -11518,16 +11518,16 @@
         <v>533</v>
       </c>
       <c r="BA37" t="s">
+        <v>612</v>
+      </c>
+      <c r="BB37" t="s">
         <v>613</v>
       </c>
-      <c r="BB37" t="s">
-        <v>350</v>
-      </c>
       <c r="BC37">
-        <v>0.97591598065988894</v>
+        <v>0.99412039195829205</v>
       </c>
       <c r="BD37">
-        <v>441.54035456870389</v>
+        <v>107.79281409797902</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11592,16 +11592,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z38" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="AA38">
-        <v>0.99548081999408422</v>
+        <v>0.9968826832446267</v>
       </c>
       <c r="AB38">
-        <v>82.851633441789744</v>
+        <v>57.150807181843469</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -11634,10 +11634,10 @@
         <v>474</v>
       </c>
       <c r="AO38">
-        <v>0.99781438034778358</v>
+        <v>0.99796586165341161</v>
       </c>
       <c r="AP38">
-        <v>40.069693623967019</v>
+        <v>37.292536354119903</v>
       </c>
       <c r="AR38" t="s">
         <v>270</v>
@@ -11667,13 +11667,13 @@
         <v>614</v>
       </c>
       <c r="BB38" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="BC38">
-        <v>0.9437657388784082</v>
+        <v>0.97589985979527272</v>
       </c>
       <c r="BD38">
-        <v>1030.9614538958492</v>
+        <v>441.83590375333313</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11738,16 +11738,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="Z39" t="s">
         <v>359</v>
       </c>
       <c r="AA39">
-        <v>0.99905729110642394</v>
+        <v>0.99348252287636563</v>
       </c>
       <c r="AB39">
-        <v>17.282996382227537</v>
+        <v>119.48708059996392</v>
       </c>
       <c r="AD39" t="s">
         <v>270</v>
@@ -11780,10 +11780,10 @@
         <v>476</v>
       </c>
       <c r="AO39">
-        <v>0.99682717865030179</v>
+        <v>0.99811838305018963</v>
       </c>
       <c r="AP39">
-        <v>58.168391411134159</v>
+        <v>34.496310746523356</v>
       </c>
       <c r="AR39" t="s">
         <v>270</v>
@@ -11810,16 +11810,16 @@
         <v>537</v>
       </c>
       <c r="BA39" t="s">
+        <v>615</v>
+      </c>
+      <c r="BB39" t="s">
         <v>616</v>
       </c>
-      <c r="BB39" t="s">
-        <v>350</v>
-      </c>
       <c r="BC39">
-        <v>0.95957195194316591</v>
+        <v>0.99502210016107762</v>
       </c>
       <c r="BD39">
-        <v>741.18088104195795</v>
+        <v>91.26149704691008</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11884,16 +11884,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z40" t="s">
         <v>360</v>
       </c>
       <c r="AA40">
-        <v>0.99419544959877137</v>
+        <v>0.9962850624543711</v>
       </c>
       <c r="AB40">
-        <v>106.41675735585797</v>
+        <v>68.107188336529873</v>
       </c>
       <c r="AD40" t="s">
         <v>270</v>
@@ -11926,10 +11926,10 @@
         <v>478</v>
       </c>
       <c r="AO40">
-        <v>0.99770761097472849</v>
+        <v>0.99514593439357002</v>
       </c>
       <c r="AP40">
-        <v>42.027132129978384</v>
+        <v>88.991202784549174</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -11962,10 +11962,10 @@
         <v>618</v>
       </c>
       <c r="BC40">
-        <v>0.99232897920121688</v>
+        <v>0.99114508565756532</v>
       </c>
       <c r="BD40">
-        <v>140.63538131102445</v>
+        <v>162.34009627796874</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12000,10 +12000,10 @@
         <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99825578453224051</v>
+        <v>0.9969234886911541</v>
       </c>
       <c r="AP41">
-        <v>31.977283575591127</v>
+        <v>56.402707328841686</v>
       </c>
       <c r="AR41" t="s">
         <v>270</v>
@@ -12036,10 +12036,10 @@
         <v>620</v>
       </c>
       <c r="BC41">
-        <v>0.9205295464439136</v>
+        <v>0.99648308811729225</v>
       </c>
       <c r="BD41">
-        <v>1456.9583151949184</v>
+        <v>64.476717849642213</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12074,10 +12074,10 @@
         <v>622</v>
       </c>
       <c r="BC42">
-        <v>0.98881218539944515</v>
+        <v>0.98779966071713954</v>
       </c>
       <c r="BD42">
-        <v>205.10993434350485</v>
+        <v>223.67288685244134</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12112,10 +12112,10 @@
         <v>624</v>
       </c>
       <c r="BC43">
-        <v>0.95726256957223688</v>
+        <v>0.99604247516580058</v>
       </c>
       <c r="BD43">
-        <v>783.51955784232393</v>
+        <v>72.554621960323615</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12147,13 +12147,13 @@
         <v>625</v>
       </c>
       <c r="BB44" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="BC44">
-        <v>0.96140381292129873</v>
+        <v>0.98235584693125277</v>
       </c>
       <c r="BD44">
-        <v>707.59676310952364</v>
+        <v>323.47613959369914</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12185,13 +12185,13 @@
         <v>626</v>
       </c>
       <c r="BB45" t="s">
-        <v>627</v>
+        <v>350</v>
       </c>
       <c r="BC45">
-        <v>0.99490784156958001</v>
+        <v>0.934538160869965</v>
       </c>
       <c r="BD45">
-        <v>93.356237891033686</v>
+        <v>1200.1337173839754</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>551</v>
       </c>
       <c r="BA46" t="s">
+        <v>627</v>
+      </c>
+      <c r="BB46" t="s">
         <v>628</v>
       </c>
-      <c r="BB46" t="s">
-        <v>629</v>
-      </c>
       <c r="BC46">
-        <v>0.99560371543286275</v>
+        <v>0.98822137145239475</v>
       </c>
       <c r="BD46">
-        <v>80.598550397515965</v>
+        <v>215.94152337276336</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12258,16 +12258,16 @@
         <v>553</v>
       </c>
       <c r="BA47" t="s">
+        <v>629</v>
+      </c>
+      <c r="BB47" t="s">
         <v>630</v>
       </c>
-      <c r="BB47" t="s">
-        <v>631</v>
-      </c>
       <c r="BC47">
-        <v>0.99663140513677484</v>
+        <v>0.99234935324205875</v>
       </c>
       <c r="BD47">
-        <v>61.757572492461378</v>
+        <v>140.26185722892211</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12296,16 +12296,16 @@
         <v>555</v>
       </c>
       <c r="BA48" t="s">
+        <v>631</v>
+      </c>
+      <c r="BB48" t="s">
         <v>632</v>
       </c>
-      <c r="BB48" t="s">
-        <v>350</v>
-      </c>
       <c r="BC48">
-        <v>0.934538160869965</v>
+        <v>0.99361371414581767</v>
       </c>
       <c r="BD48">
-        <v>1200.1337173839754</v>
+        <v>117.0819073266757</v>
       </c>
     </row>
     <row r="49" spans="44:56">
@@ -12340,10 +12340,10 @@
         <v>634</v>
       </c>
       <c r="BC49">
-        <v>0.98822137145239475</v>
+        <v>0.99637036284424008</v>
       </c>
       <c r="BD49">
-        <v>215.94152337276336</v>
+        <v>66.543347855598327</v>
       </c>
     </row>
     <row r="50" spans="44:56">
@@ -12378,10 +12378,10 @@
         <v>636</v>
       </c>
       <c r="BC50">
-        <v>0.99234935324205875</v>
+        <v>0.99571574761974857</v>
       </c>
       <c r="BD50">
-        <v>140.26185722892211</v>
+        <v>78.544626971276415</v>
       </c>
     </row>
     <row r="51" spans="44:56">
@@ -12413,13 +12413,13 @@
         <v>637</v>
       </c>
       <c r="BB51" t="s">
-        <v>638</v>
+        <v>339</v>
       </c>
       <c r="BC51">
-        <v>0.99361371414581767</v>
+        <v>0.97902641975794957</v>
       </c>
       <c r="BD51">
-        <v>117.0819073266757</v>
+        <v>384.51563777092457</v>
       </c>
     </row>
     <row r="52" spans="44:56">
@@ -12448,16 +12448,16 @@
         <v>563</v>
       </c>
       <c r="BA52" t="s">
+        <v>638</v>
+      </c>
+      <c r="BB52" t="s">
         <v>639</v>
       </c>
-      <c r="BB52" t="s">
-        <v>640</v>
-      </c>
       <c r="BC52">
-        <v>0.99637036284424008</v>
+        <v>0.95726256957223688</v>
       </c>
       <c r="BD52">
-        <v>66.543347855598327</v>
+        <v>783.51955784232393</v>
       </c>
     </row>
     <row r="53" spans="44:56">
@@ -12486,16 +12486,16 @@
         <v>565</v>
       </c>
       <c r="BA53" t="s">
+        <v>640</v>
+      </c>
+      <c r="BB53" t="s">
         <v>641</v>
       </c>
-      <c r="BB53" t="s">
-        <v>642</v>
-      </c>
       <c r="BC53">
-        <v>0.99571574761974857</v>
+        <v>0.99603752315790417</v>
       </c>
       <c r="BD53">
-        <v>78.544626971276415</v>
+        <v>72.64540877175618</v>
       </c>
     </row>
     <row r="54" spans="44:56">
@@ -12524,16 +12524,16 @@
         <v>567</v>
       </c>
       <c r="BA54" t="s">
+        <v>642</v>
+      </c>
+      <c r="BB54" t="s">
         <v>643</v>
       </c>
-      <c r="BB54" t="s">
-        <v>355</v>
-      </c>
       <c r="BC54">
-        <v>0.97902641975794957</v>
+        <v>0.88199812838352587</v>
       </c>
       <c r="BD54">
-        <v>384.51563777092457</v>
+        <v>2163.367646302027</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A7E4FA2-CD64-4B6D-B237-D2CD46BDBA55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E0D0C1-E2F7-4769-907F-B3CBCC770B16}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -12654,7 +12654,7 @@
         <v>644</v>
       </c>
       <c r="K11" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="L11">
         <v>3.1880690460590064</v>
@@ -12687,7 +12687,7 @@
         <v>706</v>
       </c>
       <c r="X11" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="Y11">
         <v>32.783999999999999</v>
@@ -12722,7 +12722,7 @@
         <v>646</v>
       </c>
       <c r="K12" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="L12">
         <v>6.8219170694949156</v>
@@ -12755,7 +12755,7 @@
         <v>708</v>
       </c>
       <c r="X12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Y12">
         <v>36.320999999999998</v>
@@ -12790,7 +12790,7 @@
         <v>648</v>
       </c>
       <c r="K13" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="L13">
         <v>20.428642188273205</v>
@@ -12823,7 +12823,7 @@
         <v>710</v>
       </c>
       <c r="X13" t="s">
-        <v>612</v>
+        <v>583</v>
       </c>
       <c r="Y13">
         <v>43.956000000000003</v>
@@ -12858,7 +12858,7 @@
         <v>650</v>
       </c>
       <c r="K14" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="L14">
         <v>30.572093860622111</v>
@@ -12891,7 +12891,7 @@
         <v>712</v>
       </c>
       <c r="X14" t="s">
-        <v>613</v>
+        <v>584</v>
       </c>
       <c r="Y14">
         <v>62.099249999999998</v>
@@ -12926,7 +12926,7 @@
         <v>652</v>
       </c>
       <c r="K15" t="s">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="L15">
         <v>15.257265136698221</v>
@@ -12959,7 +12959,7 @@
         <v>714</v>
       </c>
       <c r="X15" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="Y15">
         <v>0.38324999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>654</v>
       </c>
       <c r="K16" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="L16">
         <v>11.827617201120189</v>
@@ -13027,7 +13027,7 @@
         <v>716</v>
       </c>
       <c r="X16" t="s">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="Y16">
         <v>56.725499999999997</v>
@@ -13062,7 +13062,7 @@
         <v>656</v>
       </c>
       <c r="K17" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="L17">
         <v>8.2886361396336365</v>
@@ -13095,7 +13095,7 @@
         <v>718</v>
       </c>
       <c r="X17" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="Y17">
         <v>58.03275</v>
@@ -13130,7 +13130,7 @@
         <v>658</v>
       </c>
       <c r="K18" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="L18">
         <v>26.915511431987859</v>
@@ -13163,7 +13163,7 @@
         <v>720</v>
       </c>
       <c r="X18" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="Y18">
         <v>14.47725</v>
@@ -13198,7 +13198,7 @@
         <v>660</v>
       </c>
       <c r="K19" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="L19">
         <v>7.5025171344716721</v>
@@ -13231,7 +13231,7 @@
         <v>722</v>
       </c>
       <c r="X19" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="Y19">
         <v>13.051</v>
@@ -13266,7 +13266,7 @@
         <v>662</v>
       </c>
       <c r="K20" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="L20">
         <v>21.508336570084424</v>
@@ -13299,7 +13299,7 @@
         <v>724</v>
       </c>
       <c r="X20" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="Y20">
         <v>22.079249999999998</v>
@@ -13334,7 +13334,7 @@
         <v>664</v>
       </c>
       <c r="K21" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="L21">
         <v>39.857504639772579</v>
@@ -13367,7 +13367,7 @@
         <v>726</v>
       </c>
       <c r="X21" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="Y21">
         <v>28.995750000000001</v>
@@ -13402,7 +13402,7 @@
         <v>666</v>
       </c>
       <c r="K22" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="L22">
         <v>7.0903888161806279</v>
@@ -13435,7 +13435,7 @@
         <v>728</v>
       </c>
       <c r="X22" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="Y22">
         <v>117.89700000000001</v>
@@ -13470,7 +13470,7 @@
         <v>668</v>
       </c>
       <c r="K23" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="L23">
         <v>16.900662525397827</v>
@@ -13503,7 +13503,7 @@
         <v>730</v>
       </c>
       <c r="X23" t="s">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="Y23">
         <v>71.912499999999994</v>
@@ -13538,7 +13538,7 @@
         <v>670</v>
       </c>
       <c r="K24" t="s">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="L24">
         <v>2.5242004930684354</v>
@@ -13571,7 +13571,7 @@
         <v>732</v>
       </c>
       <c r="X24" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Y24">
         <v>10.469749999999999</v>
@@ -13606,7 +13606,7 @@
         <v>672</v>
       </c>
       <c r="K25" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="L25">
         <v>5.423126107176425</v>
@@ -13639,7 +13639,7 @@
         <v>734</v>
       </c>
       <c r="X25" t="s">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="Y25">
         <v>81.302250000000001</v>
@@ -13674,7 +13674,7 @@
         <v>674</v>
       </c>
       <c r="K26" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="L26">
         <v>8.2996449615793466</v>
@@ -13707,7 +13707,7 @@
         <v>736</v>
       </c>
       <c r="X26" t="s">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="Y26">
         <v>17.654499999999999</v>
@@ -13742,7 +13742,7 @@
         <v>676</v>
       </c>
       <c r="K27" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="L27">
         <v>8.1047047321444712</v>
@@ -13775,7 +13775,7 @@
         <v>738</v>
       </c>
       <c r="X27" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="Y27">
         <v>62.444249999999997</v>
@@ -13810,7 +13810,7 @@
         <v>678</v>
       </c>
       <c r="K28" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="L28">
         <v>15.547155865570664</v>
@@ -13843,7 +13843,7 @@
         <v>740</v>
       </c>
       <c r="X28" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="Y28">
         <v>20.298249999999999</v>
@@ -13878,7 +13878,7 @@
         <v>680</v>
       </c>
       <c r="K29" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="L29">
         <v>23.639478129461853</v>
@@ -13911,7 +13911,7 @@
         <v>742</v>
       </c>
       <c r="X29" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="Y29">
         <v>38.15925</v>
@@ -13946,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="K30" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="L30">
         <v>12.287407796473463</v>
@@ -13979,7 +13979,7 @@
         <v>744</v>
       </c>
       <c r="X30" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="Y30">
         <v>3.38625</v>
@@ -14014,7 +14014,7 @@
         <v>684</v>
       </c>
       <c r="K31" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="L31">
         <v>21.675684512539679</v>
@@ -14047,7 +14047,7 @@
         <v>746</v>
       </c>
       <c r="X31" t="s">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="Y31">
         <v>30.597750000000001</v>
@@ -14082,7 +14082,7 @@
         <v>686</v>
       </c>
       <c r="K32" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="L32">
         <v>12.920913180463023</v>
@@ -14115,7 +14115,7 @@
         <v>748</v>
       </c>
       <c r="X32" t="s">
-        <v>609</v>
+        <v>573</v>
       </c>
       <c r="Y32">
         <v>96.239249999999998</v>
@@ -14150,7 +14150,7 @@
         <v>688</v>
       </c>
       <c r="K33" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="L33">
         <v>23.376816650626843</v>
@@ -14183,7 +14183,7 @@
         <v>750</v>
       </c>
       <c r="X33" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="Y33">
         <v>28.459499999999998</v>
@@ -14218,7 +14218,7 @@
         <v>690</v>
       </c>
       <c r="K34" t="s">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="L34">
         <v>50.076680799526407</v>
@@ -14251,7 +14251,7 @@
         <v>752</v>
       </c>
       <c r="X34" t="s">
-        <v>591</v>
+        <v>625</v>
       </c>
       <c r="Y34">
         <v>33.609749999999998</v>
@@ -14286,7 +14286,7 @@
         <v>692</v>
       </c>
       <c r="K35" t="s">
-        <v>477</v>
+        <v>427</v>
       </c>
       <c r="L35">
         <v>44.351334115294186</v>
@@ -14319,7 +14319,7 @@
         <v>754</v>
       </c>
       <c r="X35" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Y35">
         <v>48.133499999999998</v>
@@ -14354,7 +14354,7 @@
         <v>694</v>
       </c>
       <c r="K36" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L36">
         <v>13.77281970660486</v>
@@ -14387,7 +14387,7 @@
         <v>756</v>
       </c>
       <c r="X36" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="Y36">
         <v>18.011749999999999</v>
@@ -14422,7 +14422,7 @@
         <v>696</v>
       </c>
       <c r="K37" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L37">
         <v>37.84172313097659</v>
@@ -14455,7 +14455,7 @@
         <v>758</v>
       </c>
       <c r="X37" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="Y37">
         <v>29.186250000000001</v>
@@ -14490,7 +14490,7 @@
         <v>698</v>
       </c>
       <c r="K38" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L38">
         <v>33.851015501811965</v>
@@ -14523,7 +14523,7 @@
         <v>760</v>
       </c>
       <c r="X38" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="Y38">
         <v>14.49</v>
@@ -14558,7 +14558,7 @@
         <v>700</v>
       </c>
       <c r="K39" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L39">
         <v>29.76120824924126</v>
@@ -14591,7 +14591,7 @@
         <v>762</v>
       </c>
       <c r="X39" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="Y39">
         <v>64.437749999999994</v>
@@ -14626,7 +14626,7 @@
         <v>702</v>
       </c>
       <c r="K40" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="L40">
         <v>24.336756153668478</v>
@@ -14659,7 +14659,7 @@
         <v>764</v>
       </c>
       <c r="X40" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="Y40">
         <v>59.085000000000001</v>
@@ -14694,7 +14694,7 @@
         <v>704</v>
       </c>
       <c r="K41" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="L41">
         <v>28.258903899090868</v>
@@ -14727,7 +14727,7 @@
         <v>766</v>
       </c>
       <c r="X41" t="s">
-        <v>587</v>
+        <v>621</v>
       </c>
       <c r="Y41">
         <v>37.460250000000002</v>
@@ -14762,7 +14762,7 @@
         <v>768</v>
       </c>
       <c r="X42" t="s">
-        <v>589</v>
+        <v>623</v>
       </c>
       <c r="Y42">
         <v>27.492750000000001</v>
@@ -14797,7 +14797,7 @@
         <v>770</v>
       </c>
       <c r="X43" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="Y43">
         <v>62.597250000000003</v>
@@ -14832,7 +14832,7 @@
         <v>772</v>
       </c>
       <c r="X44" t="s">
-        <v>614</v>
+        <v>585</v>
       </c>
       <c r="Y44">
         <v>17.07525</v>
@@ -14867,7 +14867,7 @@
         <v>774</v>
       </c>
       <c r="X45" t="s">
-        <v>571</v>
+        <v>642</v>
       </c>
       <c r="Y45">
         <v>0.42149999999999999</v>
@@ -14902,7 +14902,7 @@
         <v>776</v>
       </c>
       <c r="X46" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="Y46">
         <v>5.7389999999999999</v>
@@ -14937,7 +14937,7 @@
         <v>778</v>
       </c>
       <c r="X47" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="Y47">
         <v>1.81725</v>
@@ -14972,7 +14972,7 @@
         <v>780</v>
       </c>
       <c r="X48" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="Y48">
         <v>10.709250000000001</v>
@@ -15007,7 +15007,7 @@
         <v>782</v>
       </c>
       <c r="X49" t="s">
-        <v>607</v>
+        <v>571</v>
       </c>
       <c r="Y49">
         <v>15.222</v>
@@ -15042,7 +15042,7 @@
         <v>784</v>
       </c>
       <c r="X50" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
       <c r="Y50">
         <v>53.960999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>786</v>
       </c>
       <c r="X51" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="Y51">
         <v>33.036000000000001</v>
@@ -15112,7 +15112,7 @@
         <v>788</v>
       </c>
       <c r="X52" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Y52">
         <v>31.234500000000001</v>
@@ -15147,7 +15147,7 @@
         <v>790</v>
       </c>
       <c r="X53" t="s">
-        <v>569</v>
+        <v>640</v>
       </c>
       <c r="Y53">
         <v>29.806249999999999</v>
@@ -15182,7 +15182,7 @@
         <v>792</v>
       </c>
       <c r="X54" t="s">
-        <v>585</v>
+        <v>619</v>
       </c>
       <c r="Y54">
         <v>15.124000000000001</v>
@@ -15197,7 +15197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB69CD3E-6E4A-4896-AEFF-8AE3EEB2CADE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA962E6-1188-4A1A-94E1-3F96834ED502}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17014,7 +17014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10B7AC1-03B4-4B62-8538-00CBB9FC5FBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A9C3B0-84CE-4F1A-B135-5F6E35431E03}">
   <dimension ref="B2:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
